--- a/Design-Files/SM_Top_Board_v3.4/BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Design-Files/SM_Top_Board_v3.4/BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Design-Files\SM_Top_Board_v3.3\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Design-Files\SM_Top_Board_v3.4\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="516">
   <si>
     <t>Component list</t>
   </si>
@@ -1066,12 +1066,6 @@
     <t>Winsource</t>
   </si>
   <si>
-    <t>TLV75733PDBVR</t>
-  </si>
-  <si>
-    <t>C485517</t>
-  </si>
-  <si>
     <t>BD9876AEFJ-E2</t>
   </si>
   <si>
@@ -1082,15 +1076,6 @@
   </si>
   <si>
     <t>C516354</t>
-  </si>
-  <si>
-    <t>ISO7221ADR</t>
-  </si>
-  <si>
-    <t>C28037</t>
-  </si>
-  <si>
-    <t>ISO6761FDWR</t>
   </si>
   <si>
     <t>Digikey</t>
@@ -1224,12 +1209,6 @@
     <t>R38, RF1, RF2, RF3, RF4, RF5</t>
   </si>
   <si>
-    <t>U8, U9</t>
-  </si>
-  <si>
-    <t>U11</t>
-  </si>
-  <si>
     <t>0603B682K500NT</t>
   </si>
   <si>
@@ -1273,21 +1252,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">C7, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C38, C39</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">C3, </t>
     </r>
     <r>
@@ -1359,9 +1323,6 @@
     <t>Ali-E</t>
   </si>
   <si>
-    <t>C23, C24, C37</t>
-  </si>
-  <si>
     <t>C5, C6, C14, C29, C34, C35</t>
   </si>
   <si>
@@ -1437,12 +1398,6 @@
     <t>MSKSEMI</t>
   </si>
   <si>
-    <t>IC REG LINEAR 3.3V 1A SOT23-5</t>
-  </si>
-  <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
     <t>NO Step-down type 1 Step-down 1V~29.4V 7V~42V 3A 300kHz SOIC-8_EP_150mil DC-DC Converters ROHS</t>
   </si>
   <si>
@@ -1452,12 +1407,6 @@
     <t>ROHM Semicon</t>
   </si>
   <si>
-    <t>DGTL ISO 2500VRMS 2CH GP 8SOIC</t>
-  </si>
-  <si>
-    <t>GENERAL PURPOSE, 50-MBPS, SIX-CH</t>
-  </si>
-  <si>
     <t>USB 3.0 3A 1 Brick nogging 24 Female -35℃~+75℃ Type-C SMD USB Connectors ROHS</t>
   </si>
   <si>
@@ -1479,9 +1428,6 @@
     <t>Pololu</t>
   </si>
   <si>
-    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, CF1, CF2, Cx1, Cx2</t>
-  </si>
-  <si>
     <t>J7</t>
   </si>
   <si>
@@ -1498,14 +1444,261 @@
   </si>
   <si>
     <t>C48, C49</t>
+  </si>
+  <si>
+    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, Cx1, Cx2</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C23, C24</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>C44, C45</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>D16, D18</t>
+  </si>
+  <si>
+    <t>D17</t>
+  </si>
+  <si>
+    <t>D19</t>
+  </si>
+  <si>
+    <t>D20, D21</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>GRM155R62A104KE14D</t>
+  </si>
+  <si>
+    <t>C1608X5R1E106M080AC</t>
+  </si>
+  <si>
+    <t>C2012X5R1V226MT000E</t>
+  </si>
+  <si>
+    <t>ESD5302F-3/TR</t>
+  </si>
+  <si>
+    <t>SMAJ48A</t>
+  </si>
+  <si>
+    <t>FNR3015S3R9MT</t>
+  </si>
+  <si>
+    <t>RC0201FR-074K7L</t>
+  </si>
+  <si>
+    <t>AP63203WU-7</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 100V X5R 0402</t>
+  </si>
+  <si>
+    <t>Cap-0402</t>
+  </si>
+  <si>
+    <t>C162178</t>
+  </si>
+  <si>
+    <t>0.1uf</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 25V X5R 0603</t>
+  </si>
+  <si>
+    <t>Cap-0603</t>
+  </si>
+  <si>
+    <t>C2168289</t>
+  </si>
+  <si>
+    <t>CAP CER 22UF 35V X5R 0805</t>
+  </si>
+  <si>
+    <t>Cap-0805</t>
+  </si>
+  <si>
+    <t>TDK Corporation</t>
+  </si>
+  <si>
+    <t>C338080</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>16A 20V 7V 5V@Max Unidirectional SOT-23 TVS ROHS</t>
+  </si>
+  <si>
+    <t>Sot-23</t>
+  </si>
+  <si>
+    <t>WILLSEMI</t>
+  </si>
+  <si>
+    <t>C239643</t>
+  </si>
+  <si>
+    <t>TVS  Diode</t>
+  </si>
+  <si>
+    <t>TVS DIODE 48VWM 77.4VC DO214AC</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t>C223991</t>
+  </si>
+  <si>
+    <t>TVS Diode</t>
+  </si>
+  <si>
+    <t>TVS DIODE 3.3VWM 11.5VC MICROSMP</t>
+  </si>
+  <si>
+    <t>MicroSMP</t>
+  </si>
+  <si>
+    <t>C241899</t>
+  </si>
+  <si>
+    <t>MSP3V3HM3/89A</t>
+  </si>
+  <si>
+    <t>TVS DIODE 12VWM 19.9VC MICROSMP</t>
+  </si>
+  <si>
+    <t>C1973858</t>
+  </si>
+  <si>
+    <t>MSMP12A-M3/89A</t>
+  </si>
+  <si>
+    <t>ESD Diode</t>
+  </si>
+  <si>
+    <t>TVS DIODE 5.25VWM 17VC SOT23-6</t>
+  </si>
+  <si>
+    <t>C111212</t>
+  </si>
+  <si>
+    <t>USBLC6-4SC6</t>
+  </si>
+  <si>
+    <t>TVS DIODE 5.25VWM 17VC SOT666</t>
+  </si>
+  <si>
+    <t>SOT-666</t>
+  </si>
+  <si>
+    <t>C15999</t>
+  </si>
+  <si>
+    <t>USBLC6-2P6</t>
+  </si>
+  <si>
+    <t>1.5A 3.9uH ±20% 1.4A SMD,3x3mm Power Inductors ROHS</t>
+  </si>
+  <si>
+    <t>cjiang</t>
+  </si>
+  <si>
+    <t>C167751</t>
+  </si>
+  <si>
+    <t>3.9uH</t>
+  </si>
+  <si>
+    <t>RES SMD 4.7K OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
+    <t>Res-0201</t>
+  </si>
+  <si>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>IC REG BUCK 3.3V 2A TSOT26</t>
+  </si>
+  <si>
+    <t>TSOT-23-6</t>
+  </si>
+  <si>
+    <t>Diodes</t>
+  </si>
+  <si>
+    <t>C780769</t>
+  </si>
+  <si>
+    <t>DGTL ISO 3000VRMS 4CH GP 16SSOP</t>
+  </si>
+  <si>
+    <t>16-SSOP</t>
+  </si>
+  <si>
+    <t>C544482</t>
+  </si>
+  <si>
+    <t>ISO7740FDBQR</t>
+  </si>
+  <si>
+    <t>AUTOMOTIVE, GENERAL-PURPOSE, 50-</t>
+  </si>
+  <si>
+    <t>C5216383</t>
+  </si>
+  <si>
+    <t>ISO6762FQDWRQ1</t>
+  </si>
+  <si>
+    <t>Vishay Intertech</t>
+  </si>
+  <si>
+    <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>C138135.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
@@ -2014,7 +2207,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2304,6 +2497,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2313,7 +2509,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2658,7 +2863,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z91"/>
+  <dimension ref="A1:Z103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2694,14 +2899,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2749,7 +2954,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="107"/>
+      <c r="R3" s="108"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2773,7 +2978,7 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="108"/>
+      <c r="R4" s="109"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2795,7 +3000,7 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="108"/>
+      <c r="R5" s="109"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2815,7 +3020,7 @@
       <c r="O6" s="56"/>
       <c r="P6" s="56"/>
       <c r="Q6" s="56"/>
-      <c r="R6" s="108"/>
+      <c r="R6" s="109"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2835,7 +3040,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="108"/>
+      <c r="R7" s="109"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2855,7 +3060,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="108"/>
+      <c r="R8" s="109"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2913,7 +3118,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="109">
+      <c r="B10" s="106">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
@@ -2930,7 +3135,7 @@
         <v>254</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>202</v>
@@ -2939,7 +3144,7 @@
         <v>259</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="K10" s="38" t="s">
         <v>211</v>
@@ -2968,15 +3173,15 @@
     </row>
     <row r="11" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="109">
-        <f t="shared" ref="B11:B74" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="106">
+        <f t="shared" ref="B11:B86" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="77" t="s">
         <v>261</v>
       </c>
-      <c r="D11" s="82" t="s">
-        <v>441</v>
+      <c r="D11" s="78" t="s">
+        <v>434</v>
       </c>
       <c r="E11" s="79" t="s">
         <v>61</v>
@@ -3000,14 +3205,14 @@
         <v>212</v>
       </c>
       <c r="L11" s="78">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M11" s="72">
         <f>L11*20</f>
+        <v>260</v>
+      </c>
+      <c r="N11" s="72">
         <v>300</v>
-      </c>
-      <c r="N11" s="72">
-        <v>400</v>
       </c>
       <c r="O11" s="80" t="s">
         <v>286</v>
@@ -3017,13 +3222,13 @@
       </c>
       <c r="Q11" s="72">
         <f>N11*P11</f>
-        <v>0.55999999999999994</v>
+        <v>0.42</v>
       </c>
       <c r="R11" s="72"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="109">
+      <c r="B12" s="106">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -3031,7 +3236,7 @@
         <v>261</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>62</v>
@@ -3058,7 +3263,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="39">
-        <f t="shared" ref="M12:M70" si="1">L12*20</f>
+        <f t="shared" ref="M12:M82" si="1">L12*20</f>
         <v>40</v>
       </c>
       <c r="N12" s="39">
@@ -3078,7 +3283,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="109">
+      <c r="B13" s="106">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -3086,7 +3291,7 @@
         <v>261</v>
       </c>
       <c r="D13" s="78" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E13" s="79" t="s">
         <v>63</v>
@@ -3133,7 +3338,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="109">
+      <c r="B14" s="106">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3141,7 +3346,7 @@
         <v>261</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>64</v>
@@ -3188,7 +3393,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="109">
+      <c r="B15" s="106">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -3196,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D15" s="78" t="s">
-        <v>388</v>
+        <v>435</v>
       </c>
       <c r="E15" s="79" t="s">
         <v>65</v>
@@ -3220,11 +3425,11 @@
         <v>216</v>
       </c>
       <c r="L15" s="82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" s="72">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="N15" s="87">
         <v>100</v>
@@ -3243,7 +3448,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="109">
+      <c r="B16" s="106">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3251,16 +3456,16 @@
         <v>261</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="F16" s="37" t="s">
         <v>119</v>
       </c>
       <c r="G16" s="76" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H16" s="100" t="s">
         <v>186</v>
@@ -3269,7 +3474,7 @@
         <v>259</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="K16" s="38" t="s">
         <v>217</v>
@@ -3298,7 +3503,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="109">
+      <c r="B17" s="106">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -3353,7 +3558,7 @@
     </row>
     <row r="18" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="109">
+      <c r="B18" s="106">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -3408,7 +3613,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="109">
+      <c r="B19" s="106">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3463,7 +3668,7 @@
     </row>
     <row r="20" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="109">
+      <c r="B20" s="106">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -3518,7 +3723,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="109">
+      <c r="B21" s="106">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -3526,7 +3731,7 @@
         <v>261</v>
       </c>
       <c r="D21" s="78" t="s">
-        <v>401</v>
+        <v>436</v>
       </c>
       <c r="E21" s="79" t="s">
         <v>74</v>
@@ -3550,11 +3755,11 @@
         <v>224</v>
       </c>
       <c r="L21" s="78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M21" s="72">
         <f>L21*20</f>
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="N21" s="72">
         <v>100</v>
@@ -3573,7 +3778,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="109">
+      <c r="B22" s="106">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -3628,7 +3833,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="109">
+      <c r="B23" s="106">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -3683,7 +3888,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="109">
+      <c r="B24" s="106">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3691,7 +3896,7 @@
         <v>261</v>
       </c>
       <c r="D24" s="78" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E24" s="79" t="s">
         <v>72</v>
@@ -3738,7 +3943,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="109">
+      <c r="B25" s="106">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3793,227 +3998,227 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="109">
-        <f t="shared" si="0"/>
+      <c r="B26" s="106">
+        <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="77" t="s">
+      <c r="C26" s="55" t="s">
         <v>261</v>
       </c>
-      <c r="D26" s="78" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="81" t="s">
-        <v>364</v>
-      </c>
-      <c r="F26" s="78" t="s">
+      <c r="D26" s="37" t="s">
+        <v>437</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="G26" s="81" t="s">
-        <v>385</v>
-      </c>
-      <c r="H26" s="101" t="s">
-        <v>200</v>
-      </c>
-      <c r="I26" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J26" s="78" t="s">
-        <v>365</v>
-      </c>
-      <c r="K26" s="81" t="s">
-        <v>375</v>
-      </c>
-      <c r="L26" s="78">
+      <c r="G26" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J26" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="K26" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="L26" s="37">
         <v>1</v>
       </c>
-      <c r="M26" s="72">
+      <c r="M26" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N26" s="72">
+      <c r="N26" s="37">
         <v>100</v>
       </c>
-      <c r="O26" s="80" t="s">
+      <c r="O26" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="P26" s="72">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="Q26" s="72">
-        <f t="shared" ref="Q26" si="15">N26*P26</f>
-        <v>0.33999999999999997</v>
-      </c>
-      <c r="R26" s="68"/>
+      <c r="P26" s="110">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q26" s="110">
+        <f>P26*N26</f>
+        <v>0.25</v>
+      </c>
+      <c r="R26" s="37"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="109">
-        <f t="shared" si="0"/>
+      <c r="B27" s="111">
+        <f t="shared" ref="B27" si="15">ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
       <c r="C27" s="55" t="s">
         <v>261</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>374</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="H27" s="99" t="s">
+      <c r="D27" s="78" t="s">
+        <v>438</v>
+      </c>
+      <c r="E27" s="78" t="s">
+        <v>459</v>
+      </c>
+      <c r="F27" s="78" t="s">
+        <v>460</v>
+      </c>
+      <c r="G27" s="78" t="s">
+        <v>451</v>
+      </c>
+      <c r="H27" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="I27" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J27" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="K27" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="L27" s="37">
+      <c r="I27" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J27" s="78" t="s">
+        <v>461</v>
+      </c>
+      <c r="K27" s="78" t="s">
+        <v>462</v>
+      </c>
+      <c r="L27" s="78">
         <v>1</v>
       </c>
       <c r="M27" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N27" s="39">
-        <v>30</v>
-      </c>
-      <c r="O27" s="57" t="s">
+      <c r="N27" s="78">
+        <v>50</v>
+      </c>
+      <c r="O27" s="113" t="s">
         <v>286</v>
       </c>
-      <c r="P27" s="39">
-        <v>0.2525</v>
-      </c>
-      <c r="Q27" s="39">
+      <c r="P27" s="112">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="Q27" s="112">
         <f t="shared" ref="Q27" si="16">P27*N27</f>
-        <v>7.5750000000000002</v>
-      </c>
-      <c r="R27" s="69"/>
+        <v>0.53499999999999992</v>
+      </c>
+      <c r="R27" s="78"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="109">
-        <f t="shared" si="0"/>
+      <c r="B28" s="106">
+        <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
       <c r="C28" s="55" t="s">
         <v>261</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>447</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>76</v>
+        <v>439</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>463</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>124</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="H28" s="99" t="s">
-        <v>187</v>
+        <v>464</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>452</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>188</v>
       </c>
       <c r="I28" s="37" t="s">
         <v>259</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="K28" s="38" t="s">
-        <v>226</v>
+        <v>465</v>
+      </c>
+      <c r="K28" s="37" t="s">
+        <v>217</v>
       </c>
       <c r="L28" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="39">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N28" s="39">
-        <v>41</v>
-      </c>
-      <c r="O28" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="37">
+        <v>21</v>
+      </c>
+      <c r="O28" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="P28" s="39">
-        <v>0.89410000000000001</v>
-      </c>
-      <c r="Q28" s="39">
-        <f t="shared" ref="Q28" si="17">P28*N28</f>
-        <v>36.658099999999997</v>
-      </c>
-      <c r="R28" s="39"/>
+      <c r="P28" s="110">
+        <v>0.39529999999999998</v>
+      </c>
+      <c r="Q28" s="110">
+        <f>P28*N28</f>
+        <v>8.3012999999999995</v>
+      </c>
+      <c r="R28" s="37"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="109">
+      <c r="B29" s="106">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="C29" s="77" t="s">
         <v>261</v>
       </c>
-      <c r="D29" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="F29" s="37" t="s">
+      <c r="D29" s="78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="81" t="s">
+        <v>359</v>
+      </c>
+      <c r="F29" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="G29" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>307</v>
-      </c>
-      <c r="K29" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="L29" s="37">
+      <c r="G29" s="81" t="s">
+        <v>378</v>
+      </c>
+      <c r="H29" s="101" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J29" s="78" t="s">
+        <v>360</v>
+      </c>
+      <c r="K29" s="81" t="s">
+        <v>370</v>
+      </c>
+      <c r="L29" s="78">
         <v>1</v>
       </c>
-      <c r="M29" s="39">
+      <c r="M29" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N29" s="39">
+      <c r="N29" s="72">
         <v>100</v>
       </c>
-      <c r="O29" s="57" t="s">
+      <c r="O29" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="P29" s="39">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="Q29" s="39">
-        <f t="shared" ref="Q29" si="18">P29*N29</f>
-        <v>0.31</v>
-      </c>
-      <c r="R29" s="39"/>
+      <c r="P29" s="72">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="Q29" s="72">
+        <f t="shared" ref="Q29" si="17">N29*P29</f>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R29" s="68"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="109">
+      <c r="B30" s="106">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -4021,1303 +4226,1299 @@
         <v>261</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>17</v>
+        <v>369</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H30" s="99" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I30" s="37" t="s">
         <v>259</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L30" s="37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M30" s="39">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="N30" s="39">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="O30" s="57" t="s">
         <v>286</v>
       </c>
       <c r="P30" s="39">
-        <v>5.4999999999999997E-3</v>
+        <v>0.2525</v>
       </c>
       <c r="Q30" s="39">
-        <f t="shared" ref="Q30" si="19">P30*N30</f>
-        <v>0.54999999999999993</v>
-      </c>
-      <c r="R30" s="39"/>
+        <f t="shared" ref="Q30:Q31" si="18">P30*N30</f>
+        <v>7.5750000000000002</v>
+      </c>
+      <c r="R30" s="69"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="109">
+      <c r="B31" s="111">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C31" s="77" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D31" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="79" t="s">
-        <v>79</v>
+        <v>440</v>
+      </c>
+      <c r="E31" s="78" t="s">
+        <v>466</v>
       </c>
       <c r="F31" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G31" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="H31" s="96" t="s">
-        <v>191</v>
-      </c>
-      <c r="I31" s="78" t="s">
-        <v>259</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="G31" s="78" t="s">
+        <v>453</v>
+      </c>
+      <c r="H31" s="78" t="s">
+        <v>468</v>
+      </c>
+      <c r="I31" s="78"/>
       <c r="J31" s="78" t="s">
-        <v>309</v>
-      </c>
-      <c r="K31" s="79" t="s">
-        <v>259</v>
+        <v>469</v>
+      </c>
+      <c r="K31" s="78" t="s">
+        <v>470</v>
       </c>
       <c r="L31" s="78">
+        <v>2</v>
+      </c>
+      <c r="M31" s="39">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N31" s="78">
+        <v>45</v>
+      </c>
+      <c r="O31" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="P31" s="112">
+        <v>0.2087</v>
+      </c>
+      <c r="Q31" s="112">
+        <f t="shared" si="18"/>
+        <v>9.3915000000000006</v>
+      </c>
+      <c r="R31" s="78"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="106">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>261</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>433</v>
+      </c>
+      <c r="E32" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="H32" s="99" t="s">
+        <v>187</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="K32" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="L32" s="37">
+        <v>2</v>
+      </c>
+      <c r="M32" s="39">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N32" s="39">
+        <v>41</v>
+      </c>
+      <c r="O32" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P32" s="39">
+        <v>0.89410000000000001</v>
+      </c>
+      <c r="Q32" s="39">
+        <f t="shared" ref="Q32" si="19">P32*N32</f>
+        <v>36.658099999999997</v>
+      </c>
+      <c r="R32" s="39"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="106">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="55" t="s">
+        <v>261</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="K33" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="L33" s="37">
         <v>1</v>
       </c>
-      <c r="M31" s="72">
+      <c r="M33" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N31" s="72">
-        <v>30</v>
-      </c>
-      <c r="O31" s="80" t="s">
+      <c r="N33" s="39">
+        <v>100</v>
+      </c>
+      <c r="O33" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P31" s="72">
-        <v>4.87E-2</v>
-      </c>
-      <c r="Q31" s="72">
-        <f t="shared" ref="Q31" si="20">N31*P31</f>
-        <v>1.4610000000000001</v>
-      </c>
-      <c r="R31" s="72"/>
-    </row>
-    <row r="32" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="109">
+      <c r="P33" s="39">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="Q33" s="39">
+        <f t="shared" ref="Q33" si="20">P33*N33</f>
+        <v>0.31</v>
+      </c>
+      <c r="R33" s="39"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="106">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="55" t="s">
+        <v>261</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="H34" s="99" t="s">
+        <v>183</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J34" s="37" t="s">
+        <v>308</v>
+      </c>
+      <c r="K34" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="L34" s="37">
+        <v>4</v>
+      </c>
+      <c r="M34" s="39">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="N34" s="39">
+        <v>100</v>
+      </c>
+      <c r="O34" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P34" s="39">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="Q34" s="39">
+        <f t="shared" ref="Q34" si="21">P34*N34</f>
+        <v>0.54999999999999993</v>
+      </c>
+      <c r="R34" s="39"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="106">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="77" t="s">
         <v>262</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="H32" s="99" t="s">
-        <v>192</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>310</v>
-      </c>
-      <c r="K32" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L32" s="37">
+      <c r="D35" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G35" s="79" t="s">
+        <v>125</v>
+      </c>
+      <c r="H35" s="96" t="s">
+        <v>191</v>
+      </c>
+      <c r="I35" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J35" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="K35" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L35" s="78">
         <v>1</v>
       </c>
-      <c r="M32" s="39">
+      <c r="M35" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N32" s="39">
+      <c r="N35" s="72">
         <v>30</v>
       </c>
-      <c r="O32" s="57" t="s">
+      <c r="O35" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="P32" s="39">
+      <c r="P35" s="72">
+        <v>4.87E-2</v>
+      </c>
+      <c r="Q35" s="72">
+        <f t="shared" ref="Q35" si="22">N35*P35</f>
+        <v>1.4610000000000001</v>
+      </c>
+      <c r="R35" s="72"/>
+    </row>
+    <row r="36" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="106">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="55" t="s">
+        <v>262</v>
+      </c>
+      <c r="D36" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H36" s="99" t="s">
+        <v>192</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="K36" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L36" s="37">
+        <v>1</v>
+      </c>
+      <c r="M36" s="39">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N36" s="39">
+        <v>30</v>
+      </c>
+      <c r="O36" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P36" s="39">
         <v>7.4300000000000005E-2</v>
       </c>
-      <c r="Q32" s="39">
-        <f t="shared" ref="Q32" si="21">P32*N32</f>
+      <c r="Q36" s="39">
+        <f t="shared" ref="Q36" si="23">P36*N36</f>
         <v>2.2290000000000001</v>
       </c>
-      <c r="R32" s="39"/>
-    </row>
-    <row r="33" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="109">
+      <c r="R36" s="39"/>
+    </row>
+    <row r="37" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="106">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C33" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="77" t="s">
         <v>262</v>
       </c>
-      <c r="D33" s="78" t="s">
-        <v>390</v>
-      </c>
-      <c r="E33" s="79" t="s">
+      <c r="D37" s="78" t="s">
+        <v>382</v>
+      </c>
+      <c r="E37" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="F33" s="78" t="s">
+      <c r="F37" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="G33" s="79" t="s">
+      <c r="G37" s="79" t="s">
         <v>230</v>
       </c>
-      <c r="H33" s="96" t="s">
+      <c r="H37" s="96" t="s">
         <v>192</v>
       </c>
-      <c r="I33" s="78" t="s">
+      <c r="I37" s="78" t="s">
         <v>230</v>
       </c>
-      <c r="J33" s="78" t="s">
+      <c r="J37" s="78" t="s">
         <v>311</v>
       </c>
-      <c r="K33" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L33" s="78">
+      <c r="K37" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L37" s="78">
         <v>2</v>
       </c>
-      <c r="M33" s="72">
+      <c r="M37" s="72">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N33" s="72">
+      <c r="N37" s="72">
         <v>60</v>
       </c>
-      <c r="O33" s="80" t="s">
+      <c r="O37" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="P33" s="72">
+      <c r="P37" s="72">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="Q33" s="72">
-        <f t="shared" ref="Q33" si="22">N33*P33</f>
+      <c r="Q37" s="72">
+        <f t="shared" ref="Q37" si="24">N37*P37</f>
         <v>1.734</v>
       </c>
-      <c r="R33" s="69"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="109">
+      <c r="R37" s="69"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="106">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="89" t="s">
         <v>262</v>
       </c>
-      <c r="D34" s="90" t="s">
-        <v>376</v>
-      </c>
-      <c r="E34" s="91" t="s">
-        <v>419</v>
-      </c>
-      <c r="F34" s="91" t="s">
+      <c r="D38" s="90" t="s">
+        <v>371</v>
+      </c>
+      <c r="E38" s="91" t="s">
+        <v>410</v>
+      </c>
+      <c r="F38" s="91" t="s">
         <v>254</v>
       </c>
-      <c r="G34" s="91" t="s">
-        <v>416</v>
-      </c>
-      <c r="H34" s="102" t="s">
-        <v>420</v>
-      </c>
-      <c r="I34" s="91" t="s">
-        <v>259</v>
-      </c>
-      <c r="J34" s="91" t="s">
-        <v>435</v>
-      </c>
-      <c r="K34" s="92" t="s">
-        <v>259</v>
-      </c>
-      <c r="L34" s="91">
+      <c r="G38" s="91" t="s">
+        <v>407</v>
+      </c>
+      <c r="H38" s="102" t="s">
+        <v>411</v>
+      </c>
+      <c r="I38" s="91" t="s">
+        <v>259</v>
+      </c>
+      <c r="J38" s="91" t="s">
+        <v>422</v>
+      </c>
+      <c r="K38" s="92" t="s">
+        <v>259</v>
+      </c>
+      <c r="L38" s="91">
         <v>8</v>
       </c>
-      <c r="M34" s="92">
+      <c r="M38" s="92">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N34" s="72">
+      <c r="N38" s="72">
         <v>165</v>
       </c>
-      <c r="O34" s="93" t="s">
+      <c r="O38" s="93" t="s">
         <v>286</v>
       </c>
-      <c r="P34" s="92">
+      <c r="P38" s="92">
         <v>0.14319999999999999</v>
       </c>
-      <c r="Q34" s="92">
-        <f t="shared" ref="Q34:Q35" si="23">P34*N34</f>
+      <c r="Q38" s="92">
+        <f t="shared" ref="Q38:Q39" si="25">P38*N38</f>
         <v>23.628</v>
       </c>
-      <c r="R34" s="94"/>
-    </row>
-    <row r="35" spans="1:26" s="95" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="88"/>
-      <c r="B35" s="109">
+      <c r="R38" s="94"/>
+    </row>
+    <row r="39" spans="1:26" s="95" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="88"/>
+      <c r="B39" s="106">
         <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="77" t="s">
         <v>262</v>
       </c>
-      <c r="D35" s="78" t="s">
-        <v>408</v>
-      </c>
-      <c r="E35" s="78" t="s">
-        <v>409</v>
-      </c>
-      <c r="F35" s="78" t="s">
-        <v>410</v>
-      </c>
-      <c r="G35" s="78" t="s">
-        <v>411</v>
-      </c>
-      <c r="H35" s="96" t="s">
+      <c r="D39" s="78" t="s">
+        <v>399</v>
+      </c>
+      <c r="E39" s="78" t="s">
+        <v>400</v>
+      </c>
+      <c r="F39" s="78" t="s">
+        <v>401</v>
+      </c>
+      <c r="G39" s="78" t="s">
+        <v>402</v>
+      </c>
+      <c r="H39" s="96" t="s">
         <v>193</v>
       </c>
-      <c r="I35" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J35" s="78" t="s">
-        <v>436</v>
-      </c>
-      <c r="K35" s="72" t="s">
-        <v>259</v>
-      </c>
-      <c r="L35" s="78">
+      <c r="I39" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J39" s="78" t="s">
+        <v>423</v>
+      </c>
+      <c r="K39" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L39" s="78">
         <v>2</v>
       </c>
-      <c r="M35" s="92">
+      <c r="M39" s="92">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N35" s="72">
+      <c r="N39" s="72">
         <v>45</v>
       </c>
-      <c r="O35" s="57" t="s">
+      <c r="O39" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P35" s="39">
+      <c r="P39" s="39">
         <v>0.1464</v>
       </c>
-      <c r="Q35" s="92">
-        <f t="shared" si="23"/>
+      <c r="Q39" s="92">
+        <f t="shared" si="25"/>
         <v>6.5880000000000001</v>
       </c>
-      <c r="R35" s="72"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="109">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="D36" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="79" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G36" s="85" t="s">
-        <v>127</v>
-      </c>
-      <c r="H36" s="96" t="s">
-        <v>194</v>
-      </c>
-      <c r="I36" s="78" t="s">
-        <v>312</v>
-      </c>
-      <c r="J36" s="78" t="s">
-        <v>313</v>
-      </c>
-      <c r="K36" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L36" s="78">
+      <c r="R39" s="72"/>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39"/>
+      <c r="Z39"/>
+    </row>
+    <row r="40" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="106">
+        <f>ROW(B40) - ROW($B$9)</f>
+        <v>31</v>
+      </c>
+      <c r="C40" s="55" t="s">
+        <v>262</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>471</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>472</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="K40" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L40" s="37">
         <v>1</v>
       </c>
-      <c r="M36" s="72">
+      <c r="M40" s="92">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N36" s="72">
+      <c r="N40" s="37">
         <v>30</v>
       </c>
-      <c r="O36" s="80" t="s">
+      <c r="O40" s="70" t="s">
         <v>286</v>
       </c>
-      <c r="P36" s="72">
+      <c r="P40" s="110">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="Q40" s="110">
+        <f>P40*N40</f>
+        <v>2.5920000000000001</v>
+      </c>
+      <c r="R40" s="37"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="111">
+        <f t="shared" ref="B41:B45" si="26">ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="77" t="s">
+        <v>475</v>
+      </c>
+      <c r="D41" s="78" t="s">
+        <v>442</v>
+      </c>
+      <c r="E41" s="78" t="s">
+        <v>476</v>
+      </c>
+      <c r="F41" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="G41" s="78" t="s">
+        <v>455</v>
+      </c>
+      <c r="H41" s="78" t="s">
+        <v>477</v>
+      </c>
+      <c r="I41" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J41" s="78" t="s">
+        <v>478</v>
+      </c>
+      <c r="K41" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L41" s="78">
+        <v>1</v>
+      </c>
+      <c r="M41" s="92">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N41" s="78">
+        <v>25</v>
+      </c>
+      <c r="O41" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="P41" s="112">
+        <v>0.1709</v>
+      </c>
+      <c r="Q41" s="112">
+        <f t="shared" ref="Q41" si="27">P41*N41</f>
+        <v>4.2725</v>
+      </c>
+      <c r="R41" s="78"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="106">
+        <f>ROW(B42) - ROW($B$9)</f>
+        <v>33</v>
+      </c>
+      <c r="C42" s="55" t="s">
+        <v>479</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>480</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="I42" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="K42" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L42" s="37">
+        <v>2</v>
+      </c>
+      <c r="M42" s="92">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N42" s="37">
+        <v>45</v>
+      </c>
+      <c r="O42" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="P42" s="110">
+        <v>0.1135</v>
+      </c>
+      <c r="Q42" s="110">
+        <f>P42*N42</f>
+        <v>5.1074999999999999</v>
+      </c>
+      <c r="R42" s="37"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="111">
+        <f t="shared" si="26"/>
+        <v>34</v>
+      </c>
+      <c r="C43" s="77" t="s">
+        <v>479</v>
+      </c>
+      <c r="D43" s="78" t="s">
+        <v>444</v>
+      </c>
+      <c r="E43" s="78" t="s">
+        <v>484</v>
+      </c>
+      <c r="F43" s="78" t="s">
+        <v>481</v>
+      </c>
+      <c r="G43" s="78" t="s">
+        <v>486</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="I43" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J43" s="78" t="s">
+        <v>485</v>
+      </c>
+      <c r="K43" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L43" s="78">
+        <v>1</v>
+      </c>
+      <c r="M43" s="92">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N43" s="78">
+        <v>21</v>
+      </c>
+      <c r="O43" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="P43" s="112">
+        <v>5.91E-2</v>
+      </c>
+      <c r="Q43" s="112">
+        <f t="shared" ref="Q43" si="28">P43*N43</f>
+        <v>1.2411000000000001</v>
+      </c>
+      <c r="R43" s="78"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="106">
+        <f>ROW(B44) - ROW($B$9)</f>
+        <v>35</v>
+      </c>
+      <c r="C44" s="55" t="s">
+        <v>487</v>
+      </c>
+      <c r="D44" s="37" t="s">
+        <v>445</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>488</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="G44" s="37" t="s">
+        <v>490</v>
+      </c>
+      <c r="H44" s="37" t="s">
+        <v>514</v>
+      </c>
+      <c r="I44" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J44" s="37" t="s">
+        <v>489</v>
+      </c>
+      <c r="K44" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L44" s="37">
+        <v>1</v>
+      </c>
+      <c r="M44" s="92">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N44" s="37">
+        <v>25</v>
+      </c>
+      <c r="O44" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="P44" s="110">
+        <v>0.17249999999999999</v>
+      </c>
+      <c r="Q44" s="110">
+        <f>P44*N44</f>
+        <v>4.3125</v>
+      </c>
+      <c r="R44" s="37"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="111">
+        <f t="shared" si="26"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="77" t="s">
+        <v>487</v>
+      </c>
+      <c r="D45" s="78" t="s">
+        <v>446</v>
+      </c>
+      <c r="E45" s="78" t="s">
+        <v>491</v>
+      </c>
+      <c r="F45" s="78" t="s">
+        <v>492</v>
+      </c>
+      <c r="G45" s="78" t="s">
+        <v>494</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>514</v>
+      </c>
+      <c r="I45" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J45" s="78" t="s">
+        <v>493</v>
+      </c>
+      <c r="K45" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L45" s="78">
+        <v>2</v>
+      </c>
+      <c r="M45" s="92">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N45" s="78">
+        <v>45</v>
+      </c>
+      <c r="O45" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="P45" s="112">
+        <v>0.2072</v>
+      </c>
+      <c r="Q45" s="112">
+        <f t="shared" ref="Q45" si="29">P45*N45</f>
+        <v>9.3239999999999998</v>
+      </c>
+      <c r="R45" s="78"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="106">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="77" t="s">
+        <v>264</v>
+      </c>
+      <c r="D46" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G46" s="85" t="s">
+        <v>127</v>
+      </c>
+      <c r="H46" s="96" t="s">
+        <v>194</v>
+      </c>
+      <c r="I46" s="78" t="s">
+        <v>312</v>
+      </c>
+      <c r="J46" s="78" t="s">
+        <v>313</v>
+      </c>
+      <c r="K46" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L46" s="78">
+        <v>1</v>
+      </c>
+      <c r="M46" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N46" s="72">
+        <v>30</v>
+      </c>
+      <c r="O46" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P46" s="72">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="Q36" s="72">
-        <f t="shared" ref="Q36" si="24">N36*P36</f>
+      <c r="Q46" s="72">
+        <f t="shared" ref="Q46" si="30">N46*P46</f>
         <v>1.68</v>
       </c>
-      <c r="R36" s="72"/>
-    </row>
-    <row r="37" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="109">
+      <c r="R46" s="72"/>
+    </row>
+    <row r="47" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="106">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="55" t="s">
         <v>263</v>
       </c>
-      <c r="D37" s="37" t="s">
+      <c r="D47" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="38" t="s">
+      <c r="E47" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F47" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="G37" s="38" t="s">
+      <c r="G47" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="H37" s="99" t="s">
+      <c r="H47" s="99" t="s">
         <v>188</v>
       </c>
-      <c r="I37" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J37" s="37" t="s">
+      <c r="I47" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J47" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="K37" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L37" s="37">
+      <c r="K47" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L47" s="37">
         <v>4</v>
       </c>
-      <c r="M37" s="39">
+      <c r="M47" s="39">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N37" s="39">
+      <c r="N47" s="39">
         <v>100</v>
       </c>
-      <c r="O37" s="57" t="s">
+      <c r="O47" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P37" s="39">
+      <c r="P47" s="39">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="Q37" s="39">
-        <f t="shared" ref="Q37" si="25">P37*N37</f>
+      <c r="Q47" s="39">
+        <f t="shared" ref="Q47" si="31">P47*N47</f>
         <v>2.9499999999999997</v>
       </c>
-      <c r="R37" s="39"/>
-    </row>
-    <row r="38" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="109">
+      <c r="R47" s="39"/>
+    </row>
+    <row r="48" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="106">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C38" s="77" t="s">
-        <v>423</v>
-      </c>
-      <c r="D38" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="77" t="s">
+        <v>414</v>
+      </c>
+      <c r="D48" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="E38" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="F38" s="37" t="s">
+      <c r="E48" s="37" t="s">
+        <v>421</v>
+      </c>
+      <c r="F48" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="G38" s="37" t="s">
+      <c r="G48" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="H38" s="37" t="s">
+      <c r="H48" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="I38" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J38" s="78" t="s">
+      <c r="I48" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J48" s="78" t="s">
         <v>316</v>
       </c>
-      <c r="K38" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L38" s="78">
+      <c r="K48" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L48" s="78">
         <v>1</v>
       </c>
-      <c r="M38" s="72">
+      <c r="M48" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N38" s="72">
+      <c r="N48" s="72">
         <v>21</v>
       </c>
-      <c r="O38" s="80" t="s">
+      <c r="O48" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="P38" s="72">
+      <c r="P48" s="72">
         <v>0.53559999999999997</v>
       </c>
-      <c r="Q38" s="72">
-        <f t="shared" ref="Q38" si="26">N38*P38</f>
+      <c r="Q48" s="72">
+        <f t="shared" ref="Q48" si="32">N48*P48</f>
         <v>11.247599999999998</v>
       </c>
-      <c r="R38" s="69"/>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="109">
+      <c r="R48" s="69"/>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="106">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="77" t="s">
-        <v>421</v>
-      </c>
-      <c r="D39" s="82" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="77" t="s">
+        <v>412</v>
+      </c>
+      <c r="D49" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="78" t="s">
-        <v>422</v>
-      </c>
-      <c r="F39" s="78" t="s">
+      <c r="E49" s="78" t="s">
+        <v>413</v>
+      </c>
+      <c r="F49" s="78" t="s">
         <v>254</v>
       </c>
-      <c r="G39" s="78" t="s">
-        <v>417</v>
-      </c>
-      <c r="H39" s="96" t="s">
-        <v>414</v>
-      </c>
-      <c r="I39" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J39" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K39" s="72" t="s">
-        <v>259</v>
-      </c>
-      <c r="L39" s="78">
+      <c r="G49" s="78" t="s">
+        <v>408</v>
+      </c>
+      <c r="H49" s="96" t="s">
+        <v>405</v>
+      </c>
+      <c r="I49" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J49" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K49" s="72" t="s">
+        <v>259</v>
+      </c>
+      <c r="L49" s="78">
         <v>2</v>
       </c>
-      <c r="M39" s="39">
+      <c r="M49" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N39" s="39">
+      <c r="N49" s="39">
         <v>42</v>
       </c>
-      <c r="O39" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="P39" s="39">
+      <c r="O49" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="P49" s="39">
         <v>2.2490000000000001</v>
       </c>
-      <c r="Q39" s="39">
-        <f t="shared" ref="Q39" si="27">P39*N39</f>
+      <c r="Q49" s="39">
+        <f t="shared" ref="Q49" si="33">P49*N49</f>
         <v>94.457999999999998</v>
       </c>
-      <c r="R39" s="69"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="109">
+      <c r="R49" s="69"/>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="106">
         <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="77" t="s">
         <v>266</v>
       </c>
-      <c r="D40" s="78" t="s">
+      <c r="D50" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="E40" s="79" t="s">
+      <c r="E50" s="79" t="s">
         <v>84</v>
       </c>
-      <c r="F40" s="78" t="s">
+      <c r="F50" s="78" t="s">
         <v>254</v>
       </c>
-      <c r="G40" s="79" t="s">
+      <c r="G50" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="H40" s="96" t="s">
+      <c r="H50" s="96" t="s">
         <v>196</v>
       </c>
-      <c r="I40" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J40" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K40" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L40" s="78">
+      <c r="I50" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J50" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K50" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L50" s="78">
         <v>1</v>
       </c>
-      <c r="M40" s="72">
+      <c r="M50" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N40" s="72">
+      <c r="N50" s="72">
         <v>21</v>
       </c>
-      <c r="O40" s="80" t="s">
+      <c r="O50" s="80" t="s">
         <v>317</v>
       </c>
-      <c r="P40" s="72">
+      <c r="P50" s="72">
         <v>1.2</v>
       </c>
-      <c r="Q40" s="72">
-        <f t="shared" ref="Q40" si="28">N40*P40</f>
+      <c r="Q50" s="72">
+        <f t="shared" ref="Q50" si="34">N50*P50</f>
         <v>25.2</v>
       </c>
-      <c r="R40" s="72"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="109">
+      <c r="R50" s="72"/>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="106">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="55" t="s">
         <v>266</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D51" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E41" s="38" t="s">
+      <c r="E51" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F51" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="G41" s="38" t="s">
+      <c r="G51" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="H41" s="99" t="s">
+      <c r="H51" s="99" t="s">
         <v>197</v>
       </c>
-      <c r="I41" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J41" s="37" t="s">
+      <c r="I51" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J51" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="K41" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L41" s="37">
+      <c r="K51" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L51" s="37">
         <v>1</v>
       </c>
-      <c r="M41" s="39">
+      <c r="M51" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N41" s="39">
+      <c r="N51" s="39">
         <v>30</v>
       </c>
-      <c r="O41" s="57" t="s">
+      <c r="O51" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P41" s="39">
+      <c r="P51" s="39">
         <v>4.65E-2</v>
       </c>
-      <c r="Q41" s="39">
-        <f t="shared" ref="Q41:Q43" si="29">P41*N41</f>
+      <c r="Q51" s="39">
+        <f t="shared" ref="Q51:Q53" si="35">P51*N51</f>
         <v>1.395</v>
       </c>
-      <c r="R41" s="39"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="109">
+      <c r="R51" s="39"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="106">
         <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="55" t="s">
-        <v>437</v>
-      </c>
-      <c r="D42" s="37" t="s">
-        <v>412</v>
-      </c>
-      <c r="E42" s="37" t="s">
-        <v>413</v>
-      </c>
-      <c r="F42" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="55" t="s">
+        <v>424</v>
+      </c>
+      <c r="D52" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="F52" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="G42" s="37">
+      <c r="G52" s="37">
         <v>533980367</v>
       </c>
-      <c r="H42" s="99" t="s">
-        <v>414</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J42" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K42" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="L42" s="37">
+      <c r="H52" s="99" t="s">
+        <v>405</v>
+      </c>
+      <c r="I52" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J52" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K52" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="L52" s="37">
         <v>1</v>
       </c>
-      <c r="M42" s="39">
+      <c r="M52" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N42" s="39">
+      <c r="N52" s="39">
         <v>21</v>
       </c>
-      <c r="O42" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="P42" s="39">
+      <c r="O52" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="P52" s="39">
         <v>1.167</v>
       </c>
-      <c r="Q42" s="39">
-        <f t="shared" si="29"/>
+      <c r="Q52" s="39">
+        <f t="shared" si="35"/>
         <v>24.507000000000001</v>
       </c>
-      <c r="R42" s="39"/>
-    </row>
-    <row r="43" spans="1:26" ht="36" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="109">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="55" t="s">
-        <v>437</v>
-      </c>
-      <c r="D43" s="78" t="s">
-        <v>442</v>
-      </c>
-      <c r="E43" s="78" t="s">
-        <v>444</v>
-      </c>
-      <c r="F43" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G43" s="78" t="s">
-        <v>443</v>
-      </c>
-      <c r="H43" s="78" t="s">
-        <v>445</v>
-      </c>
-      <c r="I43" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J43" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="K43" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="L43" s="37">
-        <v>1</v>
-      </c>
-      <c r="M43" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N43" s="39">
-        <v>20</v>
-      </c>
-      <c r="O43" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P43" s="39">
-        <v>6.8699999999999997E-2</v>
-      </c>
-      <c r="Q43" s="39">
-        <f t="shared" si="29"/>
-        <v>1.3739999999999999</v>
-      </c>
-      <c r="R43" s="39"/>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="109">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="C44" s="77" t="s">
-        <v>437</v>
-      </c>
-      <c r="D44" s="82" t="s">
-        <v>397</v>
-      </c>
-      <c r="E44" s="78" t="s">
-        <v>424</v>
-      </c>
-      <c r="F44" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G44" s="78" t="s">
-        <v>418</v>
-      </c>
-      <c r="H44" s="96" t="s">
-        <v>197</v>
-      </c>
-      <c r="I44" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J44" s="78" t="s">
-        <v>438</v>
-      </c>
-      <c r="K44" s="72" t="s">
-        <v>259</v>
-      </c>
-      <c r="L44" s="78">
-        <v>1</v>
-      </c>
-      <c r="M44" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N44" s="39">
-        <v>25</v>
-      </c>
-      <c r="O44" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P44" s="39">
-        <v>0.2044</v>
-      </c>
-      <c r="Q44" s="39">
-        <f>P44*N44</f>
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="R44" s="39"/>
-    </row>
-    <row r="45" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="109">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="C45" s="77" t="s">
-        <v>263</v>
-      </c>
-      <c r="D45" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G45" s="79" t="s">
-        <v>131</v>
-      </c>
-      <c r="H45" s="96" t="s">
-        <v>188</v>
-      </c>
-      <c r="I45" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J45" s="78" t="s">
-        <v>319</v>
-      </c>
-      <c r="K45" s="79" t="s">
-        <v>231</v>
-      </c>
-      <c r="L45" s="78">
-        <v>1</v>
-      </c>
-      <c r="M45" s="72">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N45" s="72">
-        <v>21</v>
-      </c>
-      <c r="O45" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P45" s="72">
-        <v>0.45629999999999998</v>
-      </c>
-      <c r="Q45" s="72">
-        <f t="shared" ref="Q45" si="30">N45*P45</f>
-        <v>9.5823</v>
-      </c>
-      <c r="R45" s="72"/>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="109">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C46" s="55" t="s">
-        <v>263</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="38" t="s">
-        <v>379</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G46" s="38" t="s">
-        <v>378</v>
-      </c>
-      <c r="H46" s="99" t="s">
-        <v>370</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J46" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="K46" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="L46" s="37">
-        <v>1</v>
-      </c>
-      <c r="M46" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N46" s="39">
-        <v>25</v>
-      </c>
-      <c r="O46" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P46" s="39">
-        <v>0.1012</v>
-      </c>
-      <c r="Q46" s="39">
-        <f t="shared" ref="Q46" si="31">P46*N46</f>
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="R46" s="68"/>
-    </row>
-    <row r="47" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="109">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="77" t="s">
-        <v>267</v>
-      </c>
-      <c r="D47" s="78" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="F47" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G47" s="79" t="s">
-        <v>132</v>
-      </c>
-      <c r="H47" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="I47" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J47" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K47" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L47" s="78">
-        <v>1</v>
-      </c>
-      <c r="M47" s="72">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N47" s="72">
-        <v>30</v>
-      </c>
-      <c r="O47" s="80" t="s">
-        <v>320</v>
-      </c>
-      <c r="P47" s="72">
-        <v>0.156</v>
-      </c>
-      <c r="Q47" s="72">
-        <f t="shared" ref="Q47" si="32">N47*P47</f>
-        <v>4.68</v>
-      </c>
-      <c r="R47" s="72"/>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="109">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C48" s="55" t="s">
-        <v>392</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>394</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G48" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="H48" s="99" t="s">
-        <v>396</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J48" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K48" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L48" s="37">
-        <v>1</v>
-      </c>
-      <c r="M48" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N48" s="39">
-        <v>20</v>
-      </c>
-      <c r="O48" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="P48" s="39">
-        <v>0.435</v>
-      </c>
-      <c r="Q48" s="39">
-        <f t="shared" ref="Q48" si="33">P48*N48</f>
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="R48" s="69" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="109">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="77" t="s">
-        <v>265</v>
-      </c>
-      <c r="D49" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="F49" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G49" s="79" t="s">
-        <v>133</v>
-      </c>
-      <c r="H49" s="96" t="s">
-        <v>199</v>
-      </c>
-      <c r="I49" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J49" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K49" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L49" s="78">
-        <v>2</v>
-      </c>
-      <c r="M49" s="72">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N49" s="72">
-        <v>42</v>
-      </c>
-      <c r="O49" s="80" t="s">
-        <v>440</v>
-      </c>
-      <c r="P49" s="72">
-        <v>1.58</v>
-      </c>
-      <c r="Q49" s="72">
-        <f t="shared" ref="Q49" si="34">N49*P49</f>
-        <v>66.36</v>
-      </c>
-      <c r="R49" s="72"/>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="109">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C50" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="D50" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="E50" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="F50" s="74" t="s">
-        <v>254</v>
-      </c>
-      <c r="G50" s="74" t="s">
-        <v>134</v>
-      </c>
-      <c r="H50" s="103" t="s">
-        <v>259</v>
-      </c>
-      <c r="I50" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="J50" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="K50" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="L50" s="74">
-        <v>4</v>
-      </c>
-      <c r="M50" s="58">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N50" s="58">
-        <f t="shared" ref="N50" si="35">M50+(M50*0.1)</f>
-        <v>88</v>
-      </c>
-      <c r="O50" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="P50" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q50" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="R50" s="58" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="36" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="109">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C51" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>415</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>425</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>439</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="H51" s="99" t="s">
-        <v>426</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="K51" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L51" s="37">
-        <v>4</v>
-      </c>
-      <c r="M51" s="39">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N51" s="39">
-        <v>85</v>
-      </c>
-      <c r="O51" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P51" s="39">
-        <v>0.21740000000000001</v>
-      </c>
-      <c r="Q51" s="39">
-        <f t="shared" ref="Q51" si="36">P51*N51</f>
-        <v>18.478999999999999</v>
-      </c>
-      <c r="R51" s="39"/>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="109">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="C52" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D52" s="78" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="F52" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G52" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="H52" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="I52" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J52" s="78" t="s">
-        <v>324</v>
-      </c>
-      <c r="K52" s="79" t="s">
-        <v>233</v>
-      </c>
-      <c r="L52" s="78">
-        <v>2</v>
-      </c>
-      <c r="M52" s="72">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N52" s="72">
-        <v>100</v>
-      </c>
-      <c r="O52" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P52" s="72">
-        <v>1E-3</v>
-      </c>
-      <c r="Q52" s="72">
-        <f t="shared" ref="Q52" si="37">N52*P52</f>
-        <v>0.1</v>
-      </c>
-      <c r="R52" s="72"/>
-    </row>
-    <row r="53" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="R52" s="39"/>
+    </row>
+    <row r="53" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="109">
+      <c r="B53" s="106">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E53" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G53" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="H53" s="99" t="s">
-        <v>184</v>
+        <v>424</v>
+      </c>
+      <c r="D53" s="78" t="s">
+        <v>428</v>
+      </c>
+      <c r="E53" s="78" t="s">
+        <v>430</v>
+      </c>
+      <c r="F53" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G53" s="78" t="s">
+        <v>429</v>
+      </c>
+      <c r="H53" s="78" t="s">
+        <v>431</v>
       </c>
       <c r="I53" s="37" t="s">
         <v>259</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="K53" s="38" t="s">
-        <v>234</v>
+        <v>432</v>
+      </c>
+      <c r="K53" s="39" t="s">
+        <v>259</v>
       </c>
       <c r="L53" s="37">
         <v>1</v>
@@ -5327,318 +5528,318 @@
         <v>20</v>
       </c>
       <c r="N53" s="39">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="O53" s="57" t="s">
         <v>286</v>
       </c>
       <c r="P53" s="39">
-        <v>1.4E-3</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="Q53" s="39">
-        <f t="shared" ref="Q53" si="38">P53*N53</f>
-        <v>0.13999999999999999</v>
+        <f t="shared" si="35"/>
+        <v>1.3739999999999999</v>
       </c>
       <c r="R53" s="39"/>
     </row>
-    <row r="54" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="109">
+      <c r="B54" s="106">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C54" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D54" s="78" t="s">
-        <v>33</v>
-      </c>
-      <c r="E54" s="79" t="s">
-        <v>92</v>
+        <v>424</v>
+      </c>
+      <c r="D54" s="82" t="s">
+        <v>389</v>
+      </c>
+      <c r="E54" s="78" t="s">
+        <v>415</v>
       </c>
       <c r="F54" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G54" s="79" t="s">
-        <v>163</v>
+        <v>254</v>
+      </c>
+      <c r="G54" s="78" t="s">
+        <v>409</v>
       </c>
       <c r="H54" s="96" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I54" s="78" t="s">
         <v>259</v>
       </c>
       <c r="J54" s="78" t="s">
-        <v>326</v>
-      </c>
-      <c r="K54" s="79" t="s">
-        <v>235</v>
+        <v>425</v>
+      </c>
+      <c r="K54" s="72" t="s">
+        <v>259</v>
       </c>
       <c r="L54" s="78">
         <v>1</v>
       </c>
-      <c r="M54" s="72">
+      <c r="M54" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N54" s="72">
-        <v>100</v>
-      </c>
-      <c r="O54" s="80" t="s">
+      <c r="N54" s="39">
+        <v>25</v>
+      </c>
+      <c r="O54" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P54" s="72">
-        <v>1.6000000000000001E-3</v>
-      </c>
-      <c r="Q54" s="72">
-        <f t="shared" ref="Q54" si="39">N54*P54</f>
-        <v>0.16</v>
-      </c>
-      <c r="R54" s="72"/>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P54" s="39">
+        <v>0.2044</v>
+      </c>
+      <c r="Q54" s="39">
+        <f>P54*N54</f>
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="R54" s="39"/>
+    </row>
+    <row r="55" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="109">
+      <c r="B55" s="106">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D55" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E55" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="F55" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G55" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="H55" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="I55" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J55" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="L55" s="37">
-        <v>2</v>
-      </c>
-      <c r="M55" s="39">
+      <c r="C55" s="77" t="s">
+        <v>263</v>
+      </c>
+      <c r="D55" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="F55" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G55" s="79" t="s">
+        <v>131</v>
+      </c>
+      <c r="H55" s="96" t="s">
+        <v>188</v>
+      </c>
+      <c r="I55" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J55" s="78" t="s">
+        <v>319</v>
+      </c>
+      <c r="K55" s="79" t="s">
+        <v>231</v>
+      </c>
+      <c r="L55" s="78">
+        <v>1</v>
+      </c>
+      <c r="M55" s="72">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N55" s="39">
-        <v>100</v>
-      </c>
-      <c r="O55" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N55" s="72">
+        <v>21</v>
+      </c>
+      <c r="O55" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="P55" s="39">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q55" s="39">
-        <f t="shared" ref="Q55" si="40">P55*N55</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R55" s="39"/>
+      <c r="P55" s="72">
+        <v>0.45629999999999998</v>
+      </c>
+      <c r="Q55" s="72">
+        <f t="shared" ref="Q55" si="36">N55*P55</f>
+        <v>9.5823</v>
+      </c>
+      <c r="R55" s="72"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="109">
+      <c r="B56" s="106">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D56" s="78" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="79" t="s">
-        <v>94</v>
-      </c>
-      <c r="F56" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G56" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="H56" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="I56" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J56" s="78" t="s">
-        <v>328</v>
-      </c>
-      <c r="K56" s="79" t="s">
-        <v>237</v>
-      </c>
-      <c r="L56" s="78">
-        <v>4</v>
-      </c>
-      <c r="M56" s="72">
+      <c r="C56" s="55" t="s">
+        <v>263</v>
+      </c>
+      <c r="D56" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="F56" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="G56" s="38" t="s">
+        <v>373</v>
+      </c>
+      <c r="H56" s="99" t="s">
+        <v>365</v>
+      </c>
+      <c r="I56" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J56" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="K56" s="38" t="s">
+        <v>372</v>
+      </c>
+      <c r="L56" s="37">
+        <v>1</v>
+      </c>
+      <c r="M56" s="39">
         <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="N56" s="72">
-        <v>100</v>
-      </c>
-      <c r="O56" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="N56" s="39">
+        <v>25</v>
+      </c>
+      <c r="O56" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P56" s="72">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q56" s="72">
-        <f t="shared" ref="Q56" si="41">N56*P56</f>
-        <v>0.13</v>
-      </c>
-      <c r="R56" s="72"/>
+      <c r="P56" s="39">
+        <v>0.1012</v>
+      </c>
+      <c r="Q56" s="39">
+        <f t="shared" ref="Q56:Q57" si="37">P56*N56</f>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="R56" s="68"/>
     </row>
     <row r="57" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="109">
+      <c r="B57" s="111">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D57" s="37" t="s">
-        <v>403</v>
+      <c r="C57" s="77" t="s">
+        <v>263</v>
+      </c>
+      <c r="D57" s="78" t="s">
+        <v>447</v>
       </c>
       <c r="E57" s="78" t="s">
-        <v>404</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="G57" s="37" t="s">
-        <v>405</v>
-      </c>
-      <c r="H57" s="99" t="s">
-        <v>201</v>
-      </c>
-      <c r="I57" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J57" s="37" t="s">
-        <v>406</v>
-      </c>
-      <c r="K57" s="38" t="s">
-        <v>407</v>
-      </c>
-      <c r="L57" s="37">
-        <v>2</v>
+        <v>495</v>
+      </c>
+      <c r="F57" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G57" s="78" t="s">
+        <v>456</v>
+      </c>
+      <c r="H57" s="78" t="s">
+        <v>496</v>
+      </c>
+      <c r="I57" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J57" s="78" t="s">
+        <v>497</v>
+      </c>
+      <c r="K57" s="78" t="s">
+        <v>498</v>
+      </c>
+      <c r="L57" s="78">
+        <v>1</v>
       </c>
       <c r="M57" s="39">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N57" s="39">
-        <v>45</v>
-      </c>
-      <c r="O57" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N57" s="78">
+        <v>30</v>
+      </c>
+      <c r="O57" s="113" t="s">
         <v>286</v>
       </c>
-      <c r="P57" s="39">
-        <v>2.9100000000000001E-2</v>
-      </c>
-      <c r="Q57" s="39">
-        <f t="shared" ref="Q57" si="42">P57*N57</f>
-        <v>1.3095000000000001</v>
-      </c>
-      <c r="R57" s="39"/>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P57" s="112">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="Q57" s="112">
+        <f t="shared" si="37"/>
+        <v>1.1759999999999999</v>
+      </c>
+      <c r="R57" s="78"/>
+    </row>
+    <row r="58" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="B58" s="109">
+      <c r="B58" s="106">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C58" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D58" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>373</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G58" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="H58" s="99" t="s">
-        <v>203</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J58" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="K58" s="39" t="s">
-        <v>361</v>
-      </c>
-      <c r="L58" s="37">
-        <v>8</v>
-      </c>
-      <c r="M58" s="37">
+      <c r="C58" s="77" t="s">
+        <v>267</v>
+      </c>
+      <c r="D58" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G58" s="79" t="s">
+        <v>132</v>
+      </c>
+      <c r="H58" s="96" t="s">
+        <v>198</v>
+      </c>
+      <c r="I58" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J58" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K58" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L58" s="78">
+        <v>1</v>
+      </c>
+      <c r="M58" s="72">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="N58" s="72">
-        <v>100</v>
-      </c>
-      <c r="O58" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="P58" s="37">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="Q58" s="37">
-        <f t="shared" ref="Q58" si="43">N58*P58</f>
-        <v>0.11</v>
-      </c>
-      <c r="R58" s="68"/>
+        <v>30</v>
+      </c>
+      <c r="O58" s="80" t="s">
+        <v>320</v>
+      </c>
+      <c r="P58" s="72">
+        <v>0.156</v>
+      </c>
+      <c r="Q58" s="72">
+        <f t="shared" ref="Q58" si="38">N58*P58</f>
+        <v>4.68</v>
+      </c>
+      <c r="R58" s="72"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="B59" s="109">
+      <c r="B59" s="106">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>269</v>
+        <v>384</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>36</v>
+        <v>259</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>96</v>
+        <v>386</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>135</v>
+        <v>254</v>
       </c>
       <c r="G59" s="38" t="s">
-        <v>167</v>
+        <v>387</v>
       </c>
       <c r="H59" s="99" t="s">
-        <v>202</v>
+        <v>388</v>
       </c>
       <c r="I59" s="37" t="s">
         <v>259</v>
@@ -5647,7 +5848,7 @@
         <v>259</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="L59" s="37">
         <v>1</v>
@@ -5657,188 +5858,192 @@
         <v>20</v>
       </c>
       <c r="N59" s="39">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O59" s="57" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="P59" s="39">
-        <v>1.8589999999999999E-2</v>
+        <v>0.435</v>
       </c>
       <c r="Q59" s="39">
-        <f t="shared" ref="Q59" si="44">P59*N59</f>
-        <v>0.55769999999999997</v>
-      </c>
-      <c r="R59" s="39"/>
+        <f t="shared" ref="Q59" si="39">P59*N59</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R59" s="69" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="109">
+      <c r="B60" s="106">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="C60" s="77" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D60" s="78" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E60" s="79" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F60" s="78" t="s">
-        <v>135</v>
+        <v>254</v>
       </c>
       <c r="G60" s="79" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="H60" s="96" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="I60" s="78" t="s">
         <v>259</v>
       </c>
       <c r="J60" s="78" t="s">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="K60" s="79" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="L60" s="78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60" s="72">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N60" s="72">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="O60" s="80" t="s">
-        <v>286</v>
+        <v>427</v>
       </c>
       <c r="P60" s="72">
-        <v>1.4E-3</v>
+        <v>1.58</v>
       </c>
       <c r="Q60" s="72">
-        <f t="shared" ref="Q60" si="45">N60*P60</f>
-        <v>0.13999999999999999</v>
+        <f t="shared" ref="Q60" si="40">N60*P60</f>
+        <v>66.36</v>
       </c>
       <c r="R60" s="72"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="B61" s="109">
+      <c r="B61" s="106">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D61" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E61" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="F61" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G61" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="H61" s="99" t="s">
-        <v>202</v>
-      </c>
-      <c r="I61" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J61" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K61" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="L61" s="37">
-        <v>1</v>
-      </c>
-      <c r="M61" s="39">
+      <c r="C61" s="73" t="s">
+        <v>232</v>
+      </c>
+      <c r="D61" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="E61" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" s="74" t="s">
+        <v>254</v>
+      </c>
+      <c r="G61" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="H61" s="103" t="s">
+        <v>259</v>
+      </c>
+      <c r="I61" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="J61" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="K61" s="75" t="s">
+        <v>259</v>
+      </c>
+      <c r="L61" s="74">
+        <v>4</v>
+      </c>
+      <c r="M61" s="58">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N61" s="39">
-        <v>50</v>
-      </c>
-      <c r="O61" s="57" t="s">
-        <v>320</v>
-      </c>
-      <c r="P61" s="39">
-        <v>4.6699999999999997E-3</v>
-      </c>
-      <c r="Q61" s="39">
-        <f t="shared" ref="Q61" si="46">P61*N61</f>
-        <v>0.23349999999999999</v>
-      </c>
-      <c r="R61" s="39"/>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="N61" s="58">
+        <f t="shared" ref="N61" si="41">M61+(M61*0.1)</f>
+        <v>88</v>
+      </c>
+      <c r="O61" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="P61" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q61" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="R61" s="58" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="109">
+      <c r="B62" s="106">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="C62" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D62" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="E62" s="79" t="s">
-        <v>99</v>
-      </c>
-      <c r="F62" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G62" s="79" t="s">
-        <v>170</v>
-      </c>
-      <c r="H62" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="I62" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J62" s="78" t="s">
-        <v>331</v>
-      </c>
-      <c r="K62" s="79" t="s">
-        <v>242</v>
-      </c>
-      <c r="L62" s="78">
-        <v>1</v>
-      </c>
-      <c r="M62" s="72">
+      <c r="C62" s="55" t="s">
+        <v>268</v>
+      </c>
+      <c r="D62" s="37" t="s">
+        <v>406</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>416</v>
+      </c>
+      <c r="F62" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="G62" s="37" t="s">
+        <v>322</v>
+      </c>
+      <c r="H62" s="99" t="s">
+        <v>417</v>
+      </c>
+      <c r="I62" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J62" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="K62" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L62" s="37">
+        <v>4</v>
+      </c>
+      <c r="M62" s="39">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N62" s="72">
-        <v>100</v>
-      </c>
-      <c r="O62" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="N62" s="39">
+        <v>85</v>
+      </c>
+      <c r="O62" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P62" s="72">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q62" s="72">
-        <f t="shared" ref="Q62" si="47">N62*P62</f>
-        <v>0.12</v>
-      </c>
-      <c r="R62" s="72"/>
+      <c r="P62" s="39">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="Q62" s="39">
+        <f t="shared" ref="Q62" si="42">P62*N62</f>
+        <v>18.478999999999999</v>
+      </c>
+      <c r="R62" s="39"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="109">
+      <c r="B63" s="106">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -5846,16 +6051,16 @@
         <v>269</v>
       </c>
       <c r="D63" s="78" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E63" s="79" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F63" s="78" t="s">
         <v>135</v>
       </c>
       <c r="G63" s="79" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="H63" s="96" t="s">
         <v>184</v>
@@ -5864,17 +6069,17 @@
         <v>259</v>
       </c>
       <c r="J63" s="78" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="K63" s="79" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="L63" s="78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" s="72">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N63" s="72">
         <v>100</v>
@@ -5883,17 +6088,17 @@
         <v>286</v>
       </c>
       <c r="P63" s="72">
-        <v>2.0999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q63" s="72">
-        <f t="shared" ref="Q63" si="48">N63*P63</f>
-        <v>0.21</v>
+        <f t="shared" ref="Q63" si="43">N63*P63</f>
+        <v>0.1</v>
       </c>
       <c r="R63" s="72"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="109">
+      <c r="B64" s="106">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
@@ -5901,16 +6106,16 @@
         <v>269</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F64" s="37" t="s">
         <v>135</v>
       </c>
       <c r="G64" s="38" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="H64" s="99" t="s">
         <v>184</v>
@@ -5919,10 +6124,10 @@
         <v>259</v>
       </c>
       <c r="J64" s="37" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="L64" s="37">
         <v>1</v>
@@ -5938,17 +6143,17 @@
         <v>286</v>
       </c>
       <c r="P64" s="39">
-        <v>1.6000000000000001E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q64" s="39">
-        <f t="shared" ref="Q64" si="49">P64*N64</f>
-        <v>0.16</v>
+        <f t="shared" ref="Q64" si="44">P64*N64</f>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R64" s="39"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="109">
+      <c r="B65" s="106">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
@@ -5956,28 +6161,28 @@
         <v>269</v>
       </c>
       <c r="D65" s="78" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E65" s="79" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F65" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="G65" s="85" t="s">
-        <v>173</v>
+      <c r="G65" s="79" t="s">
+        <v>163</v>
       </c>
       <c r="H65" s="96" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="I65" s="78" t="s">
-        <v>334</v>
+        <v>259</v>
       </c>
       <c r="J65" s="78" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="K65" s="79" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="L65" s="78">
         <v>1</v>
@@ -5987,23 +6192,23 @@
         <v>20</v>
       </c>
       <c r="N65" s="72">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O65" s="80" t="s">
         <v>286</v>
       </c>
       <c r="P65" s="72">
-        <v>6.8999999999999999E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q65" s="72">
-        <f t="shared" ref="Q65" si="50">N65*P65</f>
-        <v>0.34499999999999997</v>
+        <f t="shared" ref="Q65" si="45">N65*P65</f>
+        <v>0.16</v>
       </c>
       <c r="R65" s="72"/>
     </row>
-    <row r="66" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
-      <c r="B66" s="109">
+      <c r="B66" s="106">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -6011,16 +6216,16 @@
         <v>269</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>391</v>
+        <v>34</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F66" s="37" t="s">
         <v>135</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="H66" s="99" t="s">
         <v>184</v>
@@ -6029,10 +6234,10 @@
         <v>259</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="L66" s="37">
         <v>2</v>
@@ -6048,125 +6253,127 @@
         <v>286</v>
       </c>
       <c r="P66" s="39">
-        <v>1.1000000000000001E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q66" s="39">
-        <f t="shared" ref="Q66" si="51">P66*N66</f>
-        <v>0.11</v>
+        <f t="shared" ref="Q66" si="46">P66*N66</f>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R66" s="39"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
-      <c r="B67" s="109">
+      <c r="B67" s="106">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C67" s="55" t="s">
+      <c r="C67" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="D67" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="E67" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="F67" s="37" t="s">
+      <c r="D67" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="G67" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="H67" s="99" t="s">
+      <c r="G67" s="79" t="s">
+        <v>165</v>
+      </c>
+      <c r="H67" s="96" t="s">
         <v>184</v>
       </c>
-      <c r="I67" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J67" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="K67" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="L67" s="37">
-        <v>2</v>
-      </c>
-      <c r="M67" s="39">
+      <c r="I67" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J67" s="78" t="s">
+        <v>328</v>
+      </c>
+      <c r="K67" s="79" t="s">
+        <v>237</v>
+      </c>
+      <c r="L67" s="78">
+        <v>4</v>
+      </c>
+      <c r="M67" s="72">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="N67" s="39">
+        <v>80</v>
+      </c>
+      <c r="N67" s="72">
         <v>100</v>
       </c>
-      <c r="O67" s="57" t="s">
+      <c r="O67" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="P67" s="39">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q67" s="39">
-        <f t="shared" ref="Q67" si="52">P67*N67</f>
-        <v>0.15</v>
-      </c>
-      <c r="R67" s="39"/>
+      <c r="P67" s="72">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q67" s="72">
+        <f t="shared" ref="Q67" si="47">N67*P67</f>
+        <v>0.13</v>
+      </c>
+      <c r="R67" s="72"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="109">
+      <c r="B68" s="111">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="C68" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="D68" s="82" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="79" t="s">
-        <v>95</v>
+      <c r="D68" s="78" t="s">
+        <v>448</v>
+      </c>
+      <c r="E68" s="78" t="s">
+        <v>499</v>
       </c>
       <c r="F68" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G68" s="79" t="s">
-        <v>166</v>
-      </c>
-      <c r="H68" s="96" t="s">
+        <v>500</v>
+      </c>
+      <c r="G68" s="78" t="s">
+        <v>457</v>
+      </c>
+      <c r="H68" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="I68" s="78"/>
+      <c r="I68" s="78" t="s">
+        <v>259</v>
+      </c>
       <c r="J68" s="78" t="s">
-        <v>329</v>
-      </c>
-      <c r="K68" s="79" t="s">
-        <v>238</v>
+        <v>515</v>
+      </c>
+      <c r="K68" s="78" t="s">
+        <v>501</v>
       </c>
       <c r="L68" s="78">
         <v>1</v>
       </c>
       <c r="M68" s="72">
-        <f>L68*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N68" s="72">
+      <c r="N68" s="78">
         <v>100</v>
       </c>
-      <c r="O68" s="80" t="s">
+      <c r="O68" s="113" t="s">
         <v>286</v>
       </c>
-      <c r="P68" s="72">
-        <v>1.5E-3</v>
-      </c>
-      <c r="Q68" s="72">
-        <f>N68*P68</f>
-        <v>0.15</v>
-      </c>
-      <c r="R68" s="68"/>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P68" s="112">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q68" s="112">
+        <f t="shared" ref="Q68" si="48">P68*N68</f>
+        <v>0.09</v>
+      </c>
+      <c r="R68" s="78"/>
+    </row>
+    <row r="69" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
-      <c r="B69" s="109">
+      <c r="B69" s="106">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -6174,28 +6381,28 @@
         <v>269</v>
       </c>
       <c r="D69" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E69" s="38" t="s">
-        <v>105</v>
+        <v>394</v>
+      </c>
+      <c r="E69" s="78" t="s">
+        <v>395</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G69" s="38" t="s">
-        <v>176</v>
+        <v>136</v>
+      </c>
+      <c r="G69" s="37" t="s">
+        <v>396</v>
       </c>
       <c r="H69" s="99" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="I69" s="37" t="s">
         <v>259</v>
       </c>
       <c r="J69" s="37" t="s">
-        <v>338</v>
+        <v>397</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>248</v>
+        <v>398</v>
       </c>
       <c r="L69" s="37">
         <v>2</v>
@@ -6205,133 +6412,133 @@
         <v>40</v>
       </c>
       <c r="N69" s="39">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="O69" s="57" t="s">
         <v>286</v>
       </c>
       <c r="P69" s="39">
-        <v>1.5E-3</v>
+        <v>2.9100000000000001E-2</v>
       </c>
       <c r="Q69" s="39">
-        <f t="shared" ref="Q69" si="53">P69*N69</f>
-        <v>0.15</v>
+        <f t="shared" ref="Q69" si="49">P69*N69</f>
+        <v>1.3095000000000001</v>
       </c>
       <c r="R69" s="39"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="109">
+      <c r="B70" s="106">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="77" t="s">
+      <c r="C70" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="D70" s="78" t="s">
-        <v>45</v>
-      </c>
-      <c r="E70" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="F70" s="78" t="s">
+      <c r="D70" s="37" t="s">
+        <v>352</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="F70" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="G70" s="79" t="s">
-        <v>177</v>
-      </c>
-      <c r="H70" s="96" t="s">
+      <c r="G70" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="H70" s="99" t="s">
+        <v>203</v>
+      </c>
+      <c r="I70" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J70" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="K70" s="39" t="s">
+        <v>356</v>
+      </c>
+      <c r="L70" s="37">
+        <v>8</v>
+      </c>
+      <c r="M70" s="37">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="N70" s="72">
+        <v>100</v>
+      </c>
+      <c r="O70" s="70" t="s">
+        <v>286</v>
+      </c>
+      <c r="P70" s="37">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="Q70" s="37">
+        <f t="shared" ref="Q70" si="50">N70*P70</f>
+        <v>0.11</v>
+      </c>
+      <c r="R70" s="68"/>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="106">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D71" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E71" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F71" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G71" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="H71" s="99" t="s">
         <v>202</v>
       </c>
-      <c r="I70" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J70" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K70" s="79" t="s">
-        <v>249</v>
-      </c>
-      <c r="L70" s="78">
+      <c r="I71" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K71" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="L71" s="37">
         <v>1</v>
       </c>
-      <c r="M70" s="72">
+      <c r="M71" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N70" s="72">
-        <v>25</v>
-      </c>
-      <c r="O70" s="80" t="s">
-        <v>339</v>
-      </c>
-      <c r="P70" s="72">
-        <v>8.5400000000000004E-2</v>
-      </c>
-      <c r="Q70" s="72">
-        <f t="shared" ref="Q70" si="54">N70*P70</f>
-        <v>2.1350000000000002</v>
-      </c>
-      <c r="R70" s="72"/>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="109">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="C71" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E71" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="F71" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="G71" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="H71" s="99" t="s">
-        <v>203</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J71" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="K71" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="L71" s="37">
-        <v>1</v>
-      </c>
-      <c r="M71" s="39">
-        <f t="shared" ref="M71:M86" si="55">L71*20</f>
-        <v>20</v>
-      </c>
       <c r="N71" s="39">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="O71" s="57" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="P71" s="39">
-        <v>3.8E-3</v>
+        <v>1.8589999999999999E-2</v>
       </c>
       <c r="Q71" s="39">
-        <f t="shared" ref="Q71" si="56">P71*N71</f>
-        <v>0.19</v>
-      </c>
-      <c r="R71" s="68"/>
+        <f t="shared" ref="Q71" si="51">P71*N71</f>
+        <v>0.55769999999999997</v>
+      </c>
+      <c r="R71" s="39"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="B72" s="109">
+      <c r="B72" s="106">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
@@ -6339,16 +6546,16 @@
         <v>269</v>
       </c>
       <c r="D72" s="78" t="s">
-        <v>382</v>
+        <v>37</v>
       </c>
       <c r="E72" s="79" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F72" s="78" t="s">
         <v>135</v>
       </c>
       <c r="G72" s="79" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="H72" s="96" t="s">
         <v>184</v>
@@ -6357,36 +6564,36 @@
         <v>259</v>
       </c>
       <c r="J72" s="78" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="K72" s="79" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="L72" s="78">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M72" s="72">
-        <f>L72*20</f>
-        <v>120</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="N72" s="72">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O72" s="80" t="s">
         <v>286</v>
       </c>
       <c r="P72" s="72">
-        <v>1.1999999999999999E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q72" s="72">
-        <f t="shared" ref="Q72" si="57">N72*P72</f>
-        <v>0.24</v>
-      </c>
-      <c r="R72" s="68"/>
-    </row>
-    <row r="73" spans="1:18" ht="36" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q72" si="52">N72*P72</f>
+        <v>0.13999999999999999</v>
+      </c>
+      <c r="R72" s="72"/>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
-      <c r="B73" s="109">
+      <c r="B73" s="106">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
@@ -6394,54 +6601,54 @@
         <v>269</v>
       </c>
       <c r="D73" s="37" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F73" s="37" t="s">
         <v>135</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>274</v>
+        <v>169</v>
       </c>
       <c r="H73" s="99" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I73" s="37" t="s">
         <v>259</v>
       </c>
       <c r="J73" s="37" t="s">
-        <v>340</v>
+        <v>259</v>
       </c>
       <c r="K73" s="38" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="L73" s="37">
         <v>1</v>
       </c>
       <c r="M73" s="39">
-        <f t="shared" si="55"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N73" s="39">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O73" s="57" t="s">
-        <v>286</v>
+        <v>320</v>
       </c>
       <c r="P73" s="39">
-        <v>1E-3</v>
+        <v>4.6699999999999997E-3</v>
       </c>
       <c r="Q73" s="39">
-        <f t="shared" ref="Q73" si="58">P73*N73</f>
-        <v>0.1</v>
+        <f t="shared" ref="Q73" si="53">P73*N73</f>
+        <v>0.23349999999999999</v>
       </c>
       <c r="R73" s="39"/>
     </row>
-    <row r="74" spans="1:18" ht="36" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="109">
+      <c r="B74" s="106">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
@@ -6449,775 +6656,1431 @@
         <v>269</v>
       </c>
       <c r="D74" s="78" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E74" s="79" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F74" s="78" t="s">
         <v>135</v>
       </c>
       <c r="G74" s="79" t="s">
-        <v>275</v>
+        <v>170</v>
       </c>
       <c r="H74" s="96" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="I74" s="78" t="s">
         <v>259</v>
       </c>
       <c r="J74" s="78" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="K74" s="79" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="L74" s="78">
         <v>1</v>
       </c>
       <c r="M74" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N74" s="72">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O74" s="80" t="s">
         <v>286</v>
       </c>
       <c r="P74" s="72">
-        <v>4.3E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q74" s="72">
-        <f t="shared" ref="Q74" si="59">N74*P74</f>
-        <v>0.215</v>
+        <f t="shared" ref="Q74" si="54">N74*P74</f>
+        <v>0.12</v>
       </c>
       <c r="R74" s="72"/>
     </row>
-    <row r="75" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="109">
-        <f t="shared" ref="B75:B86" si="60">ROW(B75) - ROW($B$9)</f>
+      <c r="B75" s="106">
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="C75" s="77" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D75" s="78" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E75" s="79" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F75" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G75" s="78" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="G75" s="79" t="s">
+        <v>171</v>
       </c>
       <c r="H75" s="96" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="I75" s="78" t="s">
         <v>259</v>
       </c>
       <c r="J75" s="78" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="K75" s="79" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="L75" s="78">
         <v>1</v>
       </c>
       <c r="M75" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N75" s="72">
-        <f t="shared" ref="N75" si="61">M75+(M75*0.1)</f>
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="O75" s="80" t="s">
-        <v>400</v>
+        <v>286</v>
       </c>
       <c r="P75" s="72">
-        <v>1.42</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q75" s="72">
-        <v>1.42</v>
+        <f t="shared" ref="Q75" si="55">N75*P75</f>
+        <v>0.21</v>
       </c>
       <c r="R75" s="72"/>
     </row>
-    <row r="76" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="109">
-        <f t="shared" si="60"/>
+      <c r="B76" s="106">
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="C76" s="55" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G76" s="38">
-        <v>750314597</v>
+        <v>135</v>
+      </c>
+      <c r="G76" s="38" t="s">
+        <v>172</v>
       </c>
       <c r="H76" s="99" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="I76" s="37" t="s">
         <v>259</v>
       </c>
       <c r="J76" s="37" t="s">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="L76" s="37">
         <v>1</v>
       </c>
       <c r="M76" s="39">
-        <f t="shared" si="55"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N76" s="39">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="O76" s="57" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="P76" s="39">
-        <v>3.81</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q76" s="39">
-        <f t="shared" ref="Q76" si="62">P76*N76</f>
-        <v>80.010000000000005</v>
+        <f t="shared" ref="Q76" si="56">P76*N76</f>
+        <v>0.16</v>
       </c>
       <c r="R76" s="39"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="109">
-        <f t="shared" si="60"/>
+      <c r="B77" s="106">
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C77" s="77" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D77" s="78" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E77" s="79" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F77" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G77" s="79" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="G77" s="85" t="s">
+        <v>173</v>
       </c>
       <c r="H77" s="96" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="I77" s="78" t="s">
-        <v>259</v>
+        <v>334</v>
       </c>
       <c r="J77" s="78" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="K77" s="79" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="L77" s="78">
         <v>1</v>
       </c>
       <c r="M77" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N77" s="72">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="O77" s="80" t="s">
-        <v>343</v>
+        <v>286</v>
       </c>
       <c r="P77" s="72">
-        <v>2.48</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q77" s="72">
-        <f t="shared" ref="Q77" si="63">N77*P77</f>
-        <v>52.08</v>
+        <f t="shared" ref="Q77" si="57">N77*P77</f>
+        <v>0.34499999999999997</v>
       </c>
       <c r="R77" s="72"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="109">
-        <f t="shared" si="60"/>
+      <c r="B78" s="106">
+        <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C78" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="D78" s="82" t="s">
-        <v>52</v>
-      </c>
-      <c r="E78" s="78" t="s">
-        <v>427</v>
-      </c>
-      <c r="F78" s="78" t="s">
-        <v>428</v>
-      </c>
-      <c r="G78" s="78" t="s">
-        <v>344</v>
-      </c>
-      <c r="H78" s="96" t="s">
-        <v>207</v>
+        <v>269</v>
+      </c>
+      <c r="D78" s="37" t="s">
+        <v>383</v>
+      </c>
+      <c r="E78" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="F78" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G78" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H78" s="99" t="s">
+        <v>184</v>
       </c>
       <c r="I78" s="37" t="s">
         <v>259</v>
       </c>
       <c r="J78" s="37" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="L78" s="37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" s="39">
-        <f t="shared" si="55"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="N78" s="39">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="O78" s="57" t="s">
         <v>286</v>
       </c>
       <c r="P78" s="39">
-        <v>0.34410000000000002</v>
+        <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q78" s="39">
-        <f t="shared" ref="Q78" si="64">P78*N78</f>
-        <v>8.6025000000000009</v>
-      </c>
-      <c r="R78" s="69"/>
-    </row>
-    <row r="79" spans="1:18" ht="36" x14ac:dyDescent="0.25">
+        <f t="shared" ref="Q78" si="58">P78*N78</f>
+        <v>0.11</v>
+      </c>
+      <c r="R78" s="39"/>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="109">
-        <f t="shared" si="60"/>
+      <c r="B79" s="106">
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="D79" s="71" t="s">
-        <v>53</v>
-      </c>
-      <c r="E79" s="37" t="s">
-        <v>429</v>
+      <c r="C79" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" s="38" t="s">
+        <v>104</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>430</v>
-      </c>
-      <c r="G79" s="37" t="s">
-        <v>346</v>
+        <v>135</v>
+      </c>
+      <c r="G79" s="38" t="s">
+        <v>175</v>
       </c>
       <c r="H79" s="99" t="s">
-        <v>431</v>
-      </c>
-      <c r="I79" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J79" s="78" t="s">
-        <v>347</v>
-      </c>
-      <c r="K79" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L79" s="78">
-        <v>1</v>
-      </c>
-      <c r="M79" s="72">
-        <f t="shared" si="55"/>
-        <v>20</v>
-      </c>
-      <c r="N79" s="72">
-        <v>21</v>
-      </c>
-      <c r="O79" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="I79" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J79" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="K79" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="L79" s="37">
+        <v>2</v>
+      </c>
+      <c r="M79" s="39">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N79" s="39">
+        <v>100</v>
+      </c>
+      <c r="O79" s="57" t="s">
         <v>286</v>
       </c>
-      <c r="P79" s="72">
-        <v>0.30709999999999998</v>
-      </c>
-      <c r="Q79" s="72">
-        <f t="shared" ref="Q79" si="65">N79*P79</f>
-        <v>6.4490999999999996</v>
-      </c>
-      <c r="R79" s="69"/>
+      <c r="P79" s="39">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q79" s="39">
+        <f t="shared" ref="Q79" si="59">P79*N79</f>
+        <v>0.15</v>
+      </c>
+      <c r="R79" s="39"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="109">
-        <f t="shared" si="60"/>
+      <c r="B80" s="106">
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C80" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="D80" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E80" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="F80" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="G80" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="H80" s="99" t="s">
-        <v>207</v>
-      </c>
-      <c r="I80" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J80" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K80" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L80" s="37">
+      <c r="C80" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D80" s="82" t="s">
+        <v>353</v>
+      </c>
+      <c r="E80" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="F80" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G80" s="79" t="s">
+        <v>166</v>
+      </c>
+      <c r="H80" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="I80" s="78"/>
+      <c r="J80" s="78" t="s">
+        <v>329</v>
+      </c>
+      <c r="K80" s="79" t="s">
+        <v>238</v>
+      </c>
+      <c r="L80" s="78">
         <v>1</v>
       </c>
-      <c r="M80" s="39">
-        <f t="shared" si="55"/>
+      <c r="M80" s="72">
+        <f>L80*20</f>
         <v>20</v>
       </c>
-      <c r="N80" s="39">
-        <v>21</v>
-      </c>
-      <c r="O80" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="P80" s="39">
-        <v>3.637</v>
-      </c>
-      <c r="Q80" s="39">
-        <f t="shared" ref="Q80" si="66">P80*N80</f>
-        <v>76.376999999999995</v>
-      </c>
-      <c r="R80" s="39"/>
-    </row>
-    <row r="81" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="N80" s="72">
+        <v>100</v>
+      </c>
+      <c r="O80" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P80" s="72">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q80" s="72">
+        <f>N80*P80</f>
+        <v>0.15</v>
+      </c>
+      <c r="R80" s="68"/>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="109">
-        <f t="shared" si="60"/>
+      <c r="B81" s="106">
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="C81" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="D81" s="78" t="s">
-        <v>55</v>
-      </c>
-      <c r="E81" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="F81" s="78" t="s">
-        <v>140</v>
-      </c>
-      <c r="G81" s="79" t="s">
-        <v>179</v>
-      </c>
-      <c r="H81" s="96" t="s">
-        <v>207</v>
-      </c>
-      <c r="I81" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J81" s="78" t="s">
-        <v>348</v>
-      </c>
-      <c r="K81" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L81" s="78">
+      <c r="C81" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D81" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E81" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F81" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G81" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="H81" s="99" t="s">
+        <v>184</v>
+      </c>
+      <c r="I81" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J81" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="K81" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="L81" s="37">
+        <v>2</v>
+      </c>
+      <c r="M81" s="39">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N81" s="39">
+        <v>100</v>
+      </c>
+      <c r="O81" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P81" s="39">
+        <v>1.5E-3</v>
+      </c>
+      <c r="Q81" s="39">
+        <f t="shared" ref="Q81" si="60">P81*N81</f>
+        <v>0.15</v>
+      </c>
+      <c r="R81" s="39"/>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="106">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="C82" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D82" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="E82" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="F82" s="78" t="s">
+        <v>135</v>
+      </c>
+      <c r="G82" s="79" t="s">
+        <v>177</v>
+      </c>
+      <c r="H82" s="96" t="s">
+        <v>202</v>
+      </c>
+      <c r="I82" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J82" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K82" s="79" t="s">
+        <v>249</v>
+      </c>
+      <c r="L82" s="78">
         <v>1</v>
       </c>
-      <c r="M81" s="72">
-        <f t="shared" si="55"/>
+      <c r="M82" s="72">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N81" s="72">
+      <c r="N82" s="72">
         <v>25</v>
       </c>
-      <c r="O81" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P81" s="72">
-        <v>0.3463</v>
-      </c>
-      <c r="Q81" s="72">
-        <f t="shared" ref="Q81" si="67">N81*P81</f>
-        <v>8.6575000000000006</v>
-      </c>
-      <c r="R81" s="72"/>
-    </row>
-    <row r="82" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="109">
-        <f t="shared" si="60"/>
-        <v>73</v>
-      </c>
-      <c r="C82" s="63" t="s">
-        <v>273</v>
-      </c>
-      <c r="D82" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="E82" s="65" t="s">
-        <v>115</v>
-      </c>
-      <c r="F82" s="64" t="s">
-        <v>141</v>
-      </c>
-      <c r="G82" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="H82" s="104" t="s">
-        <v>208</v>
-      </c>
-      <c r="I82" s="64" t="s">
-        <v>259</v>
-      </c>
-      <c r="J82" s="64" t="s">
-        <v>349</v>
-      </c>
-      <c r="K82" s="65" t="s">
-        <v>259</v>
-      </c>
-      <c r="L82" s="64">
-        <v>1</v>
-      </c>
-      <c r="M82" s="66">
-        <f t="shared" si="55"/>
-        <v>20</v>
-      </c>
-      <c r="N82" s="66">
-        <v>21</v>
-      </c>
-      <c r="O82" s="67" t="s">
-        <v>286</v>
-      </c>
-      <c r="P82" s="66">
-        <v>7.4638</v>
-      </c>
-      <c r="Q82" s="66">
-        <f t="shared" ref="Q82" si="68">P82*N82</f>
-        <v>156.7398</v>
-      </c>
-      <c r="R82" s="66" t="s">
-        <v>372</v>
-      </c>
+      <c r="O82" s="80" t="s">
+        <v>339</v>
+      </c>
+      <c r="P82" s="72">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="Q82" s="72">
+        <f t="shared" ref="Q82" si="61">N82*P82</f>
+        <v>2.1350000000000002</v>
+      </c>
+      <c r="R82" s="72"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="B83" s="109">
-        <f t="shared" si="60"/>
+      <c r="B83" s="106">
+        <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="C83" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="D83" s="78" t="s">
-        <v>57</v>
-      </c>
-      <c r="E83" s="79" t="s">
-        <v>116</v>
-      </c>
-      <c r="F83" s="78" t="s">
-        <v>142</v>
-      </c>
-      <c r="G83" s="79" t="s">
-        <v>181</v>
-      </c>
-      <c r="H83" s="96" t="s">
-        <v>209</v>
-      </c>
-      <c r="I83" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J83" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K83" s="83" t="s">
-        <v>259</v>
-      </c>
-      <c r="L83" s="78">
+      <c r="C83" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E83" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="F83" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="G83" s="38" t="s">
+        <v>376</v>
+      </c>
+      <c r="H83" s="99" t="s">
+        <v>203</v>
+      </c>
+      <c r="I83" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J83" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="K83" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="L83" s="37">
         <v>1</v>
       </c>
-      <c r="M83" s="72">
-        <f t="shared" si="55"/>
+      <c r="M83" s="39">
+        <f t="shared" ref="M83:M98" si="62">L83*20</f>
         <v>20</v>
       </c>
-      <c r="N83" s="72">
-        <v>21</v>
-      </c>
-      <c r="O83" s="80" t="s">
-        <v>343</v>
-      </c>
-      <c r="P83" s="72">
-        <v>2.6459999999999999</v>
-      </c>
-      <c r="Q83" s="72">
-        <f t="shared" ref="Q83" si="69">N83*P83</f>
-        <v>55.565999999999995</v>
-      </c>
-      <c r="R83" s="72"/>
+      <c r="N83" s="39">
+        <v>50</v>
+      </c>
+      <c r="O83" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P83" s="39">
+        <v>3.8E-3</v>
+      </c>
+      <c r="Q83" s="39">
+        <f t="shared" ref="Q83" si="63">P83*N83</f>
+        <v>0.19</v>
+      </c>
+      <c r="R83" s="68"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="B84" s="109">
-        <f t="shared" si="60"/>
+      <c r="B84" s="106">
+        <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C84" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="D84" s="82" t="s">
-        <v>383</v>
-      </c>
-      <c r="E84" s="78" t="s">
-        <v>432</v>
+      <c r="C84" s="77" t="s">
+        <v>269</v>
+      </c>
+      <c r="D84" s="78" t="s">
+        <v>377</v>
+      </c>
+      <c r="E84" s="79" t="s">
+        <v>109</v>
       </c>
       <c r="F84" s="78" t="s">
-        <v>140</v>
-      </c>
-      <c r="G84" s="78" t="s">
-        <v>350</v>
+        <v>135</v>
+      </c>
+      <c r="G84" s="79" t="s">
+        <v>178</v>
       </c>
       <c r="H84" s="96" t="s">
-        <v>207</v>
-      </c>
-      <c r="I84" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J84" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="K84" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L84" s="71">
-        <v>2</v>
-      </c>
-      <c r="M84" s="39">
-        <f t="shared" si="55"/>
-        <v>40</v>
-      </c>
-      <c r="N84" s="39">
-        <v>41</v>
-      </c>
-      <c r="O84" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="I84" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J84" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="K84" s="79" t="s">
+        <v>252</v>
+      </c>
+      <c r="L84" s="78">
+        <v>6</v>
+      </c>
+      <c r="M84" s="72">
+        <f>L84*20</f>
+        <v>120</v>
+      </c>
+      <c r="N84" s="72">
+        <v>200</v>
+      </c>
+      <c r="O84" s="80" t="s">
         <v>286</v>
       </c>
-      <c r="P84" s="39">
-        <v>1.1423000000000001</v>
-      </c>
-      <c r="Q84" s="39">
-        <f t="shared" ref="Q84" si="70">P84*N84</f>
-        <v>46.834300000000006</v>
-      </c>
-      <c r="R84" s="69"/>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P84" s="72">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q84" s="72">
+        <f t="shared" ref="Q84" si="64">N84*P84</f>
+        <v>0.24</v>
+      </c>
+      <c r="R84" s="68"/>
+    </row>
+    <row r="85" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
-      <c r="B85" s="109">
-        <f t="shared" si="60"/>
+      <c r="B85" s="106">
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E85" s="38" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="G85" s="38" t="s">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="H85" s="99" t="s">
-        <v>207</v>
-      </c>
-      <c r="I85" s="97" t="s">
-        <v>259</v>
-      </c>
-      <c r="J85" s="97" t="s">
-        <v>354</v>
+        <v>203</v>
+      </c>
+      <c r="I85" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J85" s="37" t="s">
+        <v>340</v>
       </c>
       <c r="K85" s="38" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="L85" s="37">
         <v>1</v>
       </c>
       <c r="M85" s="39">
-        <f>L85*20</f>
+        <f t="shared" si="62"/>
         <v>20</v>
       </c>
       <c r="N85" s="39">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="O85" s="57" t="s">
         <v>286</v>
       </c>
       <c r="P85" s="39">
-        <v>0.39140000000000003</v>
+        <v>1E-3</v>
       </c>
       <c r="Q85" s="39">
-        <f t="shared" ref="Q85" si="71">P85*N85</f>
-        <v>8.2194000000000003</v>
+        <f t="shared" ref="Q85" si="65">P85*N85</f>
+        <v>0.1</v>
       </c>
       <c r="R85" s="39"/>
     </row>
-    <row r="86" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
-      <c r="B86" s="109">
-        <f t="shared" si="60"/>
+      <c r="B86" s="106">
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="C86" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="D86" s="82" t="s">
-        <v>384</v>
-      </c>
-      <c r="E86" s="78" t="s">
-        <v>433</v>
+        <v>269</v>
+      </c>
+      <c r="D86" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="E86" s="79" t="s">
+        <v>108</v>
       </c>
       <c r="F86" s="78" t="s">
-        <v>257</v>
-      </c>
-      <c r="G86" s="78" t="s">
-        <v>352</v>
+        <v>135</v>
+      </c>
+      <c r="G86" s="79" t="s">
+        <v>275</v>
       </c>
       <c r="H86" s="96" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I86" s="78" t="s">
         <v>259</v>
       </c>
       <c r="J86" s="78" t="s">
-        <v>259</v>
+        <v>341</v>
       </c>
       <c r="K86" s="79" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="L86" s="78">
         <v>1</v>
       </c>
       <c r="M86" s="72">
-        <f t="shared" si="55"/>
+        <f t="shared" si="62"/>
         <v>20</v>
       </c>
       <c r="N86" s="72">
+        <v>50</v>
+      </c>
+      <c r="O86" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P86" s="72">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q86" s="72">
+        <f t="shared" ref="Q86" si="66">N86*P86</f>
+        <v>0.215</v>
+      </c>
+      <c r="R86" s="72"/>
+    </row>
+    <row r="87" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A87" s="1"/>
+      <c r="B87" s="106">
+        <f t="shared" ref="B87:B98" si="67">ROW(B87) - ROW($B$9)</f>
+        <v>78</v>
+      </c>
+      <c r="C87" s="77" t="s">
+        <v>271</v>
+      </c>
+      <c r="D87" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="E87" s="79" t="s">
+        <v>110</v>
+      </c>
+      <c r="F87" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G87" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="H87" s="96" t="s">
+        <v>205</v>
+      </c>
+      <c r="I87" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J87" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K87" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L87" s="78">
+        <v>1</v>
+      </c>
+      <c r="M87" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N87" s="72">
+        <f t="shared" ref="N87" si="68">M87+(M87*0.1)</f>
+        <v>22</v>
+      </c>
+      <c r="O87" s="80" t="s">
+        <v>392</v>
+      </c>
+      <c r="P87" s="72">
+        <v>1.42</v>
+      </c>
+      <c r="Q87" s="72">
+        <v>1.42</v>
+      </c>
+      <c r="R87" s="72"/>
+    </row>
+    <row r="88" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="B88" s="106">
+        <f t="shared" si="67"/>
+        <v>79</v>
+      </c>
+      <c r="C88" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="D88" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="E88" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="F88" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="G88" s="38">
+        <v>750314597</v>
+      </c>
+      <c r="H88" s="99" t="s">
+        <v>206</v>
+      </c>
+      <c r="I88" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J88" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K88" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L88" s="37">
+        <v>1</v>
+      </c>
+      <c r="M88" s="39">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N88" s="39">
         <v>21</v>
       </c>
-      <c r="O86" s="80" t="s">
-        <v>353</v>
-      </c>
-      <c r="P86" s="72">
-        <v>3.532</v>
-      </c>
-      <c r="Q86" s="72">
-        <f t="shared" ref="Q86" si="72">N86*P86</f>
-        <v>74.171999999999997</v>
-      </c>
-      <c r="R86" s="69"/>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="32"/>
-      <c r="C87" s="48"/>
-      <c r="D87" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="E87" s="34"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="36"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
-      <c r="J87" s="35"/>
-      <c r="K87" s="36"/>
-      <c r="L87" s="36"/>
-      <c r="M87" s="36"/>
-      <c r="N87" s="36"/>
-      <c r="O87" s="61" t="s">
-        <v>355</v>
-      </c>
-      <c r="P87" s="59"/>
-      <c r="Q87" s="59">
-        <f>SUM(Q10:Q86)</f>
-        <v>978.1422</v>
-      </c>
-      <c r="R87" s="41"/>
-    </row>
-    <row r="88" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="24"/>
-      <c r="C88" s="49"/>
-      <c r="D88" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-      <c r="H88" s="9"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="9"/>
-      <c r="K88" s="9"/>
-      <c r="L88" s="9"/>
-      <c r="M88" s="9"/>
-      <c r="N88" s="9"/>
-      <c r="O88" s="62" t="s">
-        <v>356</v>
-      </c>
-      <c r="P88" s="60"/>
-      <c r="Q88" s="105">
-        <f>Q87/20</f>
-        <v>48.907110000000003</v>
-      </c>
-      <c r="R88" s="42"/>
+      <c r="O88" s="57" t="s">
+        <v>317</v>
+      </c>
+      <c r="P88" s="39">
+        <v>3.81</v>
+      </c>
+      <c r="Q88" s="39">
+        <f t="shared" ref="Q88" si="69">P88*N88</f>
+        <v>80.010000000000005</v>
+      </c>
+      <c r="R88" s="39"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
+      <c r="B89" s="106">
+        <f t="shared" si="67"/>
+        <v>80</v>
+      </c>
+      <c r="C89" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D89" s="78" t="s">
+        <v>51</v>
+      </c>
+      <c r="E89" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="F89" s="78" t="s">
+        <v>254</v>
+      </c>
+      <c r="G89" s="79" t="s">
+        <v>138</v>
+      </c>
+      <c r="H89" s="96" t="s">
+        <v>207</v>
+      </c>
+      <c r="I89" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J89" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K89" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L89" s="78">
+        <v>1</v>
+      </c>
+      <c r="M89" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N89" s="72">
+        <v>21</v>
+      </c>
+      <c r="O89" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="P89" s="72">
+        <v>2.48</v>
+      </c>
+      <c r="Q89" s="72">
+        <f t="shared" ref="Q89" si="70">N89*P89</f>
+        <v>52.08</v>
+      </c>
+      <c r="R89" s="72"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B90" s="106">
+        <f t="shared" si="67"/>
+        <v>81</v>
+      </c>
+      <c r="C90" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D90" s="82" t="s">
+        <v>52</v>
+      </c>
+      <c r="E90" s="78" t="s">
+        <v>502</v>
+      </c>
+      <c r="F90" s="78" t="s">
+        <v>503</v>
+      </c>
+      <c r="G90" s="78" t="s">
+        <v>458</v>
+      </c>
+      <c r="H90" s="96" t="s">
+        <v>504</v>
+      </c>
+      <c r="I90" s="37"/>
+      <c r="J90" s="37" t="s">
+        <v>505</v>
+      </c>
+      <c r="K90" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L90" s="37">
+        <v>1</v>
+      </c>
+      <c r="M90" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N90" s="39">
+        <v>21</v>
+      </c>
+      <c r="O90" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P90" s="39">
+        <v>0.28160000000000002</v>
+      </c>
+      <c r="Q90" s="39">
+        <f t="shared" ref="Q90" si="71">P90*N90</f>
+        <v>5.9136000000000006</v>
+      </c>
+      <c r="R90" s="69"/>
+    </row>
+    <row r="91" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
+      <c r="B91" s="106">
+        <f t="shared" si="67"/>
+        <v>82</v>
+      </c>
+      <c r="C91" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D91" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="F91" s="37" t="s">
+        <v>419</v>
+      </c>
+      <c r="G91" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="H91" s="99" t="s">
+        <v>420</v>
+      </c>
+      <c r="I91" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J91" s="78" t="s">
+        <v>345</v>
+      </c>
+      <c r="K91" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L91" s="78">
+        <v>1</v>
+      </c>
+      <c r="M91" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N91" s="72">
+        <v>21</v>
+      </c>
+      <c r="O91" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P91" s="72">
+        <v>0.30709999999999998</v>
+      </c>
+      <c r="Q91" s="72">
+        <f t="shared" ref="Q91" si="72">N91*P91</f>
+        <v>6.4490999999999996</v>
+      </c>
+      <c r="R91" s="69"/>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="B92" s="106">
+        <f t="shared" si="67"/>
+        <v>83</v>
+      </c>
+      <c r="C92" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E92" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F92" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="G92" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="H92" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="I92" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J92" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="K92" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L92" s="37">
+        <v>1</v>
+      </c>
+      <c r="M92" s="39">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N92" s="39">
+        <v>21</v>
+      </c>
+      <c r="O92" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="P92" s="39">
+        <v>3.637</v>
+      </c>
+      <c r="Q92" s="39">
+        <f t="shared" ref="Q92" si="73">P92*N92</f>
+        <v>76.376999999999995</v>
+      </c>
+      <c r="R92" s="39"/>
+    </row>
+    <row r="93" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+      <c r="B93" s="106">
+        <f t="shared" si="67"/>
+        <v>84</v>
+      </c>
+      <c r="C93" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D93" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="E93" s="79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="G93" s="79" t="s">
+        <v>179</v>
+      </c>
+      <c r="H93" s="96" t="s">
+        <v>207</v>
+      </c>
+      <c r="I93" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J93" s="78" t="s">
+        <v>346</v>
+      </c>
+      <c r="K93" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="L93" s="78">
+        <v>1</v>
+      </c>
+      <c r="M93" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N93" s="72">
+        <v>25</v>
+      </c>
+      <c r="O93" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="P93" s="72">
+        <v>0.3463</v>
+      </c>
+      <c r="Q93" s="72">
+        <f t="shared" ref="Q93" si="74">N93*P93</f>
+        <v>8.6575000000000006</v>
+      </c>
+      <c r="R93" s="72"/>
+    </row>
+    <row r="94" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+      <c r="B94" s="106">
+        <f t="shared" si="67"/>
+        <v>85</v>
+      </c>
+      <c r="C94" s="63" t="s">
+        <v>273</v>
+      </c>
+      <c r="D94" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E94" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="F94" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="G94" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="H94" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="I94" s="64" t="s">
+        <v>259</v>
+      </c>
+      <c r="J94" s="64" t="s">
+        <v>347</v>
+      </c>
+      <c r="K94" s="65" t="s">
+        <v>259</v>
+      </c>
+      <c r="L94" s="64">
+        <v>1</v>
+      </c>
+      <c r="M94" s="66">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N94" s="66">
+        <v>21</v>
+      </c>
+      <c r="O94" s="67" t="s">
+        <v>286</v>
+      </c>
+      <c r="P94" s="66">
+        <v>7.4638</v>
+      </c>
+      <c r="Q94" s="66">
+        <f t="shared" ref="Q94" si="75">P94*N94</f>
+        <v>156.7398</v>
+      </c>
+      <c r="R94" s="66" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="B95" s="106">
+        <f t="shared" si="67"/>
+        <v>86</v>
+      </c>
+      <c r="C95" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D95" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="E95" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="F95" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="G95" s="79" t="s">
+        <v>181</v>
+      </c>
+      <c r="H95" s="96" t="s">
+        <v>209</v>
+      </c>
+      <c r="I95" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J95" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="K95" s="83" t="s">
+        <v>259</v>
+      </c>
+      <c r="L95" s="78">
+        <v>1</v>
+      </c>
+      <c r="M95" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N95" s="72">
+        <v>21</v>
+      </c>
+      <c r="O95" s="80" t="s">
+        <v>343</v>
+      </c>
+      <c r="P95" s="72">
+        <v>2.6459999999999999</v>
+      </c>
+      <c r="Q95" s="72">
+        <f t="shared" ref="Q95" si="76">N95*P95</f>
+        <v>55.565999999999995</v>
+      </c>
+      <c r="R95" s="72"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="B96" s="106">
+        <f t="shared" si="67"/>
+        <v>87</v>
+      </c>
+      <c r="C96" s="77" t="s">
+        <v>273</v>
+      </c>
+      <c r="D96" s="78" t="s">
+        <v>449</v>
+      </c>
+      <c r="E96" s="78" t="s">
+        <v>506</v>
+      </c>
+      <c r="F96" s="78" t="s">
+        <v>507</v>
+      </c>
+      <c r="G96" s="78" t="s">
+        <v>509</v>
+      </c>
+      <c r="H96" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="I96" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="J96" s="78" t="s">
+        <v>508</v>
+      </c>
+      <c r="K96" s="78" t="s">
+        <v>259</v>
+      </c>
+      <c r="L96" s="78">
+        <v>1</v>
+      </c>
+      <c r="M96" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N96" s="78">
+        <v>21</v>
+      </c>
+      <c r="O96" s="113" t="s">
+        <v>286</v>
+      </c>
+      <c r="P96" s="112">
+        <v>5.4648000000000003</v>
+      </c>
+      <c r="Q96" s="112">
+        <f t="shared" ref="Q96" si="77">P96*N96</f>
+        <v>114.7608</v>
+      </c>
+      <c r="R96" s="78"/>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+      <c r="B97" s="106">
+        <f t="shared" si="67"/>
+        <v>88</v>
+      </c>
+      <c r="C97" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D97" s="37" t="s">
+        <v>450</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>510</v>
+      </c>
+      <c r="F97" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="G97" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="H97" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="I97" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="J97" s="37" t="s">
+        <v>511</v>
+      </c>
+      <c r="K97" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="L97" s="37">
+        <v>1</v>
+      </c>
+      <c r="M97" s="72">
+        <f t="shared" si="62"/>
+        <v>20</v>
+      </c>
+      <c r="N97" s="37">
+        <v>21</v>
+      </c>
+      <c r="O97" s="70" t="s">
+        <v>286</v>
+      </c>
+      <c r="P97" s="110">
+        <v>4.1475</v>
+      </c>
+      <c r="Q97" s="110">
+        <f>P97*N97</f>
+        <v>87.097499999999997</v>
+      </c>
+      <c r="R97" s="37"/>
+    </row>
+    <row r="98" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1"/>
+      <c r="B98" s="106">
+        <f t="shared" si="67"/>
+        <v>89</v>
+      </c>
+      <c r="C98" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="D98" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E98" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="F98" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="G98" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="H98" s="99" t="s">
+        <v>207</v>
+      </c>
+      <c r="I98" s="97" t="s">
+        <v>259</v>
+      </c>
+      <c r="J98" s="97" t="s">
+        <v>349</v>
+      </c>
+      <c r="K98" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="L98" s="37">
+        <v>1</v>
+      </c>
+      <c r="M98" s="39">
+        <f>L98*20</f>
+        <v>20</v>
+      </c>
+      <c r="N98" s="39">
+        <v>21</v>
+      </c>
+      <c r="O98" s="57" t="s">
+        <v>286</v>
+      </c>
+      <c r="P98" s="39">
+        <v>0.39140000000000003</v>
+      </c>
+      <c r="Q98" s="39">
+        <f t="shared" ref="Q98" si="78">P98*N98</f>
+        <v>8.2194000000000003</v>
+      </c>
+      <c r="R98" s="39"/>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+      <c r="B99" s="32"/>
+      <c r="C99" s="48"/>
+      <c r="D99" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E99" s="34"/>
+      <c r="F99" s="35"/>
+      <c r="G99" s="36"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="35"/>
+      <c r="J99" s="35"/>
+      <c r="K99" s="36"/>
+      <c r="L99" s="36"/>
+      <c r="M99" s="36"/>
+      <c r="N99" s="36"/>
+      <c r="O99" s="61" t="s">
+        <v>350</v>
+      </c>
+      <c r="P99" s="59"/>
+      <c r="Q99" s="59">
+        <f>SUM(Q10:Q98)</f>
+        <v>1102.7587000000001</v>
+      </c>
+      <c r="R99" s="41"/>
+    </row>
+    <row r="100" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1"/>
+      <c r="B100" s="24"/>
+      <c r="C100" s="49"/>
+      <c r="D100" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
+      <c r="L100" s="9"/>
+      <c r="M100" s="9"/>
+      <c r="N100" s="9"/>
+      <c r="O100" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="P100" s="60"/>
+      <c r="Q100" s="105">
+        <f>Q99/20</f>
+        <v>55.137935000000006</v>
+      </c>
+      <c r="R100" s="42"/>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A102" s="1"/>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7240,68 +8103,80 @@
     <hyperlink ref="O24" r:id="rId13"/>
     <hyperlink ref="O25" r:id="rId14"/>
     <hyperlink ref="O21" r:id="rId15"/>
-    <hyperlink ref="O26" r:id="rId16"/>
-    <hyperlink ref="O27" r:id="rId17"/>
-    <hyperlink ref="O28" r:id="rId18"/>
-    <hyperlink ref="O29" r:id="rId19"/>
-    <hyperlink ref="O30" r:id="rId20"/>
-    <hyperlink ref="O31" r:id="rId21"/>
-    <hyperlink ref="O32" r:id="rId22"/>
-    <hyperlink ref="O33" r:id="rId23"/>
-    <hyperlink ref="O36" r:id="rId24"/>
-    <hyperlink ref="O37" r:id="rId25"/>
-    <hyperlink ref="O38" r:id="rId26"/>
-    <hyperlink ref="O40" r:id="rId27"/>
-    <hyperlink ref="O41" r:id="rId28"/>
-    <hyperlink ref="O45" r:id="rId29"/>
-    <hyperlink ref="O46" r:id="rId30"/>
-    <hyperlink ref="O47" r:id="rId31"/>
-    <hyperlink ref="O51" r:id="rId32"/>
-    <hyperlink ref="O52" r:id="rId33"/>
-    <hyperlink ref="O53" r:id="rId34"/>
-    <hyperlink ref="O54" r:id="rId35"/>
-    <hyperlink ref="O55" r:id="rId36"/>
-    <hyperlink ref="O56" r:id="rId37"/>
-    <hyperlink ref="O68" r:id="rId38"/>
-    <hyperlink ref="O59" r:id="rId39"/>
-    <hyperlink ref="O60" r:id="rId40"/>
-    <hyperlink ref="O61" r:id="rId41"/>
-    <hyperlink ref="O62" r:id="rId42"/>
-    <hyperlink ref="O63" r:id="rId43"/>
-    <hyperlink ref="O64" r:id="rId44"/>
-    <hyperlink ref="O65" r:id="rId45"/>
-    <hyperlink ref="O66" r:id="rId46"/>
-    <hyperlink ref="O67" r:id="rId47"/>
-    <hyperlink ref="O69" r:id="rId48"/>
-    <hyperlink ref="O70" r:id="rId49"/>
-    <hyperlink ref="O71" r:id="rId50"/>
-    <hyperlink ref="O74" r:id="rId51"/>
-    <hyperlink ref="O72" r:id="rId52"/>
-    <hyperlink ref="O76" r:id="rId53"/>
-    <hyperlink ref="O77" r:id="rId54"/>
-    <hyperlink ref="O78" r:id="rId55"/>
-    <hyperlink ref="O79" r:id="rId56"/>
-    <hyperlink ref="O80" r:id="rId57"/>
-    <hyperlink ref="O81" r:id="rId58"/>
-    <hyperlink ref="O82" r:id="rId59"/>
-    <hyperlink ref="O83" r:id="rId60"/>
-    <hyperlink ref="O84" r:id="rId61"/>
-    <hyperlink ref="O86" r:id="rId62"/>
-    <hyperlink ref="O85" r:id="rId63"/>
-    <hyperlink ref="O58" r:id="rId64"/>
-    <hyperlink ref="O10" r:id="rId65"/>
-    <hyperlink ref="O75" r:id="rId66"/>
-    <hyperlink ref="O57" r:id="rId67"/>
-    <hyperlink ref="O34" r:id="rId68"/>
-    <hyperlink ref="O35" r:id="rId69"/>
-    <hyperlink ref="O39" r:id="rId70"/>
-    <hyperlink ref="O42" r:id="rId71"/>
-    <hyperlink ref="O44" r:id="rId72"/>
-    <hyperlink ref="O49" r:id="rId73"/>
-    <hyperlink ref="O43" r:id="rId74"/>
+    <hyperlink ref="O29" r:id="rId16"/>
+    <hyperlink ref="O30" r:id="rId17"/>
+    <hyperlink ref="O32" r:id="rId18"/>
+    <hyperlink ref="O33" r:id="rId19"/>
+    <hyperlink ref="O34" r:id="rId20"/>
+    <hyperlink ref="O35" r:id="rId21"/>
+    <hyperlink ref="O36" r:id="rId22"/>
+    <hyperlink ref="O37" r:id="rId23"/>
+    <hyperlink ref="O46" r:id="rId24"/>
+    <hyperlink ref="O47" r:id="rId25"/>
+    <hyperlink ref="O48" r:id="rId26"/>
+    <hyperlink ref="O50" r:id="rId27"/>
+    <hyperlink ref="O51" r:id="rId28"/>
+    <hyperlink ref="O55" r:id="rId29"/>
+    <hyperlink ref="O56" r:id="rId30"/>
+    <hyperlink ref="O58" r:id="rId31"/>
+    <hyperlink ref="O62" r:id="rId32"/>
+    <hyperlink ref="O63" r:id="rId33"/>
+    <hyperlink ref="O64" r:id="rId34"/>
+    <hyperlink ref="O65" r:id="rId35"/>
+    <hyperlink ref="O66" r:id="rId36"/>
+    <hyperlink ref="O67" r:id="rId37"/>
+    <hyperlink ref="O80" r:id="rId38"/>
+    <hyperlink ref="O71" r:id="rId39"/>
+    <hyperlink ref="O72" r:id="rId40"/>
+    <hyperlink ref="O73" r:id="rId41"/>
+    <hyperlink ref="O74" r:id="rId42"/>
+    <hyperlink ref="O75" r:id="rId43"/>
+    <hyperlink ref="O76" r:id="rId44"/>
+    <hyperlink ref="O77" r:id="rId45"/>
+    <hyperlink ref="O78" r:id="rId46"/>
+    <hyperlink ref="O79" r:id="rId47"/>
+    <hyperlink ref="O81" r:id="rId48"/>
+    <hyperlink ref="O82" r:id="rId49"/>
+    <hyperlink ref="O83" r:id="rId50"/>
+    <hyperlink ref="O86" r:id="rId51"/>
+    <hyperlink ref="O84" r:id="rId52"/>
+    <hyperlink ref="O88" r:id="rId53"/>
+    <hyperlink ref="O89" r:id="rId54"/>
+    <hyperlink ref="O91" r:id="rId55"/>
+    <hyperlink ref="O92" r:id="rId56"/>
+    <hyperlink ref="O93" r:id="rId57"/>
+    <hyperlink ref="O94" r:id="rId58"/>
+    <hyperlink ref="O95" r:id="rId59"/>
+    <hyperlink ref="O98" r:id="rId60"/>
+    <hyperlink ref="O70" r:id="rId61"/>
+    <hyperlink ref="O10" r:id="rId62"/>
+    <hyperlink ref="O87" r:id="rId63"/>
+    <hyperlink ref="O69" r:id="rId64"/>
+    <hyperlink ref="O38" r:id="rId65"/>
+    <hyperlink ref="O39" r:id="rId66"/>
+    <hyperlink ref="O49" r:id="rId67"/>
+    <hyperlink ref="O52" r:id="rId68"/>
+    <hyperlink ref="O54" r:id="rId69"/>
+    <hyperlink ref="O60" r:id="rId70"/>
+    <hyperlink ref="O53" r:id="rId71"/>
+    <hyperlink ref="O26" r:id="rId72"/>
+    <hyperlink ref="O27" r:id="rId73"/>
+    <hyperlink ref="O28" r:id="rId74"/>
+    <hyperlink ref="O31" r:id="rId75"/>
+    <hyperlink ref="O40" r:id="rId76"/>
+    <hyperlink ref="O41" r:id="rId77"/>
+    <hyperlink ref="O42" r:id="rId78"/>
+    <hyperlink ref="O43" r:id="rId79"/>
+    <hyperlink ref="O44" r:id="rId80"/>
+    <hyperlink ref="O45" r:id="rId81"/>
+    <hyperlink ref="O57" r:id="rId82"/>
+    <hyperlink ref="O68" r:id="rId83"/>
+    <hyperlink ref="O96" r:id="rId84"/>
+    <hyperlink ref="O97" r:id="rId85"/>
+    <hyperlink ref="O90" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId75"/>
-  <drawing r:id="rId76"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId87"/>
+  <drawing r:id="rId88"/>
 </worksheet>
 </file>
--- a/Design-Files/SM_Top_Board_v3.4/BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Design-Files/SM_Top_Board_v3.4/BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="521">
   <si>
     <t>Component list</t>
   </si>
@@ -70,9 +70,6 @@
     <t>C22</t>
   </si>
   <si>
-    <t>C25, C32</t>
-  </si>
-  <si>
     <t>C30</t>
   </si>
   <si>
@@ -142,24 +139,12 @@
     <t>R6, R7, R8, R9</t>
   </si>
   <si>
-    <t>R21</t>
-  </si>
-  <si>
     <t>R22</t>
   </si>
   <si>
     <t>R23</t>
   </si>
   <si>
-    <t>R24</t>
-  </si>
-  <si>
-    <t>R27</t>
-  </si>
-  <si>
-    <t>R28</t>
-  </si>
-  <si>
     <t>R29</t>
   </si>
   <si>
@@ -322,24 +307,9 @@
     <t>RES SMD 150OHM 1/10W 0603</t>
   </si>
   <si>
-    <t>RES SMD 3.01K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES SMD 11K, 1%, 0.1W, 0603</t>
-  </si>
-  <si>
     <t>RES SMD 2.2OHM 0603</t>
   </si>
   <si>
-    <t>RES SMD 12.4K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES SMD 11.8K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES SMD 105K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES SMD 127K OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -382,9 +352,6 @@
     <t>IC MTR DRVR BIPOLAR 8-60V 48TQFP</t>
   </si>
   <si>
-    <t>IC OPAMP GP 1.7MHZ RRO SOT23-6</t>
-  </si>
-  <si>
     <t>IC BUS BUFFER TRI-ST QD 14TSSOP</t>
   </si>
   <si>
@@ -535,24 +502,9 @@
     <t>RC0603FR-07150RL</t>
   </si>
   <si>
-    <t>ERJ-3EKF3011V</t>
-  </si>
-  <si>
-    <t>RC0603FR-0711KL</t>
-  </si>
-  <si>
     <t>ERJ-3GEYJ2R2V</t>
   </si>
   <si>
-    <t>RC0603FR-0712K4L</t>
-  </si>
-  <si>
-    <t>AC0603FR-0711K8L</t>
-  </si>
-  <si>
-    <t>RC0603FR-07105KL</t>
-  </si>
-  <si>
     <t>RT0603FRE07127KL</t>
   </si>
   <si>
@@ -577,9 +529,6 @@
     <t>TMC5160A-TA-T</t>
   </si>
   <si>
-    <t>MAX4236EUT+T</t>
-  </si>
-  <si>
     <t>Manufacturer</t>
   </si>
   <si>
@@ -664,9 +613,6 @@
     <t>Maxim</t>
   </si>
   <si>
-    <t>Comment</t>
-  </si>
-  <si>
     <t>220uF</t>
   </si>
   <si>
@@ -751,24 +697,9 @@
     <t>150R</t>
   </si>
   <si>
-    <t>3.01K</t>
-  </si>
-  <si>
-    <t>11K</t>
-  </si>
-  <si>
     <t>2R2</t>
   </si>
   <si>
-    <t>12.4K</t>
-  </si>
-  <si>
-    <t>11.8K</t>
-  </si>
-  <si>
-    <t>105K</t>
-  </si>
-  <si>
     <t>127K</t>
   </si>
   <si>
@@ -1022,18 +953,6 @@
   </si>
   <si>
     <t>C114608</t>
-  </si>
-  <si>
-    <t>C137801</t>
-  </si>
-  <si>
-    <t>C137798</t>
-  </si>
-  <si>
-    <t>C227561</t>
-  </si>
-  <si>
-    <t>C141685</t>
   </si>
   <si>
     <t>ARG03FTC1273</t>
@@ -1237,21 +1156,6 @@
   </si>
   <si>
     <r>
-      <t>C8, C10, C11, C12,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> C41, CF3</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">C3, </t>
     </r>
     <r>
@@ -1446,9 +1350,6 @@
     <t>C48, C49</t>
   </si>
   <si>
-    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, Cx1, Cx2</t>
-  </si>
-  <si>
     <t>C7</t>
   </si>
   <si>
@@ -1690,6 +1591,108 @@
   </si>
   <si>
     <t>C138135.</t>
+  </si>
+  <si>
+    <t>BZT52C16</t>
+  </si>
+  <si>
+    <t>STD10P6F6</t>
+  </si>
+  <si>
+    <t>RT0603BRE07402RL</t>
+  </si>
+  <si>
+    <t>AC0603JR-07150KL</t>
+  </si>
+  <si>
+    <t>RC0603FR-07100RL</t>
+  </si>
+  <si>
+    <t>MAX31865ATP+</t>
+  </si>
+  <si>
+    <t>C2, C13, C15, C20, C40, C51, C52, C53, C54, C55, C61, C63</t>
+  </si>
+  <si>
+    <t>C8, C10, C11, C12, C41, C62, CF3</t>
+  </si>
+  <si>
+    <t>C25, C32, C47, C56</t>
+  </si>
+  <si>
+    <t>D22</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R21, R24</t>
+  </si>
+  <si>
+    <t>Zener Diode</t>
+  </si>
+  <si>
+    <t>±5% Single 15.3V~17.1V 500mW 16V SOD-123 Zener Diodes ROHS</t>
+  </si>
+  <si>
+    <t>SOD-123</t>
+  </si>
+  <si>
+    <t>Shikues</t>
+  </si>
+  <si>
+    <t>C216724</t>
+  </si>
+  <si>
+    <t>MOSFET</t>
+  </si>
+  <si>
+    <t>MOSFET P CH 60V 10A DPAK</t>
+  </si>
+  <si>
+    <t>DPAK</t>
+  </si>
+  <si>
+    <t>C457501</t>
+  </si>
+  <si>
+    <t>RES SMD 402 OHM 0.1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>C849745</t>
+  </si>
+  <si>
+    <t>402R</t>
+  </si>
+  <si>
+    <t>RES SMD 150K OHM 5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>150K</t>
+  </si>
+  <si>
+    <t>RES SMD 100 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>IC RTD TO DIGITAL CONVERT 20QFN</t>
+  </si>
+  <si>
+    <t>QFN-20-EP(5x5)</t>
+  </si>
+  <si>
+    <t>C404011</t>
+  </si>
+  <si>
+    <t>Chipsmall</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
 </sst>
 </file>
@@ -2207,7 +2210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2431,9 +2434,6 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2500,6 +2500,18 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2508,18 +2520,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2863,7 +2863,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z103"/>
+  <dimension ref="A1:Z106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2882,7 +2882,7 @@
     <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="29.42578125" customWidth="1"/>
-    <col min="20" max="20" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="26.140625" customWidth="1"/>
     <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -2899,14 +2899,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="110"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="50" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="51" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -2954,7 +2954,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="108"/>
+      <c r="R3" s="111"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="52" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -2978,7 +2978,7 @@
       <c r="O4" s="56"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
-      <c r="R4" s="109"/>
+      <c r="R4" s="112"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3000,7 +3000,7 @@
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
-      <c r="R5" s="109"/>
+      <c r="R5" s="112"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3020,7 +3020,7 @@
       <c r="O6" s="56"/>
       <c r="P6" s="56"/>
       <c r="Q6" s="56"/>
-      <c r="R6" s="109"/>
+      <c r="R6" s="112"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3040,7 +3040,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="109"/>
+      <c r="R7" s="112"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3060,7 +3060,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="109"/>
+      <c r="R8" s="112"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3068,86 +3068,86 @@
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="H9" s="98" t="s">
-        <v>182</v>
+        <v>133</v>
+      </c>
+      <c r="H9" s="97" t="s">
+        <v>165</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>210</v>
+        <v>520</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="O9" s="31" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="R9" s="31" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="106">
+      <c r="B10" s="105">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="54" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D10" s="37" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="L10" s="37">
         <v>1</v>
@@ -3160,7 +3160,7 @@
         <v>22</v>
       </c>
       <c r="O10" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P10" s="39">
         <v>0.38819999999999999</v>
@@ -3173,49 +3173,49 @@
     </row>
     <row r="11" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="106">
+      <c r="B11" s="105">
         <f t="shared" ref="B11:B86" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D11" s="78" t="s">
-        <v>434</v>
+        <v>493</v>
       </c>
       <c r="E11" s="79" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F11" s="78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G11" s="79" t="s">
-        <v>145</v>
-      </c>
-      <c r="H11" s="96" t="s">
-        <v>183</v>
+        <v>134</v>
+      </c>
+      <c r="H11" s="95" t="s">
+        <v>166</v>
       </c>
       <c r="I11" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J11" s="78" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K11" s="79" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="L11" s="78">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M11" s="72">
         <f>L11*20</f>
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="N11" s="72">
         <v>300</v>
       </c>
       <c r="O11" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P11" s="72">
         <v>1.4E-3</v>
@@ -3228,36 +3228,36 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="106">
+      <c r="B12" s="105">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>381</v>
+        <v>353</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="H12" s="99" t="s">
-        <v>184</v>
+        <v>135</v>
+      </c>
+      <c r="H12" s="98" t="s">
+        <v>167</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="L12" s="71">
         <v>2</v>
@@ -3270,7 +3270,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P12" s="39">
         <v>1.2999999999999999E-3</v>
@@ -3283,36 +3283,36 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="106">
+      <c r="B13" s="105">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C13" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D13" s="78" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="E13" s="79" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F13" s="78" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G13" s="79" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" s="96" t="s">
-        <v>185</v>
+        <v>136</v>
+      </c>
+      <c r="H13" s="95" t="s">
+        <v>168</v>
       </c>
       <c r="I13" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J13" s="78" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="K13" s="79" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="L13" s="82">
         <v>1</v>
@@ -3321,11 +3321,11 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N13" s="87">
+      <c r="N13" s="86">
         <v>40</v>
       </c>
       <c r="O13" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P13" s="72">
         <v>3.5900000000000001E-2</v>
@@ -3338,36 +3338,36 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="106">
+      <c r="B14" s="105">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="H14" s="99" t="s">
-        <v>186</v>
+        <v>137</v>
+      </c>
+      <c r="H14" s="98" t="s">
+        <v>169</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>290</v>
+        <v>267</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="L14" s="37">
         <v>6</v>
@@ -3380,7 +3380,7 @@
         <v>130</v>
       </c>
       <c r="O14" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P14" s="39">
         <v>4.0899999999999999E-2</v>
@@ -3393,36 +3393,36 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="106">
+      <c r="B15" s="105">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C15" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D15" s="78" t="s">
-        <v>435</v>
+        <v>406</v>
       </c>
       <c r="E15" s="79" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F15" s="78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G15" s="79" t="s">
-        <v>149</v>
-      </c>
-      <c r="H15" s="96" t="s">
-        <v>184</v>
+        <v>138</v>
+      </c>
+      <c r="H15" s="95" t="s">
+        <v>167</v>
       </c>
       <c r="I15" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J15" s="78" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="K15" s="79" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="L15" s="82">
         <v>1</v>
@@ -3431,11 +3431,11 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N15" s="87">
+      <c r="N15" s="86">
         <v>100</v>
       </c>
       <c r="O15" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P15" s="72">
         <v>5.8999999999999999E-3</v>
@@ -3448,91 +3448,91 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="106">
+      <c r="B16" s="105">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>380</v>
+        <v>494</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G16" s="76" t="s">
-        <v>361</v>
-      </c>
-      <c r="H16" s="100" t="s">
-        <v>186</v>
+        <v>334</v>
+      </c>
+      <c r="H16" s="99" t="s">
+        <v>169</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="L16" s="37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M16" s="39">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N16" s="39">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="O16" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P16" s="39">
         <v>3.32E-2</v>
       </c>
       <c r="Q16" s="39">
         <f t="shared" ref="Q16" si="5">P16*N16</f>
-        <v>4.3159999999999998</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="R16" s="68"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="106">
+      <c r="B17" s="105">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D17" s="78" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="79" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F17" s="78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G17" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="H17" s="96" t="s">
-        <v>184</v>
+        <v>139</v>
+      </c>
+      <c r="H17" s="95" t="s">
+        <v>167</v>
       </c>
       <c r="I17" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J17" s="78" t="s">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="K17" s="79" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="L17" s="78">
         <v>1</v>
@@ -3545,7 +3545,7 @@
         <v>100</v>
       </c>
       <c r="O17" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P17" s="72">
         <v>3.0999999999999999E-3</v>
@@ -3558,36 +3558,36 @@
     </row>
     <row r="18" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="106">
+      <c r="B18" s="105">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C18" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D18" s="78" t="s">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="E18" s="79" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F18" s="78" t="s">
-        <v>121</v>
-      </c>
-      <c r="G18" s="85" t="s">
-        <v>151</v>
-      </c>
-      <c r="H18" s="96" t="s">
-        <v>187</v>
+        <v>110</v>
+      </c>
+      <c r="G18" s="84" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" s="95" t="s">
+        <v>170</v>
       </c>
       <c r="I18" s="78" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="J18" s="78" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="K18" s="79" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="L18" s="78">
         <v>8</v>
@@ -3600,7 +3600,7 @@
         <v>180</v>
       </c>
       <c r="O18" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P18" s="72">
         <v>3.09E-2</v>
@@ -3613,36 +3613,36 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="106">
+      <c r="B19" s="105">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D19" s="37" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="G19" s="84" t="s">
-        <v>152</v>
-      </c>
-      <c r="H19" s="99" t="s">
-        <v>188</v>
+        <v>108</v>
+      </c>
+      <c r="G19" s="83" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="98" t="s">
+        <v>171</v>
       </c>
       <c r="I19" s="37" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="J19" s="37" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="K19" s="38" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="L19" s="37">
         <v>1</v>
@@ -3655,7 +3655,7 @@
         <v>100</v>
       </c>
       <c r="O19" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P19" s="39">
         <v>5.3E-3</v>
@@ -3668,36 +3668,36 @@
     </row>
     <row r="20" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="106">
+      <c r="B20" s="105">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C20" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D20" s="78" t="s">
         <v>11</v>
       </c>
       <c r="E20" s="79" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F20" s="78" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G20" s="78" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="96" t="s">
-        <v>189</v>
+        <v>111</v>
+      </c>
+      <c r="H20" s="95" t="s">
+        <v>172</v>
       </c>
       <c r="I20" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J20" s="78" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="K20" s="79" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="L20" s="78">
         <v>1</v>
@@ -3710,7 +3710,7 @@
         <v>25</v>
       </c>
       <c r="O20" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P20" s="72">
         <v>0.22189999999999999</v>
@@ -3723,36 +3723,36 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="106">
+      <c r="B21" s="105">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C21" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D21" s="78" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="E21" s="79" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F21" s="78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G21" s="79" t="s">
-        <v>156</v>
-      </c>
-      <c r="H21" s="96" t="s">
-        <v>184</v>
+        <v>145</v>
+      </c>
+      <c r="H21" s="95" t="s">
+        <v>167</v>
       </c>
       <c r="I21" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J21" s="78" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="K21" s="79" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L21" s="78">
         <v>2</v>
@@ -3765,7 +3765,7 @@
         <v>100</v>
       </c>
       <c r="O21" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P21" s="72">
         <v>3.2000000000000002E-3</v>
@@ -3778,49 +3778,49 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="106">
+      <c r="B22" s="105">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>12</v>
+        <v>495</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="H22" s="99" t="s">
-        <v>183</v>
+        <v>142</v>
+      </c>
+      <c r="H22" s="98" t="s">
+        <v>166</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="L22" s="37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M22" s="39">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="N22" s="39">
         <v>100</v>
       </c>
       <c r="O22" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P22" s="39">
         <v>7.7000000000000002E-3</v>
@@ -3833,36 +3833,36 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="106">
+      <c r="B23" s="105">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="99" t="s">
-        <v>185</v>
+        <v>143</v>
+      </c>
+      <c r="H23" s="98" t="s">
+        <v>168</v>
       </c>
       <c r="I23" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J23" s="37" t="s">
-        <v>300</v>
+        <v>277</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="L23" s="37">
         <v>1</v>
@@ -3875,7 +3875,7 @@
         <v>40</v>
       </c>
       <c r="O23" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P23" s="39">
         <v>3.49E-2</v>
@@ -3888,36 +3888,36 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="106">
+      <c r="B24" s="105">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C24" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D24" s="78" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="E24" s="79" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F24" s="78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G24" s="79" t="s">
-        <v>155</v>
-      </c>
-      <c r="H24" s="96" t="s">
-        <v>183</v>
+        <v>144</v>
+      </c>
+      <c r="H24" s="95" t="s">
+        <v>166</v>
       </c>
       <c r="I24" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J24" s="78" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="K24" s="79" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="L24" s="78">
         <v>1</v>
@@ -3930,7 +3930,7 @@
         <v>40</v>
       </c>
       <c r="O24" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P24" s="72">
         <v>1.9199999999999998E-2</v>
@@ -3943,36 +3943,36 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="106">
+      <c r="B25" s="105">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="G25" s="86">
+        <v>109</v>
+      </c>
+      <c r="G25" s="85">
         <v>885012205080</v>
       </c>
-      <c r="H25" s="99" t="s">
-        <v>190</v>
+      <c r="H25" s="98" t="s">
+        <v>173</v>
       </c>
       <c r="I25" s="37" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="J25" s="37" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="L25" s="37">
         <v>1</v>
@@ -3985,7 +3985,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P25" s="39">
         <v>3.0000000000000001E-3</v>
@@ -3998,36 +3998,36 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="106">
+      <c r="B26" s="105">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>437</v>
+        <v>408</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -4040,12 +4040,12 @@
         <v>100</v>
       </c>
       <c r="O26" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="P26" s="110">
+        <v>263</v>
+      </c>
+      <c r="P26" s="106">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="Q26" s="110">
+      <c r="Q26" s="106">
         <f>P26*N26</f>
         <v>0.25</v>
       </c>
@@ -4053,36 +4053,36 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="111">
+      <c r="B27" s="107">
         <f t="shared" ref="B27" si="15">ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D27" s="78" t="s">
-        <v>438</v>
+        <v>409</v>
       </c>
       <c r="E27" s="78" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="F27" s="78" t="s">
-        <v>460</v>
+        <v>431</v>
       </c>
       <c r="G27" s="78" t="s">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="H27" s="78" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="I27" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J27" s="78" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="K27" s="78" t="s">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="L27" s="78">
         <v>1</v>
@@ -4094,13 +4094,13 @@
       <c r="N27" s="78">
         <v>50</v>
       </c>
-      <c r="O27" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P27" s="112">
+      <c r="O27" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P27" s="108">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="Q27" s="112">
+      <c r="Q27" s="108">
         <f t="shared" ref="Q27" si="16">P27*N27</f>
         <v>0.53499999999999992</v>
       </c>
@@ -4108,36 +4108,36 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="106">
+      <c r="B28" s="105">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -4150,12 +4150,12 @@
         <v>21</v>
       </c>
       <c r="O28" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="P28" s="110">
+        <v>263</v>
+      </c>
+      <c r="P28" s="106">
         <v>0.39529999999999998</v>
       </c>
-      <c r="Q28" s="110">
+      <c r="Q28" s="106">
         <f>P28*N28</f>
         <v>8.3012999999999995</v>
       </c>
@@ -4163,36 +4163,36 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="106">
+      <c r="B29" s="105">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C29" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D29" s="78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" s="81" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="F29" s="78" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G29" s="81" t="s">
-        <v>378</v>
-      </c>
-      <c r="H29" s="101" t="s">
-        <v>200</v>
+        <v>351</v>
+      </c>
+      <c r="H29" s="100" t="s">
+        <v>183</v>
       </c>
       <c r="I29" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J29" s="78" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="K29" s="81" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="L29" s="78">
         <v>1</v>
@@ -4205,7 +4205,7 @@
         <v>100</v>
       </c>
       <c r="O29" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P29" s="72">
         <v>3.3999999999999998E-3</v>
@@ -4218,36 +4218,36 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="106">
+      <c r="B30" s="105">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="H30" s="99" t="s">
-        <v>186</v>
+        <v>146</v>
+      </c>
+      <c r="H30" s="98" t="s">
+        <v>169</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -4260,7 +4260,7 @@
         <v>30</v>
       </c>
       <c r="O30" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P30" s="39">
         <v>0.2525</v>
@@ -4273,34 +4273,34 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="111">
+      <c r="B31" s="107">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C31" s="77" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D31" s="78" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="E31" s="78" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="F31" s="78" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="G31" s="78" t="s">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="H31" s="78" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="I31" s="78"/>
       <c r="J31" s="78" t="s">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="K31" s="78" t="s">
-        <v>470</v>
+        <v>441</v>
       </c>
       <c r="L31" s="78">
         <v>2</v>
@@ -4312,13 +4312,13 @@
       <c r="N31" s="78">
         <v>45</v>
       </c>
-      <c r="O31" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P31" s="112">
+      <c r="O31" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P31" s="108">
         <v>0.2087</v>
       </c>
-      <c r="Q31" s="112">
+      <c r="Q31" s="108">
         <f t="shared" si="18"/>
         <v>9.3915000000000006</v>
       </c>
@@ -4326,36 +4326,36 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="106">
+      <c r="B32" s="105">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="H32" s="99" t="s">
-        <v>187</v>
+        <v>147</v>
+      </c>
+      <c r="H32" s="98" t="s">
+        <v>170</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="L32" s="37">
         <v>2</v>
@@ -4368,7 +4368,7 @@
         <v>41</v>
       </c>
       <c r="O32" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P32" s="39">
         <v>0.89410000000000001</v>
@@ -4381,36 +4381,36 @@
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="106">
+      <c r="B33" s="105">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="H33" s="99" t="s">
-        <v>184</v>
+        <v>148</v>
+      </c>
+      <c r="H33" s="98" t="s">
+        <v>167</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="L33" s="37">
         <v>1</v>
@@ -4423,7 +4423,7 @@
         <v>100</v>
       </c>
       <c r="O33" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P33" s="39">
         <v>3.0999999999999999E-3</v>
@@ -4436,36 +4436,36 @@
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="106">
+      <c r="B34" s="105">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="H34" s="99" t="s">
-        <v>183</v>
+        <v>149</v>
+      </c>
+      <c r="H34" s="98" t="s">
+        <v>166</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -4478,7 +4478,7 @@
         <v>100</v>
       </c>
       <c r="O34" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P34" s="39">
         <v>5.4999999999999997E-3</v>
@@ -4491,36 +4491,36 @@
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="106">
+      <c r="B35" s="105">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C35" s="77" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D35" s="78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E35" s="79" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F35" s="78" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G35" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="H35" s="96" t="s">
-        <v>191</v>
+        <v>114</v>
+      </c>
+      <c r="H35" s="95" t="s">
+        <v>174</v>
       </c>
       <c r="I35" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J35" s="78" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="K35" s="79" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L35" s="78">
         <v>1</v>
@@ -4533,7 +4533,7 @@
         <v>30</v>
       </c>
       <c r="O35" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P35" s="72">
         <v>4.87E-2</v>
@@ -4546,36 +4546,36 @@
     </row>
     <row r="36" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="106">
+      <c r="B36" s="105">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="H36" s="99" t="s">
-        <v>192</v>
+        <v>211</v>
+      </c>
+      <c r="H36" s="98" t="s">
+        <v>175</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L36" s="37">
         <v>1</v>
@@ -4588,7 +4588,7 @@
         <v>30</v>
       </c>
       <c r="O36" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P36" s="39">
         <v>7.4300000000000005E-2</v>
@@ -4601,36 +4601,36 @@
     </row>
     <row r="37" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="106">
+      <c r="B37" s="105">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C37" s="77" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D37" s="78" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="E37" s="79" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F37" s="78" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G37" s="79" t="s">
-        <v>230</v>
-      </c>
-      <c r="H37" s="96" t="s">
-        <v>192</v>
+        <v>212</v>
+      </c>
+      <c r="H37" s="95" t="s">
+        <v>175</v>
       </c>
       <c r="I37" s="78" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="J37" s="78" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="K37" s="79" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L37" s="78">
         <v>2</v>
@@ -4643,7 +4643,7 @@
         <v>60</v>
       </c>
       <c r="O37" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P37" s="72">
         <v>2.8899999999999999E-2</v>
@@ -4656,96 +4656,96 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="106">
+      <c r="B38" s="105">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="89" t="s">
-        <v>262</v>
-      </c>
-      <c r="D38" s="90" t="s">
-        <v>371</v>
-      </c>
-      <c r="E38" s="91" t="s">
-        <v>410</v>
-      </c>
-      <c r="F38" s="91" t="s">
-        <v>254</v>
-      </c>
-      <c r="G38" s="91" t="s">
-        <v>407</v>
-      </c>
-      <c r="H38" s="102" t="s">
-        <v>411</v>
-      </c>
-      <c r="I38" s="91" t="s">
-        <v>259</v>
-      </c>
-      <c r="J38" s="91" t="s">
-        <v>422</v>
-      </c>
-      <c r="K38" s="92" t="s">
-        <v>259</v>
-      </c>
-      <c r="L38" s="91">
+      <c r="C38" s="88" t="s">
+        <v>239</v>
+      </c>
+      <c r="D38" s="89" t="s">
+        <v>344</v>
+      </c>
+      <c r="E38" s="90" t="s">
+        <v>382</v>
+      </c>
+      <c r="F38" s="90" t="s">
+        <v>231</v>
+      </c>
+      <c r="G38" s="90" t="s">
+        <v>379</v>
+      </c>
+      <c r="H38" s="101" t="s">
+        <v>383</v>
+      </c>
+      <c r="I38" s="90" t="s">
+        <v>236</v>
+      </c>
+      <c r="J38" s="90" t="s">
+        <v>394</v>
+      </c>
+      <c r="K38" s="91" t="s">
+        <v>236</v>
+      </c>
+      <c r="L38" s="90">
         <v>8</v>
       </c>
-      <c r="M38" s="92">
+      <c r="M38" s="91">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
       <c r="N38" s="72">
         <v>165</v>
       </c>
-      <c r="O38" s="93" t="s">
-        <v>286</v>
-      </c>
-      <c r="P38" s="92">
+      <c r="O38" s="92" t="s">
+        <v>263</v>
+      </c>
+      <c r="P38" s="91">
         <v>0.14319999999999999</v>
       </c>
-      <c r="Q38" s="92">
+      <c r="Q38" s="91">
         <f t="shared" ref="Q38:Q39" si="25">P38*N38</f>
         <v>23.628</v>
       </c>
-      <c r="R38" s="94"/>
-    </row>
-    <row r="39" spans="1:26" s="95" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="88"/>
-      <c r="B39" s="106">
+      <c r="R38" s="93"/>
+    </row>
+    <row r="39" spans="1:26" s="94" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="87"/>
+      <c r="B39" s="105">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="77" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="E39" s="78" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="F39" s="78" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="G39" s="78" t="s">
-        <v>402</v>
-      </c>
-      <c r="H39" s="96" t="s">
-        <v>193</v>
+        <v>374</v>
+      </c>
+      <c r="H39" s="95" t="s">
+        <v>176</v>
       </c>
       <c r="I39" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J39" s="78" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="K39" s="72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L39" s="78">
         <v>2</v>
       </c>
-      <c r="M39" s="92">
+      <c r="M39" s="91">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
@@ -4753,12 +4753,12 @@
         <v>45</v>
       </c>
       <c r="O39" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P39" s="39">
         <v>0.1464</v>
       </c>
-      <c r="Q39" s="92">
+      <c r="Q39" s="91">
         <f t="shared" si="25"/>
         <v>6.5880000000000001</v>
       </c>
@@ -4774,41 +4774,41 @@
     </row>
     <row r="40" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="106">
+      <c r="B40" s="105">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>472</v>
+        <v>443</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
       <c r="K40" s="72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
       </c>
-      <c r="M40" s="92">
+      <c r="M40" s="91">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -4816,12 +4816,12 @@
         <v>30</v>
       </c>
       <c r="O40" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="P40" s="110">
+        <v>263</v>
+      </c>
+      <c r="P40" s="106">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="Q40" s="110">
+      <c r="Q40" s="106">
         <f>P40*N40</f>
         <v>2.5920000000000001</v>
       </c>
@@ -4829,54 +4829,54 @@
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="111">
-        <f t="shared" ref="B41:B45" si="26">ROW(B41) - ROW($B$9)</f>
+      <c r="B41" s="107">
+        <f t="shared" ref="B41:B46" si="26">ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
       <c r="C41" s="77" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="D41" s="78" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="E41" s="78" t="s">
-        <v>476</v>
+        <v>447</v>
       </c>
       <c r="F41" s="78" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G41" s="78" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="H41" s="78" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="I41" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J41" s="78" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="K41" s="72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L41" s="78">
         <v>1</v>
       </c>
-      <c r="M41" s="92">
+      <c r="M41" s="91">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N41" s="78">
         <v>25</v>
       </c>
-      <c r="O41" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P41" s="112">
+      <c r="O41" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P41" s="108">
         <v>0.1709</v>
       </c>
-      <c r="Q41" s="112">
+      <c r="Q41" s="108">
         <f t="shared" ref="Q41" si="27">P41*N41</f>
         <v>4.2725</v>
       </c>
@@ -4884,54 +4884,54 @@
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="B42" s="106">
+      <c r="B42" s="105">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>513</v>
+        <v>484</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="K42" s="72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L42" s="37">
         <v>2</v>
       </c>
-      <c r="M42" s="92">
+      <c r="M42" s="91">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="N42" s="37">
         <v>45</v>
       </c>
-      <c r="O42" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P42" s="110">
+      <c r="O42" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P42" s="106">
         <v>0.1135</v>
       </c>
-      <c r="Q42" s="110">
+      <c r="Q42" s="106">
         <f>P42*N42</f>
         <v>5.1074999999999999</v>
       </c>
@@ -4939,54 +4939,54 @@
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="B43" s="111">
+      <c r="B43" s="107">
         <f t="shared" si="26"/>
         <v>34</v>
       </c>
       <c r="C43" s="77" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="D43" s="78" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="E43" s="78" t="s">
+        <v>455</v>
+      </c>
+      <c r="F43" s="78" t="s">
+        <v>452</v>
+      </c>
+      <c r="G43" s="78" t="s">
+        <v>457</v>
+      </c>
+      <c r="H43" s="37" t="s">
         <v>484</v>
       </c>
-      <c r="F43" s="78" t="s">
-        <v>481</v>
-      </c>
-      <c r="G43" s="78" t="s">
-        <v>486</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>513</v>
-      </c>
       <c r="I43" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J43" s="78" t="s">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="K43" s="72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L43" s="78">
         <v>1</v>
       </c>
-      <c r="M43" s="92">
+      <c r="M43" s="91">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N43" s="78">
         <v>21</v>
       </c>
-      <c r="O43" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P43" s="112">
+      <c r="O43" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P43" s="108">
         <v>5.91E-2</v>
       </c>
-      <c r="Q43" s="112">
+      <c r="Q43" s="108">
         <f t="shared" ref="Q43" si="28">P43*N43</f>
         <v>1.2411000000000001</v>
       </c>
@@ -4994,54 +4994,54 @@
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="106">
+      <c r="B44" s="105">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="K44" s="72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L44" s="37">
         <v>1</v>
       </c>
-      <c r="M44" s="92">
+      <c r="M44" s="91">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="N44" s="37">
         <v>25</v>
       </c>
-      <c r="O44" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P44" s="110">
+      <c r="O44" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P44" s="106">
         <v>0.17249999999999999</v>
       </c>
-      <c r="Q44" s="110">
+      <c r="Q44" s="106">
         <f>P44*N44</f>
         <v>4.3125</v>
       </c>
@@ -5049,421 +5049,421 @@
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="B45" s="111">
+      <c r="B45" s="107">
         <f t="shared" si="26"/>
         <v>36</v>
       </c>
       <c r="C45" s="77" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="D45" s="78" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="E45" s="78" t="s">
-        <v>491</v>
+        <v>462</v>
       </c>
       <c r="F45" s="78" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
       <c r="G45" s="78" t="s">
-        <v>494</v>
+        <v>465</v>
       </c>
       <c r="H45" s="37" t="s">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="I45" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J45" s="78" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="K45" s="72" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L45" s="78">
         <v>2</v>
       </c>
-      <c r="M45" s="92">
+      <c r="M45" s="91">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="N45" s="78">
         <v>45</v>
       </c>
-      <c r="O45" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P45" s="112">
+      <c r="O45" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P45" s="108">
         <v>0.2072</v>
       </c>
-      <c r="Q45" s="112">
+      <c r="Q45" s="108">
         <f t="shared" ref="Q45" si="29">P45*N45</f>
         <v>9.3239999999999998</v>
       </c>
       <c r="R45" s="78"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="24" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="B46" s="106">
+      <c r="B46" s="107">
+        <f t="shared" si="26"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="55" t="s">
+        <v>500</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>501</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>502</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>487</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>503</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>504</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="L46" s="37">
+        <v>1</v>
+      </c>
+      <c r="M46" s="37">
+        <f>L46*5</f>
+        <v>5</v>
+      </c>
+      <c r="N46" s="37">
+        <v>50</v>
+      </c>
+      <c r="O46" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="P46" s="106">
+        <v>1.41E-2</v>
+      </c>
+      <c r="Q46" s="106">
+        <f>P46*N46</f>
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="R46" s="37"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="105">
         <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C46" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="D46" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="79" t="s">
-        <v>82</v>
-      </c>
-      <c r="F46" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G46" s="85" t="s">
-        <v>127</v>
-      </c>
-      <c r="H46" s="96" t="s">
-        <v>194</v>
-      </c>
-      <c r="I46" s="78" t="s">
-        <v>312</v>
-      </c>
-      <c r="J46" s="78" t="s">
-        <v>313</v>
-      </c>
-      <c r="K46" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L46" s="78">
+        <v>38</v>
+      </c>
+      <c r="C47" s="77" t="s">
+        <v>241</v>
+      </c>
+      <c r="D47" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G47" s="84" t="s">
+        <v>116</v>
+      </c>
+      <c r="H47" s="95" t="s">
+        <v>177</v>
+      </c>
+      <c r="I47" s="78" t="s">
+        <v>289</v>
+      </c>
+      <c r="J47" s="78" t="s">
+        <v>290</v>
+      </c>
+      <c r="K47" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="L47" s="78">
         <v>1</v>
       </c>
-      <c r="M46" s="72">
+      <c r="M47" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N46" s="72">
+      <c r="N47" s="72">
         <v>30</v>
       </c>
-      <c r="O46" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P46" s="72">
+      <c r="O47" s="80" t="s">
+        <v>263</v>
+      </c>
+      <c r="P47" s="72">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="Q46" s="72">
-        <f t="shared" ref="Q46" si="30">N46*P46</f>
+      <c r="Q47" s="72">
+        <f t="shared" ref="Q47" si="30">N47*P47</f>
         <v>1.68</v>
       </c>
-      <c r="R46" s="72"/>
-    </row>
-    <row r="47" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="106">
+      <c r="R47" s="72"/>
+    </row>
+    <row r="48" spans="1:26" ht="24" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="105">
         <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="55" t="s">
-        <v>263</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>255</v>
-      </c>
-      <c r="G47" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="H47" s="99" t="s">
-        <v>188</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J47" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="K47" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L47" s="37">
+        <v>39</v>
+      </c>
+      <c r="C48" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="D48" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="F48" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="H48" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="I48" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J48" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="K48" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="L48" s="37">
         <v>4</v>
       </c>
-      <c r="M47" s="39">
+      <c r="M48" s="39">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N47" s="39">
+      <c r="N48" s="39">
         <v>100</v>
       </c>
-      <c r="O47" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P47" s="39">
+      <c r="O48" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P48" s="39">
         <v>2.9499999999999998E-2</v>
       </c>
-      <c r="Q47" s="39">
-        <f t="shared" ref="Q47" si="31">P47*N47</f>
+      <c r="Q48" s="39">
+        <f t="shared" ref="Q48" si="31">P48*N48</f>
         <v>2.9499999999999997</v>
       </c>
-      <c r="R47" s="39"/>
-    </row>
-    <row r="48" spans="1:26" ht="24" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="106">
+      <c r="R48" s="39"/>
+    </row>
+    <row r="49" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="105">
         <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C48" s="77" t="s">
-        <v>414</v>
-      </c>
-      <c r="D48" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>315</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I48" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J48" s="78" t="s">
-        <v>316</v>
-      </c>
-      <c r="K48" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L48" s="78">
+        <v>40</v>
+      </c>
+      <c r="C49" s="77" t="s">
+        <v>386</v>
+      </c>
+      <c r="D49" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="37" t="s">
+        <v>393</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="G49" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="I49" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J49" s="78" t="s">
+        <v>293</v>
+      </c>
+      <c r="K49" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="L49" s="78">
         <v>1</v>
       </c>
-      <c r="M48" s="72">
+      <c r="M49" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N48" s="72">
+      <c r="N49" s="72">
         <v>21</v>
       </c>
-      <c r="O48" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P48" s="72">
+      <c r="O49" s="80" t="s">
+        <v>263</v>
+      </c>
+      <c r="P49" s="72">
         <v>0.53559999999999997</v>
       </c>
-      <c r="Q48" s="72">
-        <f t="shared" ref="Q48" si="32">N48*P48</f>
+      <c r="Q49" s="72">
+        <f t="shared" ref="Q49" si="32">N49*P49</f>
         <v>11.247599999999998</v>
       </c>
-      <c r="R48" s="69"/>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="106">
+      <c r="R49" s="69"/>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="105">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="77" t="s">
-        <v>412</v>
-      </c>
-      <c r="D49" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="78" t="s">
-        <v>413</v>
-      </c>
-      <c r="F49" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G49" s="78" t="s">
-        <v>408</v>
-      </c>
-      <c r="H49" s="96" t="s">
-        <v>405</v>
-      </c>
-      <c r="I49" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J49" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K49" s="72" t="s">
-        <v>259</v>
-      </c>
-      <c r="L49" s="78">
+        <v>41</v>
+      </c>
+      <c r="C50" s="77" t="s">
+        <v>384</v>
+      </c>
+      <c r="D50" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="78" t="s">
+        <v>385</v>
+      </c>
+      <c r="F50" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G50" s="78" t="s">
+        <v>380</v>
+      </c>
+      <c r="H50" s="95" t="s">
+        <v>377</v>
+      </c>
+      <c r="I50" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J50" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="K50" s="72" t="s">
+        <v>236</v>
+      </c>
+      <c r="L50" s="78">
         <v>2</v>
       </c>
-      <c r="M49" s="39">
+      <c r="M50" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N49" s="39">
+      <c r="N50" s="39">
         <v>42</v>
       </c>
-      <c r="O49" s="57" t="s">
-        <v>348</v>
-      </c>
-      <c r="P49" s="39">
+      <c r="O50" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="P50" s="39">
         <v>2.2490000000000001</v>
       </c>
-      <c r="Q49" s="39">
-        <f t="shared" ref="Q49" si="33">P49*N49</f>
+      <c r="Q50" s="39">
+        <f t="shared" ref="Q50" si="33">P50*N50</f>
         <v>94.457999999999998</v>
       </c>
-      <c r="R49" s="69"/>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="106">
+      <c r="R50" s="69"/>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="105">
         <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C50" s="77" t="s">
-        <v>266</v>
-      </c>
-      <c r="D50" s="78" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="F50" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G50" s="79" t="s">
-        <v>129</v>
-      </c>
-      <c r="H50" s="96" t="s">
-        <v>196</v>
-      </c>
-      <c r="I50" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J50" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K50" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L50" s="78">
+        <v>42</v>
+      </c>
+      <c r="C51" s="77" t="s">
+        <v>243</v>
+      </c>
+      <c r="D51" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G51" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="H51" s="95" t="s">
+        <v>179</v>
+      </c>
+      <c r="I51" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J51" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="K51" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="L51" s="78">
         <v>1</v>
       </c>
-      <c r="M50" s="72">
+      <c r="M51" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N50" s="72">
+      <c r="N51" s="72">
         <v>21</v>
       </c>
-      <c r="O50" s="80" t="s">
-        <v>317</v>
-      </c>
-      <c r="P50" s="72">
+      <c r="O51" s="80" t="s">
+        <v>294</v>
+      </c>
+      <c r="P51" s="72">
         <v>1.2</v>
       </c>
-      <c r="Q50" s="72">
-        <f t="shared" ref="Q50" si="34">N50*P50</f>
+      <c r="Q51" s="72">
+        <f t="shared" ref="Q51" si="34">N51*P51</f>
         <v>25.2</v>
       </c>
-      <c r="R50" s="72"/>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="106">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C51" s="55" t="s">
-        <v>266</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G51" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="H51" s="99" t="s">
-        <v>197</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="K51" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L51" s="37">
-        <v>1</v>
-      </c>
-      <c r="M51" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N51" s="39">
-        <v>30</v>
-      </c>
-      <c r="O51" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P51" s="39">
-        <v>4.65E-2</v>
-      </c>
-      <c r="Q51" s="39">
-        <f t="shared" ref="Q51:Q53" si="35">P51*N51</f>
-        <v>1.395</v>
-      </c>
-      <c r="R51" s="39"/>
+      <c r="R51" s="72"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="B52" s="106">
+      <c r="B52" s="105">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C52" s="55" t="s">
-        <v>424</v>
+        <v>243</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>404</v>
+        <v>24</v>
+      </c>
+      <c r="E52" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G52" s="37">
-        <v>533980367</v>
-      </c>
-      <c r="H52" s="99" t="s">
-        <v>405</v>
+        <v>231</v>
+      </c>
+      <c r="G52" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="H52" s="98" t="s">
+        <v>180</v>
       </c>
       <c r="I52" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J52" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K52" s="39" t="s">
-        <v>259</v>
+        <v>295</v>
+      </c>
+      <c r="K52" s="38" t="s">
+        <v>236</v>
       </c>
       <c r="L52" s="37">
         <v>1</v>
@@ -5473,52 +5473,52 @@
         <v>20</v>
       </c>
       <c r="N52" s="39">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O52" s="57" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
       <c r="P52" s="39">
-        <v>1.167</v>
+        <v>4.65E-2</v>
       </c>
       <c r="Q52" s="39">
-        <f t="shared" si="35"/>
-        <v>24.507000000000001</v>
+        <f t="shared" ref="Q52:Q54" si="35">P52*N52</f>
+        <v>1.395</v>
       </c>
       <c r="R52" s="39"/>
     </row>
-    <row r="53" spans="1:18" ht="36" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="106">
+      <c r="B53" s="105">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>424</v>
-      </c>
-      <c r="D53" s="78" t="s">
-        <v>428</v>
-      </c>
-      <c r="E53" s="78" t="s">
-        <v>430</v>
-      </c>
-      <c r="F53" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G53" s="78" t="s">
-        <v>429</v>
-      </c>
-      <c r="H53" s="78" t="s">
-        <v>431</v>
+        <v>396</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="F53" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="G53" s="37">
+        <v>533980367</v>
+      </c>
+      <c r="H53" s="98" t="s">
+        <v>377</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>432</v>
+        <v>236</v>
       </c>
       <c r="K53" s="39" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L53" s="37">
         <v>1</v>
@@ -5528,54 +5528,54 @@
         <v>20</v>
       </c>
       <c r="N53" s="39">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O53" s="57" t="s">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="P53" s="39">
-        <v>6.8699999999999997E-2</v>
+        <v>1.167</v>
       </c>
       <c r="Q53" s="39">
         <f t="shared" si="35"/>
-        <v>1.3739999999999999</v>
+        <v>24.507000000000001</v>
       </c>
       <c r="R53" s="39"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="B54" s="106">
+      <c r="B54" s="105">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C54" s="77" t="s">
-        <v>424</v>
-      </c>
-      <c r="D54" s="82" t="s">
-        <v>389</v>
+      <c r="C54" s="55" t="s">
+        <v>396</v>
+      </c>
+      <c r="D54" s="78" t="s">
+        <v>400</v>
       </c>
       <c r="E54" s="78" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="F54" s="78" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G54" s="78" t="s">
-        <v>409</v>
-      </c>
-      <c r="H54" s="96" t="s">
-        <v>197</v>
-      </c>
-      <c r="I54" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J54" s="78" t="s">
-        <v>425</v>
-      </c>
-      <c r="K54" s="72" t="s">
-        <v>259</v>
-      </c>
-      <c r="L54" s="78">
+        <v>401</v>
+      </c>
+      <c r="H54" s="78" t="s">
+        <v>403</v>
+      </c>
+      <c r="I54" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J54" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="K54" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="L54" s="37">
         <v>1</v>
       </c>
       <c r="M54" s="39">
@@ -5583,1211 +5583,1211 @@
         <v>20</v>
       </c>
       <c r="N54" s="39">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O54" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P54" s="39">
-        <v>0.2044</v>
+        <v>6.8699999999999997E-2</v>
       </c>
       <c r="Q54" s="39">
-        <f>P54*N54</f>
-        <v>5.1100000000000003</v>
+        <f t="shared" si="35"/>
+        <v>1.3739999999999999</v>
       </c>
       <c r="R54" s="39"/>
     </row>
-    <row r="55" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
-      <c r="B55" s="106">
+      <c r="B55" s="105">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C55" s="77" t="s">
-        <v>263</v>
-      </c>
-      <c r="D55" s="78" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" s="79" t="s">
-        <v>86</v>
+        <v>396</v>
+      </c>
+      <c r="D55" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="E55" s="78" t="s">
+        <v>387</v>
       </c>
       <c r="F55" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G55" s="79" t="s">
-        <v>131</v>
-      </c>
-      <c r="H55" s="96" t="s">
-        <v>188</v>
+        <v>231</v>
+      </c>
+      <c r="G55" s="78" t="s">
+        <v>381</v>
+      </c>
+      <c r="H55" s="95" t="s">
+        <v>180</v>
       </c>
       <c r="I55" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J55" s="78" t="s">
-        <v>319</v>
-      </c>
-      <c r="K55" s="79" t="s">
-        <v>231</v>
+        <v>397</v>
+      </c>
+      <c r="K55" s="72" t="s">
+        <v>236</v>
       </c>
       <c r="L55" s="78">
         <v>1</v>
       </c>
-      <c r="M55" s="72">
+      <c r="M55" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N55" s="72">
-        <v>21</v>
-      </c>
-      <c r="O55" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P55" s="72">
-        <v>0.45629999999999998</v>
-      </c>
-      <c r="Q55" s="72">
-        <f t="shared" ref="Q55" si="36">N55*P55</f>
-        <v>9.5823</v>
-      </c>
-      <c r="R55" s="72"/>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N55" s="39">
+        <v>25</v>
+      </c>
+      <c r="O55" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P55" s="39">
+        <v>0.2044</v>
+      </c>
+      <c r="Q55" s="39">
+        <f>P55*N55</f>
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="R55" s="39"/>
+    </row>
+    <row r="56" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
-      <c r="B56" s="106">
+      <c r="B56" s="105">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C56" s="55" t="s">
-        <v>263</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="F56" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G56" s="38" t="s">
-        <v>373</v>
-      </c>
-      <c r="H56" s="99" t="s">
-        <v>365</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J56" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="K56" s="38" t="s">
-        <v>372</v>
-      </c>
-      <c r="L56" s="37">
+      <c r="C56" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" s="78" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G56" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="H56" s="95" t="s">
+        <v>171</v>
+      </c>
+      <c r="I56" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J56" s="78" t="s">
+        <v>296</v>
+      </c>
+      <c r="K56" s="79" t="s">
+        <v>213</v>
+      </c>
+      <c r="L56" s="78">
         <v>1</v>
       </c>
-      <c r="M56" s="39">
+      <c r="M56" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N56" s="39">
-        <v>25</v>
-      </c>
-      <c r="O56" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P56" s="39">
-        <v>0.1012</v>
-      </c>
-      <c r="Q56" s="39">
-        <f t="shared" ref="Q56:Q57" si="37">P56*N56</f>
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="R56" s="68"/>
-    </row>
-    <row r="57" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="N56" s="72">
+        <v>21</v>
+      </c>
+      <c r="O56" s="80" t="s">
+        <v>263</v>
+      </c>
+      <c r="P56" s="72">
+        <v>0.45629999999999998</v>
+      </c>
+      <c r="Q56" s="72">
+        <f t="shared" ref="Q56" si="36">N56*P56</f>
+        <v>9.5823</v>
+      </c>
+      <c r="R56" s="72"/>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="B57" s="111">
+      <c r="B57" s="105">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="77" t="s">
-        <v>263</v>
-      </c>
-      <c r="D57" s="78" t="s">
-        <v>447</v>
-      </c>
-      <c r="E57" s="78" t="s">
-        <v>495</v>
-      </c>
-      <c r="F57" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G57" s="78" t="s">
-        <v>456</v>
-      </c>
-      <c r="H57" s="78" t="s">
-        <v>496</v>
-      </c>
-      <c r="I57" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J57" s="78" t="s">
-        <v>497</v>
-      </c>
-      <c r="K57" s="78" t="s">
-        <v>498</v>
-      </c>
-      <c r="L57" s="78">
+      <c r="C57" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="D57" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" s="38" t="s">
+        <v>347</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="G57" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="H57" s="98" t="s">
+        <v>338</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J57" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="K57" s="38" t="s">
+        <v>345</v>
+      </c>
+      <c r="L57" s="37">
         <v>1</v>
       </c>
       <c r="M57" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N57" s="78">
+      <c r="N57" s="39">
+        <v>25</v>
+      </c>
+      <c r="O57" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P57" s="39">
+        <v>0.1012</v>
+      </c>
+      <c r="Q57" s="39">
+        <f t="shared" ref="Q57:Q58" si="37">P57*N57</f>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="R57" s="68"/>
+    </row>
+    <row r="58" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="107">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C58" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="D58" s="78" t="s">
+        <v>418</v>
+      </c>
+      <c r="E58" s="78" t="s">
+        <v>466</v>
+      </c>
+      <c r="F58" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G58" s="78" t="s">
+        <v>427</v>
+      </c>
+      <c r="H58" s="78" t="s">
+        <v>467</v>
+      </c>
+      <c r="I58" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J58" s="78" t="s">
+        <v>468</v>
+      </c>
+      <c r="K58" s="78" t="s">
+        <v>469</v>
+      </c>
+      <c r="L58" s="78">
+        <v>1</v>
+      </c>
+      <c r="M58" s="39">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N58" s="78">
         <v>30</v>
       </c>
-      <c r="O57" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P57" s="112">
+      <c r="O58" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P58" s="108">
         <v>3.9199999999999999E-2</v>
       </c>
-      <c r="Q57" s="112">
+      <c r="Q58" s="108">
         <f t="shared" si="37"/>
         <v>1.1759999999999999</v>
       </c>
-      <c r="R57" s="78"/>
-    </row>
-    <row r="58" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="106">
+      <c r="R58" s="78"/>
+    </row>
+    <row r="59" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="105">
         <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="C58" s="77" t="s">
-        <v>267</v>
-      </c>
-      <c r="D58" s="78" t="s">
-        <v>28</v>
-      </c>
-      <c r="E58" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="F58" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G58" s="79" t="s">
-        <v>132</v>
-      </c>
-      <c r="H58" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="I58" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J58" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K58" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L58" s="78">
+        <v>50</v>
+      </c>
+      <c r="C59" s="77" t="s">
+        <v>244</v>
+      </c>
+      <c r="D59" s="78" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="F59" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G59" s="79" t="s">
+        <v>121</v>
+      </c>
+      <c r="H59" s="95" t="s">
+        <v>181</v>
+      </c>
+      <c r="I59" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J59" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="K59" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="L59" s="78">
         <v>1</v>
       </c>
-      <c r="M58" s="72">
+      <c r="M59" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N58" s="72">
+      <c r="N59" s="72">
         <v>30</v>
       </c>
-      <c r="O58" s="80" t="s">
-        <v>320</v>
-      </c>
-      <c r="P58" s="72">
+      <c r="O59" s="80" t="s">
+        <v>297</v>
+      </c>
+      <c r="P59" s="72">
         <v>0.156</v>
       </c>
-      <c r="Q58" s="72">
-        <f t="shared" ref="Q58" si="38">N58*P58</f>
+      <c r="Q59" s="72">
+        <f t="shared" ref="Q59" si="38">N59*P59</f>
         <v>4.68</v>
       </c>
-      <c r="R58" s="72"/>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="106">
+      <c r="R59" s="72"/>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="105">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="C59" s="55" t="s">
-        <v>384</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="E59" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>254</v>
-      </c>
-      <c r="G59" s="38" t="s">
-        <v>387</v>
-      </c>
-      <c r="H59" s="99" t="s">
-        <v>388</v>
-      </c>
-      <c r="I59" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J59" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K59" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L59" s="37">
+        <v>51</v>
+      </c>
+      <c r="C60" s="55" t="s">
+        <v>356</v>
+      </c>
+      <c r="D60" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="E60" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="F60" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="G60" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="H60" s="98" t="s">
+        <v>360</v>
+      </c>
+      <c r="I60" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J60" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="K60" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="L60" s="37">
         <v>1</v>
       </c>
-      <c r="M59" s="39">
+      <c r="M60" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N59" s="39">
+      <c r="N60" s="39">
         <v>20</v>
       </c>
-      <c r="O59" s="57" t="s">
-        <v>348</v>
-      </c>
-      <c r="P59" s="39">
+      <c r="O60" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="P60" s="39">
         <v>0.435</v>
       </c>
-      <c r="Q59" s="39">
-        <f t="shared" ref="Q59" si="39">P59*N59</f>
+      <c r="Q60" s="39">
+        <f t="shared" ref="Q60" si="39">P60*N60</f>
         <v>8.6999999999999993</v>
       </c>
-      <c r="R59" s="69" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="106">
+      <c r="R60" s="69" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="105">
         <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="C60" s="77" t="s">
-        <v>265</v>
-      </c>
-      <c r="D60" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="E60" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="F60" s="78" t="s">
-        <v>254</v>
-      </c>
-      <c r="G60" s="79" t="s">
-        <v>133</v>
-      </c>
-      <c r="H60" s="96" t="s">
-        <v>199</v>
-      </c>
-      <c r="I60" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J60" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K60" s="79" t="s">
-        <v>259</v>
-      </c>
-      <c r="L60" s="78">
+        <v>52</v>
+      </c>
+      <c r="C61" s="77" t="s">
+        <v>242</v>
+      </c>
+      <c r="D61" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="F61" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G61" s="79" t="s">
+        <v>122</v>
+      </c>
+      <c r="H61" s="95" t="s">
+        <v>182</v>
+      </c>
+      <c r="I61" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J61" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="K61" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="L61" s="78">
         <v>2</v>
       </c>
-      <c r="M60" s="72">
+      <c r="M61" s="72">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N60" s="72">
+      <c r="N61" s="72">
         <v>42</v>
       </c>
-      <c r="O60" s="80" t="s">
-        <v>427</v>
-      </c>
-      <c r="P60" s="72">
+      <c r="O61" s="80" t="s">
+        <v>399</v>
+      </c>
+      <c r="P61" s="72">
         <v>1.58</v>
       </c>
-      <c r="Q60" s="72">
-        <f t="shared" ref="Q60" si="40">N60*P60</f>
+      <c r="Q61" s="72">
+        <f t="shared" ref="Q61" si="40">N61*P61</f>
         <v>66.36</v>
       </c>
-      <c r="R60" s="72"/>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="106">
+      <c r="R61" s="72"/>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="105">
         <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="C61" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="D61" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="E61" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="F61" s="74" t="s">
-        <v>254</v>
-      </c>
-      <c r="G61" s="74" t="s">
-        <v>134</v>
-      </c>
-      <c r="H61" s="103" t="s">
-        <v>259</v>
-      </c>
-      <c r="I61" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="J61" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="K61" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="L61" s="74">
+        <v>53</v>
+      </c>
+      <c r="C62" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="D62" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" s="74" t="s">
+        <v>231</v>
+      </c>
+      <c r="G62" s="74" t="s">
+        <v>123</v>
+      </c>
+      <c r="H62" s="102" t="s">
+        <v>236</v>
+      </c>
+      <c r="I62" s="74" t="s">
+        <v>236</v>
+      </c>
+      <c r="J62" s="74" t="s">
+        <v>236</v>
+      </c>
+      <c r="K62" s="75" t="s">
+        <v>236</v>
+      </c>
+      <c r="L62" s="74">
         <v>4</v>
       </c>
-      <c r="M61" s="58">
+      <c r="M62" s="58">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N61" s="58">
-        <f t="shared" ref="N61" si="41">M61+(M61*0.1)</f>
+      <c r="N62" s="58">
+        <f t="shared" ref="N62" si="41">M62+(M62*0.1)</f>
         <v>88</v>
       </c>
-      <c r="O61" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="P61" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q61" s="58" t="s">
-        <v>259</v>
-      </c>
-      <c r="R61" s="58" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="36" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="106">
+      <c r="O62" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="P62" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q62" s="58" t="s">
+        <v>236</v>
+      </c>
+      <c r="R62" s="58" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="36" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="105">
         <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="C62" s="55" t="s">
-        <v>268</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>406</v>
-      </c>
-      <c r="E62" s="37" t="s">
-        <v>416</v>
-      </c>
-      <c r="F62" s="37" t="s">
-        <v>426</v>
-      </c>
-      <c r="G62" s="37" t="s">
-        <v>322</v>
-      </c>
-      <c r="H62" s="99" t="s">
-        <v>417</v>
-      </c>
-      <c r="I62" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J62" s="37" t="s">
-        <v>323</v>
-      </c>
-      <c r="K62" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="L62" s="37">
+        <v>54</v>
+      </c>
+      <c r="C63" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>388</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>398</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>299</v>
+      </c>
+      <c r="H63" s="98" t="s">
+        <v>389</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J63" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="K63" s="38" t="s">
+        <v>236</v>
+      </c>
+      <c r="L63" s="37">
         <v>4</v>
       </c>
-      <c r="M62" s="39">
+      <c r="M63" s="39">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N62" s="39">
+      <c r="N63" s="39">
         <v>85</v>
       </c>
-      <c r="O62" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P62" s="39">
+      <c r="O63" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P63" s="39">
         <v>0.21740000000000001</v>
       </c>
-      <c r="Q62" s="39">
-        <f t="shared" ref="Q62" si="42">P62*N62</f>
+      <c r="Q63" s="39">
+        <f t="shared" ref="Q63:Q64" si="42">P63*N63</f>
         <v>18.478999999999999</v>
       </c>
-      <c r="R62" s="39"/>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="106">
+      <c r="R63" s="39"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="107">
         <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="C63" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D63" s="78" t="s">
-        <v>31</v>
-      </c>
-      <c r="E63" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="F63" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G63" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="H63" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="I63" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J63" s="78" t="s">
-        <v>324</v>
-      </c>
-      <c r="K63" s="79" t="s">
-        <v>233</v>
-      </c>
-      <c r="L63" s="78">
+        <v>55</v>
+      </c>
+      <c r="C64" s="77" t="s">
+        <v>505</v>
+      </c>
+      <c r="D64" s="78" t="s">
+        <v>497</v>
+      </c>
+      <c r="E64" s="78" t="s">
+        <v>506</v>
+      </c>
+      <c r="F64" s="78" t="s">
+        <v>507</v>
+      </c>
+      <c r="G64" s="78" t="s">
+        <v>488</v>
+      </c>
+      <c r="H64" s="78" t="s">
+        <v>485</v>
+      </c>
+      <c r="I64" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J64" s="78" t="s">
+        <v>508</v>
+      </c>
+      <c r="K64" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="L64" s="78">
+        <v>1</v>
+      </c>
+      <c r="M64" s="78">
+        <f t="shared" ref="M64" si="43">L64*5</f>
+        <v>5</v>
+      </c>
+      <c r="N64" s="78">
+        <v>6</v>
+      </c>
+      <c r="O64" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P64" s="108">
+        <v>1.6523000000000001</v>
+      </c>
+      <c r="Q64" s="108">
+        <f t="shared" si="42"/>
+        <v>9.9138000000000002</v>
+      </c>
+      <c r="R64" s="78"/>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="105">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="C65" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="D65" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="F65" s="78" t="s">
+        <v>124</v>
+      </c>
+      <c r="G65" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="H65" s="95" t="s">
+        <v>167</v>
+      </c>
+      <c r="I65" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J65" s="78" t="s">
+        <v>301</v>
+      </c>
+      <c r="K65" s="79" t="s">
+        <v>215</v>
+      </c>
+      <c r="L65" s="78">
         <v>2</v>
       </c>
-      <c r="M63" s="72">
+      <c r="M65" s="72">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N63" s="72">
+      <c r="N65" s="72">
         <v>100</v>
       </c>
-      <c r="O63" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P63" s="72">
+      <c r="O65" s="80" t="s">
+        <v>263</v>
+      </c>
+      <c r="P65" s="72">
         <v>1E-3</v>
       </c>
-      <c r="Q63" s="72">
-        <f t="shared" ref="Q63" si="43">N63*P63</f>
+      <c r="Q65" s="72">
+        <f t="shared" ref="Q65" si="44">N65*P65</f>
         <v>0.1</v>
       </c>
-      <c r="R63" s="72"/>
-    </row>
-    <row r="64" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="106">
+      <c r="R65" s="72"/>
+    </row>
+    <row r="66" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="105">
         <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="C64" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E64" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G64" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="H64" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="I64" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J64" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="K64" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="L64" s="37">
+        <v>57</v>
+      </c>
+      <c r="C66" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G66" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="H66" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="I66" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J66" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="K66" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="L66" s="37">
         <v>1</v>
       </c>
-      <c r="M64" s="39">
+      <c r="M66" s="39">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N64" s="39">
+      <c r="N66" s="39">
         <v>100</v>
       </c>
-      <c r="O64" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P64" s="39">
+      <c r="O66" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P66" s="39">
         <v>1.4E-3</v>
       </c>
-      <c r="Q64" s="39">
-        <f t="shared" ref="Q64" si="44">P64*N64</f>
+      <c r="Q66" s="39">
+        <f t="shared" ref="Q66" si="45">P66*N66</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R64" s="39"/>
-    </row>
-    <row r="65" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="106">
+      <c r="R66" s="39"/>
+    </row>
+    <row r="67" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="105">
         <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="C65" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D65" s="78" t="s">
-        <v>33</v>
-      </c>
-      <c r="E65" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="F65" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G65" s="79" t="s">
-        <v>163</v>
-      </c>
-      <c r="H65" s="96" t="s">
-        <v>200</v>
-      </c>
-      <c r="I65" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J65" s="78" t="s">
-        <v>326</v>
-      </c>
-      <c r="K65" s="79" t="s">
-        <v>235</v>
-      </c>
-      <c r="L65" s="78">
+        <v>58</v>
+      </c>
+      <c r="C67" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="D67" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="F67" s="78" t="s">
+        <v>124</v>
+      </c>
+      <c r="G67" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="H67" s="95" t="s">
+        <v>183</v>
+      </c>
+      <c r="I67" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J67" s="78" t="s">
+        <v>303</v>
+      </c>
+      <c r="K67" s="79" t="s">
+        <v>217</v>
+      </c>
+      <c r="L67" s="78">
         <v>1</v>
       </c>
-      <c r="M65" s="72">
+      <c r="M67" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N65" s="72">
+      <c r="N67" s="72">
         <v>100</v>
       </c>
-      <c r="O65" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P65" s="72">
+      <c r="O67" s="80" t="s">
+        <v>263</v>
+      </c>
+      <c r="P67" s="72">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q65" s="72">
-        <f t="shared" ref="Q65" si="45">N65*P65</f>
+      <c r="Q67" s="72">
+        <f t="shared" ref="Q67" si="46">N67*P67</f>
         <v>0.16</v>
       </c>
-      <c r="R65" s="72"/>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="106">
+      <c r="R67" s="72"/>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="105">
         <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="C66" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D66" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="E66" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G66" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="H66" s="99" t="s">
-        <v>184</v>
-      </c>
-      <c r="I66" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J66" s="37" t="s">
-        <v>327</v>
-      </c>
-      <c r="K66" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="L66" s="37">
+        <v>59</v>
+      </c>
+      <c r="C68" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E68" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="F68" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G68" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="H68" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="I68" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J68" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="K68" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="L68" s="37">
         <v>2</v>
       </c>
-      <c r="M66" s="39">
+      <c r="M68" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N66" s="39">
+      <c r="N68" s="39">
         <v>100</v>
       </c>
-      <c r="O66" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P66" s="39">
+      <c r="O68" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P68" s="39">
         <v>1.4E-3</v>
       </c>
-      <c r="Q66" s="39">
-        <f t="shared" ref="Q66" si="46">P66*N66</f>
+      <c r="Q68" s="39">
+        <f t="shared" ref="Q68" si="47">P68*N68</f>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R66" s="39"/>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="106">
+      <c r="R68" s="39"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="105">
         <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="C67" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D67" s="78" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="79" t="s">
-        <v>94</v>
-      </c>
-      <c r="F67" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G67" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="H67" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="I67" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J67" s="78" t="s">
-        <v>328</v>
-      </c>
-      <c r="K67" s="79" t="s">
-        <v>237</v>
-      </c>
-      <c r="L67" s="78">
+        <v>60</v>
+      </c>
+      <c r="C69" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="D69" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="F69" s="78" t="s">
+        <v>124</v>
+      </c>
+      <c r="G69" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="H69" s="95" t="s">
+        <v>167</v>
+      </c>
+      <c r="I69" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J69" s="78" t="s">
+        <v>305</v>
+      </c>
+      <c r="K69" s="79" t="s">
+        <v>219</v>
+      </c>
+      <c r="L69" s="78">
         <v>4</v>
       </c>
-      <c r="M67" s="72">
+      <c r="M69" s="72">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="N67" s="72">
+      <c r="N69" s="72">
         <v>100</v>
       </c>
-      <c r="O67" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P67" s="72">
+      <c r="O69" s="80" t="s">
+        <v>263</v>
+      </c>
+      <c r="P69" s="72">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q67" s="72">
-        <f t="shared" ref="Q67" si="47">N67*P67</f>
+      <c r="Q69" s="72">
+        <f t="shared" ref="Q69" si="48">N69*P69</f>
         <v>0.13</v>
       </c>
-      <c r="R67" s="72"/>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="111">
+      <c r="R69" s="72"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="107">
         <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="C68" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D68" s="78" t="s">
-        <v>448</v>
-      </c>
-      <c r="E68" s="78" t="s">
-        <v>499</v>
-      </c>
-      <c r="F68" s="78" t="s">
-        <v>500</v>
-      </c>
-      <c r="G68" s="78" t="s">
-        <v>457</v>
-      </c>
-      <c r="H68" s="78" t="s">
-        <v>184</v>
-      </c>
-      <c r="I68" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J68" s="78" t="s">
-        <v>515</v>
-      </c>
-      <c r="K68" s="78" t="s">
-        <v>501</v>
-      </c>
-      <c r="L68" s="78">
+        <v>61</v>
+      </c>
+      <c r="C70" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="D70" s="78" t="s">
+        <v>419</v>
+      </c>
+      <c r="E70" s="78" t="s">
+        <v>470</v>
+      </c>
+      <c r="F70" s="78" t="s">
+        <v>471</v>
+      </c>
+      <c r="G70" s="78" t="s">
+        <v>428</v>
+      </c>
+      <c r="H70" s="78" t="s">
+        <v>167</v>
+      </c>
+      <c r="I70" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="J70" s="78" t="s">
+        <v>486</v>
+      </c>
+      <c r="K70" s="78" t="s">
+        <v>472</v>
+      </c>
+      <c r="L70" s="78">
         <v>1</v>
       </c>
-      <c r="M68" s="72">
+      <c r="M70" s="72">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="N68" s="78">
+      <c r="N70" s="78">
         <v>100</v>
       </c>
-      <c r="O68" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P68" s="112">
+      <c r="O70" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P70" s="108">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="Q68" s="112">
-        <f t="shared" ref="Q68" si="48">P68*N68</f>
+      <c r="Q70" s="108">
+        <f t="shared" ref="Q70" si="49">P70*N70</f>
         <v>0.09</v>
       </c>
-      <c r="R68" s="78"/>
-    </row>
-    <row r="69" spans="1:18" ht="24" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="106">
+      <c r="R70" s="78"/>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="105">
+        <f>ROW(B71) - ROW($B$9)</f>
+        <v>62</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D71" s="37" t="s">
+        <v>498</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>509</v>
+      </c>
+      <c r="F71" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>489</v>
+      </c>
+      <c r="H71" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J71" s="37" t="s">
+        <v>510</v>
+      </c>
+      <c r="K71" s="37" t="s">
+        <v>511</v>
+      </c>
+      <c r="L71" s="37">
+        <v>1</v>
+      </c>
+      <c r="M71" s="37">
+        <f>L71*5</f>
+        <v>5</v>
+      </c>
+      <c r="N71" s="37">
+        <v>20</v>
+      </c>
+      <c r="O71" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="P71" s="106">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="Q71" s="106">
+        <f>P71*N71</f>
+        <v>0.52</v>
+      </c>
+      <c r="R71" s="37"/>
+    </row>
+    <row r="72" spans="1:18" ht="24" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="105">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="C69" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D69" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="E69" s="78" t="s">
-        <v>395</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>396</v>
-      </c>
-      <c r="H69" s="99" t="s">
-        <v>201</v>
-      </c>
-      <c r="I69" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J69" s="37" t="s">
-        <v>397</v>
-      </c>
-      <c r="K69" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="L69" s="37">
+        <v>63</v>
+      </c>
+      <c r="C72" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D72" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="E72" s="78" t="s">
+        <v>367</v>
+      </c>
+      <c r="F72" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="G72" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="H72" s="98" t="s">
+        <v>184</v>
+      </c>
+      <c r="I72" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J72" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="L72" s="37">
         <v>2</v>
       </c>
-      <c r="M69" s="39">
+      <c r="M72" s="39">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N69" s="39">
+      <c r="N72" s="39">
         <v>45</v>
       </c>
-      <c r="O69" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="P69" s="39">
+      <c r="O72" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P72" s="39">
         <v>2.9100000000000001E-2</v>
       </c>
-      <c r="Q69" s="39">
-        <f t="shared" ref="Q69" si="49">P69*N69</f>
+      <c r="Q72" s="39">
+        <f t="shared" ref="Q72" si="50">P72*N72</f>
         <v>1.3095000000000001</v>
       </c>
-      <c r="R69" s="39"/>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="106">
+      <c r="R72" s="39"/>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="105">
         <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="C70" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D70" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="E70" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="F70" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="H70" s="99" t="s">
-        <v>203</v>
-      </c>
-      <c r="I70" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J70" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="K70" s="39" t="s">
-        <v>356</v>
-      </c>
-      <c r="L70" s="37">
+        <v>64</v>
+      </c>
+      <c r="C73" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D73" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="F73" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G73" s="37" t="s">
+        <v>327</v>
+      </c>
+      <c r="H73" s="98" t="s">
+        <v>186</v>
+      </c>
+      <c r="I73" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J73" s="37" t="s">
+        <v>328</v>
+      </c>
+      <c r="K73" s="39" t="s">
+        <v>329</v>
+      </c>
+      <c r="L73" s="37">
         <v>8</v>
       </c>
-      <c r="M70" s="37">
+      <c r="M73" s="37">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="N70" s="72">
-        <v>100</v>
-      </c>
-      <c r="O70" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="P70" s="37">
+      <c r="N73" s="72">
+        <v>200</v>
+      </c>
+      <c r="O73" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="P73" s="37">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q70" s="37">
-        <f t="shared" ref="Q70" si="50">N70*P70</f>
-        <v>0.11</v>
-      </c>
-      <c r="R70" s="68"/>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="106">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="C71" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D71" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="E71" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="F71" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G71" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="H71" s="99" t="s">
-        <v>202</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J71" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K71" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="L71" s="37">
-        <v>1</v>
-      </c>
-      <c r="M71" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N71" s="39">
-        <v>30</v>
-      </c>
-      <c r="O71" s="57" t="s">
-        <v>320</v>
-      </c>
-      <c r="P71" s="39">
-        <v>1.8589999999999999E-2</v>
-      </c>
-      <c r="Q71" s="39">
-        <f t="shared" ref="Q71" si="51">P71*N71</f>
-        <v>0.55769999999999997</v>
-      </c>
-      <c r="R71" s="39"/>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="106">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="C72" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D72" s="78" t="s">
-        <v>37</v>
-      </c>
-      <c r="E72" s="79" t="s">
-        <v>97</v>
-      </c>
-      <c r="F72" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G72" s="79" t="s">
-        <v>168</v>
-      </c>
-      <c r="H72" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="I72" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J72" s="78" t="s">
-        <v>330</v>
-      </c>
-      <c r="K72" s="79" t="s">
-        <v>240</v>
-      </c>
-      <c r="L72" s="78">
-        <v>1</v>
-      </c>
-      <c r="M72" s="72">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N72" s="72">
-        <v>100</v>
-      </c>
-      <c r="O72" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P72" s="72">
-        <v>1.4E-3</v>
-      </c>
-      <c r="Q72" s="72">
-        <f t="shared" ref="Q72" si="52">N72*P72</f>
-        <v>0.13999999999999999</v>
-      </c>
-      <c r="R72" s="72"/>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="106">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="C73" s="55" t="s">
-        <v>269</v>
-      </c>
-      <c r="D73" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E73" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G73" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="H73" s="99" t="s">
-        <v>202</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="J73" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K73" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="L73" s="37">
-        <v>1</v>
-      </c>
-      <c r="M73" s="39">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N73" s="39">
-        <v>50</v>
-      </c>
-      <c r="O73" s="57" t="s">
-        <v>320</v>
-      </c>
-      <c r="P73" s="39">
-        <v>4.6699999999999997E-3</v>
-      </c>
-      <c r="Q73" s="39">
-        <f t="shared" ref="Q73" si="53">P73*N73</f>
-        <v>0.23349999999999999</v>
-      </c>
-      <c r="R73" s="39"/>
+      <c r="Q73" s="37">
+        <f t="shared" ref="Q73" si="51">N73*P73</f>
+        <v>0.22</v>
+      </c>
+      <c r="R73" s="68"/>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="106">
+      <c r="B74" s="105">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="77" t="s">
-        <v>269</v>
+      <c r="C74" s="55" t="s">
+        <v>246</v>
       </c>
       <c r="D74" s="78" t="s">
-        <v>39</v>
-      </c>
-      <c r="E74" s="79" t="s">
-        <v>99</v>
+        <v>499</v>
+      </c>
+      <c r="E74" s="78" t="s">
+        <v>512</v>
       </c>
       <c r="F74" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G74" s="79" t="s">
-        <v>170</v>
-      </c>
-      <c r="H74" s="96" t="s">
-        <v>184</v>
+        <v>124</v>
+      </c>
+      <c r="G74" s="78" t="s">
+        <v>490</v>
+      </c>
+      <c r="H74" s="78" t="s">
+        <v>167</v>
       </c>
       <c r="I74" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J74" s="78" t="s">
-        <v>331</v>
-      </c>
-      <c r="K74" s="79" t="s">
-        <v>242</v>
+        <v>236</v>
+      </c>
+      <c r="K74" s="78" t="s">
+        <v>513</v>
       </c>
       <c r="L74" s="78">
-        <v>1</v>
-      </c>
-      <c r="M74" s="72">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N74" s="72">
-        <v>100</v>
-      </c>
-      <c r="O74" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P74" s="72">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q74" s="72">
-        <f t="shared" ref="Q74" si="54">N74*P74</f>
-        <v>0.12</v>
-      </c>
-      <c r="R74" s="72"/>
+        <v>2</v>
+      </c>
+      <c r="M74" s="78">
+        <f t="shared" ref="M74" si="52">L74*5</f>
+        <v>10</v>
+      </c>
+      <c r="N74" s="78">
+        <v>11</v>
+      </c>
+      <c r="O74" s="109" t="s">
+        <v>519</v>
+      </c>
+      <c r="P74" s="108">
+        <v>4.9800000000000001E-3</v>
+      </c>
+      <c r="Q74" s="108">
+        <f t="shared" ref="Q74" si="53">P74*N74</f>
+        <v>5.4780000000000002E-2</v>
+      </c>
+      <c r="R74" s="39"/>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="B75" s="106">
+      <c r="B75" s="105">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="C75" s="77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D75" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="E75" s="79" t="s">
-        <v>100</v>
-      </c>
-      <c r="F75" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G75" s="79" t="s">
-        <v>171</v>
-      </c>
-      <c r="H75" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="I75" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J75" s="78" t="s">
-        <v>332</v>
-      </c>
-      <c r="K75" s="79" t="s">
-        <v>243</v>
-      </c>
-      <c r="L75" s="78">
+      <c r="C75" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D75" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>514</v>
+      </c>
+      <c r="F75" s="37" t="s">
+        <v>124</v>
+      </c>
+      <c r="G75" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="H75" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="I75" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J75" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="K75" s="37" t="s">
+        <v>515</v>
+      </c>
+      <c r="L75" s="37">
         <v>1</v>
       </c>
-      <c r="M75" s="72">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N75" s="72">
-        <v>100</v>
-      </c>
-      <c r="O75" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="P75" s="72">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q75" s="72">
-        <f t="shared" ref="Q75" si="55">N75*P75</f>
-        <v>0.21</v>
+      <c r="M75" s="37">
+        <f>L75*5</f>
+        <v>5</v>
+      </c>
+      <c r="N75" s="37">
+        <v>6</v>
+      </c>
+      <c r="O75" s="70" t="s">
+        <v>297</v>
+      </c>
+      <c r="P75" s="106">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="Q75" s="106">
+        <f>P75*N75</f>
+        <v>2.52E-2</v>
       </c>
       <c r="R75" s="72"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
-      <c r="B76" s="106">
+      <c r="B76" s="105">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="C76" s="55" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G76" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="H76" s="99" t="s">
-        <v>184</v>
+        <v>156</v>
+      </c>
+      <c r="H76" s="98" t="s">
+        <v>185</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J76" s="37" t="s">
-        <v>333</v>
+        <v>236</v>
       </c>
       <c r="K76" s="38" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="L76" s="37">
         <v>1</v>
@@ -6797,52 +6797,52 @@
         <v>20</v>
       </c>
       <c r="N76" s="39">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O76" s="57" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="P76" s="39">
-        <v>1.6000000000000001E-3</v>
+        <v>4.6699999999999997E-3</v>
       </c>
       <c r="Q76" s="39">
-        <f t="shared" ref="Q76" si="56">P76*N76</f>
-        <v>0.16</v>
+        <f t="shared" ref="Q76" si="54">P76*N76</f>
+        <v>0.23349999999999999</v>
       </c>
       <c r="R76" s="39"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="106">
+      <c r="B77" s="105">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="C77" s="77" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D77" s="78" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E77" s="79" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F77" s="78" t="s">
-        <v>135</v>
-      </c>
-      <c r="G77" s="85" t="s">
-        <v>173</v>
-      </c>
-      <c r="H77" s="96" t="s">
-        <v>184</v>
+        <v>124</v>
+      </c>
+      <c r="G77" s="84" t="s">
+        <v>157</v>
+      </c>
+      <c r="H77" s="95" t="s">
+        <v>167</v>
       </c>
       <c r="I77" s="78" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="J77" s="78" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="K77" s="79" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="L77" s="78">
         <v>1</v>
@@ -6855,49 +6855,49 @@
         <v>50</v>
       </c>
       <c r="O77" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P77" s="72">
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q77" s="72">
-        <f t="shared" ref="Q77" si="57">N77*P77</f>
+        <f t="shared" ref="Q77" si="55">N77*P77</f>
         <v>0.34499999999999997</v>
       </c>
       <c r="R77" s="72"/>
     </row>
     <row r="78" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
-      <c r="B78" s="106">
+      <c r="B78" s="105">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C78" s="55" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="E78" s="38" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F78" s="37" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G78" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="H78" s="99" t="s">
-        <v>184</v>
+        <v>158</v>
+      </c>
+      <c r="H78" s="98" t="s">
+        <v>167</v>
       </c>
       <c r="I78" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J78" s="37" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="K78" s="38" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="L78" s="37">
         <v>2</v>
@@ -6910,49 +6910,49 @@
         <v>100</v>
       </c>
       <c r="O78" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P78" s="39">
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q78" s="39">
-        <f t="shared" ref="Q78" si="58">P78*N78</f>
+        <f t="shared" ref="Q78" si="56">P78*N78</f>
         <v>0.11</v>
       </c>
       <c r="R78" s="39"/>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
-      <c r="B79" s="106">
+      <c r="B79" s="105">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="C79" s="55" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E79" s="38" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F79" s="37" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G79" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="H79" s="99" t="s">
-        <v>184</v>
+        <v>159</v>
+      </c>
+      <c r="H79" s="98" t="s">
+        <v>167</v>
       </c>
       <c r="I79" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J79" s="37" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="K79" s="38" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="L79" s="37">
         <v>2</v>
@@ -6965,47 +6965,47 @@
         <v>100</v>
       </c>
       <c r="O79" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P79" s="39">
         <v>1.5E-3</v>
       </c>
       <c r="Q79" s="39">
-        <f t="shared" ref="Q79" si="59">P79*N79</f>
+        <f t="shared" ref="Q79" si="57">P79*N79</f>
         <v>0.15</v>
       </c>
       <c r="R79" s="39"/>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
-      <c r="B80" s="106">
+      <c r="B80" s="105">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C80" s="77" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D80" s="82" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="E80" s="79" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F80" s="78" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G80" s="79" t="s">
-        <v>166</v>
-      </c>
-      <c r="H80" s="96" t="s">
-        <v>184</v>
+        <v>155</v>
+      </c>
+      <c r="H80" s="95" t="s">
+        <v>167</v>
       </c>
       <c r="I80" s="78"/>
       <c r="J80" s="78" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="K80" s="79" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="L80" s="78">
         <v>1</v>
@@ -7018,7 +7018,7 @@
         <v>100</v>
       </c>
       <c r="O80" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P80" s="72">
         <v>1.5E-3</v>
@@ -7031,36 +7031,36 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="B81" s="106">
+      <c r="B81" s="105">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="C81" s="55" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D81" s="37" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E81" s="38" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G81" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="H81" s="99" t="s">
-        <v>184</v>
+        <v>160</v>
+      </c>
+      <c r="H81" s="98" t="s">
+        <v>167</v>
       </c>
       <c r="I81" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J81" s="37" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="K81" s="38" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="L81" s="37">
         <v>2</v>
@@ -7073,49 +7073,49 @@
         <v>100</v>
       </c>
       <c r="O81" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P81" s="39">
         <v>1.5E-3</v>
       </c>
       <c r="Q81" s="39">
-        <f t="shared" ref="Q81" si="60">P81*N81</f>
+        <f t="shared" ref="Q81" si="58">P81*N81</f>
         <v>0.15</v>
       </c>
       <c r="R81" s="39"/>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
-      <c r="B82" s="106">
+      <c r="B82" s="105">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="C82" s="77" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D82" s="78" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E82" s="79" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F82" s="78" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G82" s="79" t="s">
-        <v>177</v>
-      </c>
-      <c r="H82" s="96" t="s">
-        <v>202</v>
+        <v>161</v>
+      </c>
+      <c r="H82" s="95" t="s">
+        <v>185</v>
       </c>
       <c r="I82" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J82" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="K82" s="79" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="L82" s="78">
         <v>1</v>
@@ -7128,104 +7128,104 @@
         <v>25</v>
       </c>
       <c r="O82" s="80" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="P82" s="72">
         <v>8.5400000000000004E-2</v>
       </c>
       <c r="Q82" s="72">
-        <f t="shared" ref="Q82" si="61">N82*P82</f>
+        <f t="shared" ref="Q82" si="59">N82*P82</f>
         <v>2.1350000000000002</v>
       </c>
       <c r="R82" s="72"/>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="B83" s="106">
+      <c r="B83" s="105">
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
       <c r="C83" s="55" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D83" s="37" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E83" s="38" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="F83" s="71" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G83" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="H83" s="99" t="s">
-        <v>203</v>
+        <v>349</v>
+      </c>
+      <c r="H83" s="98" t="s">
+        <v>186</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J83" s="37" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="K83" s="38" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="L83" s="37">
         <v>1</v>
       </c>
       <c r="M83" s="39">
-        <f t="shared" ref="M83:M98" si="62">L83*20</f>
+        <f t="shared" ref="M83:M94" si="60">L83*20</f>
         <v>20</v>
       </c>
       <c r="N83" s="39">
         <v>50</v>
       </c>
       <c r="O83" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P83" s="39">
         <v>3.8E-3</v>
       </c>
       <c r="Q83" s="39">
-        <f t="shared" ref="Q83" si="63">P83*N83</f>
+        <f t="shared" ref="Q83" si="61">P83*N83</f>
         <v>0.19</v>
       </c>
       <c r="R83" s="68"/>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="B84" s="106">
+      <c r="B84" s="105">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C84" s="77" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D84" s="78" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="E84" s="79" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F84" s="78" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G84" s="79" t="s">
-        <v>178</v>
-      </c>
-      <c r="H84" s="96" t="s">
-        <v>184</v>
+        <v>162</v>
+      </c>
+      <c r="H84" s="95" t="s">
+        <v>167</v>
       </c>
       <c r="I84" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J84" s="78" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="K84" s="79" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="L84" s="78">
         <v>6</v>
@@ -7238,173 +7238,173 @@
         <v>200</v>
       </c>
       <c r="O84" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P84" s="72">
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q84" s="72">
-        <f t="shared" ref="Q84" si="64">N84*P84</f>
+        <f t="shared" ref="Q84" si="62">N84*P84</f>
         <v>0.24</v>
       </c>
       <c r="R84" s="68"/>
     </row>
     <row r="85" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
-      <c r="B85" s="106">
+      <c r="B85" s="105">
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E85" s="38" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G85" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="H85" s="99" t="s">
-        <v>203</v>
+        <v>251</v>
+      </c>
+      <c r="H85" s="98" t="s">
+        <v>186</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J85" s="37" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
       <c r="K85" s="38" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="L85" s="37">
         <v>1</v>
       </c>
       <c r="M85" s="39">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N85" s="39">
         <v>100</v>
       </c>
       <c r="O85" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P85" s="39">
         <v>1E-3</v>
       </c>
       <c r="Q85" s="39">
-        <f t="shared" ref="Q85" si="65">P85*N85</f>
+        <f t="shared" ref="Q85" si="63">P85*N85</f>
         <v>0.1</v>
       </c>
       <c r="R85" s="39"/>
     </row>
     <row r="86" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
-      <c r="B86" s="106">
+      <c r="B86" s="105">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="C86" s="77" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="D86" s="78" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E86" s="79" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F86" s="78" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="G86" s="79" t="s">
-        <v>275</v>
-      </c>
-      <c r="H86" s="96" t="s">
-        <v>204</v>
+        <v>252</v>
+      </c>
+      <c r="H86" s="95" t="s">
+        <v>187</v>
       </c>
       <c r="I86" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J86" s="78" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="K86" s="79" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="L86" s="78">
         <v>1</v>
       </c>
       <c r="M86" s="72">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N86" s="72">
         <v>50</v>
       </c>
       <c r="O86" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P86" s="72">
         <v>4.3E-3</v>
       </c>
       <c r="Q86" s="72">
-        <f t="shared" ref="Q86" si="66">N86*P86</f>
+        <f t="shared" ref="Q86" si="64">N86*P86</f>
         <v>0.215</v>
       </c>
       <c r="R86" s="72"/>
     </row>
     <row r="87" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
-      <c r="B87" s="106">
-        <f t="shared" ref="B87:B98" si="67">ROW(B87) - ROW($B$9)</f>
+      <c r="B87" s="105">
+        <f t="shared" ref="B87:B98" si="65">ROW(B87) - ROW($B$9)</f>
         <v>78</v>
       </c>
       <c r="C87" s="77" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="D87" s="78" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E87" s="79" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F87" s="78" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G87" s="78" t="s">
-        <v>137</v>
-      </c>
-      <c r="H87" s="96" t="s">
-        <v>205</v>
+        <v>126</v>
+      </c>
+      <c r="H87" s="95" t="s">
+        <v>188</v>
       </c>
       <c r="I87" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J87" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="K87" s="79" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L87" s="78">
         <v>1</v>
       </c>
       <c r="M87" s="72">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N87" s="72">
-        <f t="shared" ref="N87" si="68">M87+(M87*0.1)</f>
+        <f t="shared" ref="N87" si="66">M87+(M87*0.1)</f>
         <v>22</v>
       </c>
       <c r="O87" s="80" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="P87" s="72">
         <v>1.42</v>
@@ -7416,586 +7416,586 @@
     </row>
     <row r="88" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
-      <c r="B88" s="106">
-        <f t="shared" si="67"/>
+      <c r="B88" s="105">
+        <f t="shared" si="65"/>
         <v>79</v>
       </c>
       <c r="C88" s="55" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E88" s="38" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F88" s="37" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G88" s="38">
         <v>750314597</v>
       </c>
-      <c r="H88" s="99" t="s">
-        <v>206</v>
+      <c r="H88" s="98" t="s">
+        <v>189</v>
       </c>
       <c r="I88" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J88" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="K88" s="38" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L88" s="37">
         <v>1</v>
       </c>
       <c r="M88" s="39">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N88" s="39">
         <v>21</v>
       </c>
       <c r="O88" s="57" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="P88" s="39">
         <v>3.81</v>
       </c>
       <c r="Q88" s="39">
-        <f t="shared" ref="Q88" si="69">P88*N88</f>
+        <f t="shared" ref="Q88" si="67">P88*N88</f>
         <v>80.010000000000005</v>
       </c>
       <c r="R88" s="39"/>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
-      <c r="B89" s="106">
-        <f t="shared" si="67"/>
+      <c r="B89" s="105">
+        <f t="shared" si="65"/>
         <v>80</v>
       </c>
       <c r="C89" s="77" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D89" s="78" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E89" s="79" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F89" s="78" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="G89" s="79" t="s">
-        <v>138</v>
-      </c>
-      <c r="H89" s="96" t="s">
-        <v>207</v>
+        <v>127</v>
+      </c>
+      <c r="H89" s="95" t="s">
+        <v>190</v>
       </c>
       <c r="I89" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J89" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="K89" s="79" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L89" s="78">
         <v>1</v>
       </c>
       <c r="M89" s="72">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N89" s="72">
         <v>21</v>
       </c>
       <c r="O89" s="80" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="P89" s="72">
         <v>2.48</v>
       </c>
       <c r="Q89" s="72">
-        <f t="shared" ref="Q89" si="70">N89*P89</f>
+        <f t="shared" ref="Q89" si="68">N89*P89</f>
         <v>52.08</v>
       </c>
       <c r="R89" s="72"/>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-      <c r="B90" s="106">
-        <f t="shared" si="67"/>
+      <c r="B90" s="105">
+        <f t="shared" si="65"/>
         <v>81</v>
       </c>
       <c r="C90" s="55" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D90" s="82" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E90" s="78" t="s">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="F90" s="78" t="s">
-        <v>503</v>
+        <v>474</v>
       </c>
       <c r="G90" s="78" t="s">
-        <v>458</v>
-      </c>
-      <c r="H90" s="96" t="s">
-        <v>504</v>
+        <v>429</v>
+      </c>
+      <c r="H90" s="95" t="s">
+        <v>475</v>
       </c>
       <c r="I90" s="37"/>
       <c r="J90" s="37" t="s">
-        <v>505</v>
+        <v>476</v>
       </c>
       <c r="K90" s="38" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L90" s="37">
         <v>1</v>
       </c>
       <c r="M90" s="72">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N90" s="39">
         <v>21</v>
       </c>
       <c r="O90" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P90" s="39">
         <v>0.28160000000000002</v>
       </c>
       <c r="Q90" s="39">
-        <f t="shared" ref="Q90" si="71">P90*N90</f>
+        <f t="shared" ref="Q90" si="69">P90*N90</f>
         <v>5.9136000000000006</v>
       </c>
       <c r="R90" s="69"/>
     </row>
     <row r="91" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="B91" s="106">
-        <f t="shared" si="67"/>
+      <c r="B91" s="105">
+        <f t="shared" si="65"/>
         <v>82</v>
       </c>
       <c r="C91" s="77" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D91" s="71" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E91" s="37" t="s">
-        <v>418</v>
+        <v>390</v>
       </c>
       <c r="F91" s="37" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="H91" s="99" t="s">
-        <v>420</v>
+        <v>317</v>
+      </c>
+      <c r="H91" s="98" t="s">
+        <v>392</v>
       </c>
       <c r="I91" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J91" s="78" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="K91" s="79" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L91" s="78">
         <v>1</v>
       </c>
       <c r="M91" s="72">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N91" s="72">
         <v>21</v>
       </c>
       <c r="O91" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P91" s="72">
         <v>0.30709999999999998</v>
       </c>
       <c r="Q91" s="72">
-        <f t="shared" ref="Q91" si="72">N91*P91</f>
+        <f t="shared" ref="Q91" si="70">N91*P91</f>
         <v>6.4490999999999996</v>
       </c>
       <c r="R91" s="69"/>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
-      <c r="B92" s="106">
-        <f t="shared" si="67"/>
+      <c r="B92" s="105">
+        <f t="shared" si="65"/>
         <v>83</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D92" s="37" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E92" s="38" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="F92" s="37" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="G92" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="H92" s="99" t="s">
-        <v>207</v>
+        <v>128</v>
+      </c>
+      <c r="H92" s="98" t="s">
+        <v>190</v>
       </c>
       <c r="I92" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J92" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="K92" s="38" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L92" s="37">
         <v>1</v>
       </c>
       <c r="M92" s="39">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N92" s="39">
         <v>21</v>
       </c>
       <c r="O92" s="57" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="P92" s="39">
         <v>3.637</v>
       </c>
       <c r="Q92" s="39">
-        <f t="shared" ref="Q92" si="73">P92*N92</f>
+        <f t="shared" ref="Q92" si="71">P92*N92</f>
         <v>76.376999999999995</v>
       </c>
       <c r="R92" s="39"/>
     </row>
     <row r="93" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
-      <c r="B93" s="106">
-        <f t="shared" si="67"/>
+      <c r="B93" s="105">
+        <f t="shared" si="65"/>
         <v>84</v>
       </c>
       <c r="C93" s="77" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D93" s="78" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E93" s="79" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="F93" s="78" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G93" s="79" t="s">
-        <v>179</v>
-      </c>
-      <c r="H93" s="96" t="s">
-        <v>207</v>
+        <v>163</v>
+      </c>
+      <c r="H93" s="95" t="s">
+        <v>190</v>
       </c>
       <c r="I93" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J93" s="78" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="K93" s="79" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L93" s="78">
         <v>1</v>
       </c>
       <c r="M93" s="72">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N93" s="72">
         <v>25</v>
       </c>
       <c r="O93" s="80" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P93" s="72">
         <v>0.3463</v>
       </c>
       <c r="Q93" s="72">
-        <f t="shared" ref="Q93" si="74">N93*P93</f>
+        <f t="shared" ref="Q93" si="72">N93*P93</f>
         <v>8.6575000000000006</v>
       </c>
       <c r="R93" s="72"/>
     </row>
     <row r="94" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
-      <c r="B94" s="106">
-        <f t="shared" si="67"/>
+      <c r="B94" s="105">
+        <f t="shared" si="65"/>
         <v>85</v>
       </c>
       <c r="C94" s="63" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D94" s="64" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E94" s="65" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F94" s="64" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G94" s="65" t="s">
-        <v>180</v>
-      </c>
-      <c r="H94" s="104" t="s">
-        <v>208</v>
+        <v>164</v>
+      </c>
+      <c r="H94" s="103" t="s">
+        <v>191</v>
       </c>
       <c r="I94" s="64" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J94" s="64" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="K94" s="65" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L94" s="64">
         <v>1</v>
       </c>
       <c r="M94" s="66">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>20</v>
       </c>
       <c r="N94" s="66">
         <v>21</v>
       </c>
       <c r="O94" s="67" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P94" s="66">
         <v>7.4638</v>
       </c>
       <c r="Q94" s="66">
-        <f t="shared" ref="Q94" si="75">P94*N94</f>
+        <f t="shared" ref="Q94" si="73">P94*N94</f>
         <v>156.7398</v>
       </c>
       <c r="R94" s="66" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
-      <c r="B95" s="106">
-        <f t="shared" si="67"/>
+      <c r="B95" s="105">
+        <f t="shared" si="65"/>
         <v>86</v>
       </c>
-      <c r="C95" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="D95" s="78" t="s">
-        <v>57</v>
-      </c>
-      <c r="E95" s="79" t="s">
-        <v>116</v>
-      </c>
-      <c r="F95" s="78" t="s">
-        <v>142</v>
-      </c>
-      <c r="G95" s="79" t="s">
-        <v>181</v>
-      </c>
-      <c r="H95" s="96" t="s">
-        <v>209</v>
-      </c>
-      <c r="I95" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="J95" s="78" t="s">
-        <v>259</v>
-      </c>
-      <c r="K95" s="83" t="s">
-        <v>259</v>
-      </c>
-      <c r="L95" s="78">
+      <c r="C95" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="D95" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E95" s="37" t="s">
+        <v>516</v>
+      </c>
+      <c r="F95" s="37" t="s">
+        <v>517</v>
+      </c>
+      <c r="G95" s="37" t="s">
+        <v>492</v>
+      </c>
+      <c r="H95" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="I95" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="J95" s="37" t="s">
+        <v>518</v>
+      </c>
+      <c r="K95" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="L95" s="37">
         <v>1</v>
       </c>
-      <c r="M95" s="72">
-        <f t="shared" si="62"/>
-        <v>20</v>
-      </c>
-      <c r="N95" s="72">
-        <v>21</v>
-      </c>
-      <c r="O95" s="80" t="s">
-        <v>343</v>
-      </c>
-      <c r="P95" s="72">
-        <v>2.6459999999999999</v>
-      </c>
-      <c r="Q95" s="72">
-        <f t="shared" ref="Q95" si="76">N95*P95</f>
-        <v>55.565999999999995</v>
+      <c r="M95" s="37">
+        <f>L95*5</f>
+        <v>5</v>
+      </c>
+      <c r="N95" s="37">
+        <v>6</v>
+      </c>
+      <c r="O95" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="P95" s="106">
+        <v>2.6154999999999999</v>
+      </c>
+      <c r="Q95" s="106">
+        <f>P95*N95</f>
+        <v>15.693</v>
       </c>
       <c r="R95" s="72"/>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="B96" s="106">
-        <f t="shared" si="67"/>
+      <c r="B96" s="105">
+        <f t="shared" si="65"/>
         <v>87</v>
       </c>
       <c r="C96" s="77" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D96" s="78" t="s">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="E96" s="78" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="F96" s="78" t="s">
-        <v>507</v>
+        <v>478</v>
       </c>
       <c r="G96" s="78" t="s">
-        <v>509</v>
-      </c>
-      <c r="H96" s="99" t="s">
-        <v>207</v>
+        <v>480</v>
+      </c>
+      <c r="H96" s="98" t="s">
+        <v>190</v>
       </c>
       <c r="I96" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J96" s="78" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="K96" s="78" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L96" s="78">
         <v>1</v>
       </c>
-      <c r="M96" s="72">
-        <f t="shared" si="62"/>
-        <v>20</v>
+      <c r="M96" s="78">
+        <f t="shared" ref="M96" si="74">L96*5</f>
+        <v>5</v>
       </c>
       <c r="N96" s="78">
-        <v>21</v>
-      </c>
-      <c r="O96" s="113" t="s">
-        <v>286</v>
-      </c>
-      <c r="P96" s="112">
-        <v>5.4648000000000003</v>
-      </c>
-      <c r="Q96" s="112">
-        <f t="shared" ref="Q96" si="77">P96*N96</f>
-        <v>114.7608</v>
+        <v>6</v>
+      </c>
+      <c r="O96" s="109" t="s">
+        <v>263</v>
+      </c>
+      <c r="P96" s="108">
+        <v>6.2301000000000002</v>
+      </c>
+      <c r="Q96" s="108">
+        <f t="shared" ref="Q96" si="75">P96*N96</f>
+        <v>37.380600000000001</v>
       </c>
       <c r="R96" s="78"/>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
-      <c r="B97" s="106">
-        <f t="shared" si="67"/>
+      <c r="B97" s="105">
+        <f t="shared" si="65"/>
         <v>88</v>
       </c>
       <c r="C97" s="55" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D97" s="37" t="s">
-        <v>450</v>
+        <v>421</v>
       </c>
       <c r="E97" s="37" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>512</v>
-      </c>
-      <c r="H97" s="99" t="s">
-        <v>207</v>
+        <v>483</v>
+      </c>
+      <c r="H97" s="98" t="s">
+        <v>190</v>
       </c>
       <c r="I97" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="J97" s="37" t="s">
-        <v>511</v>
+        <v>482</v>
       </c>
       <c r="K97" s="37" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L97" s="37">
         <v>1</v>
       </c>
-      <c r="M97" s="72">
-        <f t="shared" si="62"/>
-        <v>20</v>
+      <c r="M97" s="37">
+        <f>L97*5</f>
+        <v>5</v>
       </c>
       <c r="N97" s="37">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="O97" s="70" t="s">
-        <v>286</v>
-      </c>
-      <c r="P97" s="110">
-        <v>4.1475</v>
-      </c>
-      <c r="Q97" s="110">
+        <v>263</v>
+      </c>
+      <c r="P97" s="106">
+        <v>4.7154999999999996</v>
+      </c>
+      <c r="Q97" s="106">
         <f>P97*N97</f>
-        <v>87.097499999999997</v>
+        <v>28.292999999999999</v>
       </c>
       <c r="R97" s="37"/>
     </row>
     <row r="98" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
-      <c r="B98" s="106">
-        <f t="shared" si="67"/>
+      <c r="B98" s="105">
+        <f t="shared" si="65"/>
         <v>89</v>
       </c>
       <c r="C98" s="55" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D98" s="37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E98" s="38" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F98" s="37" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="G98" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="H98" s="99" t="s">
-        <v>207</v>
-      </c>
-      <c r="I98" s="97" t="s">
-        <v>259</v>
-      </c>
-      <c r="J98" s="97" t="s">
-        <v>349</v>
+        <v>132</v>
+      </c>
+      <c r="H98" s="98" t="s">
+        <v>190</v>
+      </c>
+      <c r="I98" s="96" t="s">
+        <v>236</v>
+      </c>
+      <c r="J98" s="96" t="s">
+        <v>322</v>
       </c>
       <c r="K98" s="38" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="L98" s="37">
         <v>1</v>
@@ -8008,13 +8008,13 @@
         <v>21</v>
       </c>
       <c r="O98" s="57" t="s">
-        <v>286</v>
+        <v>263</v>
       </c>
       <c r="P98" s="39">
         <v>0.39140000000000003</v>
       </c>
       <c r="Q98" s="39">
-        <f t="shared" ref="Q98" si="78">P98*N98</f>
+        <f t="shared" ref="Q98" si="76">P98*N98</f>
         <v>8.2194000000000003</v>
       </c>
       <c r="R98" s="39"/>
@@ -8037,12 +8037,12 @@
       <c r="M99" s="36"/>
       <c r="N99" s="36"/>
       <c r="O99" s="61" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="P99" s="59"/>
       <c r="Q99" s="59">
         <f>SUM(Q10:Q98)</f>
-        <v>1102.7587000000001</v>
+        <v>937.50607999999977</v>
       </c>
       <c r="R99" s="41"/>
     </row>
@@ -8064,12 +8064,12 @@
       <c r="M100" s="9"/>
       <c r="N100" s="9"/>
       <c r="O100" s="62" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="P100" s="60"/>
-      <c r="Q100" s="105">
+      <c r="Q100" s="104">
         <f>Q99/20</f>
-        <v>55.137935000000006</v>
+        <v>46.875303999999986</v>
       </c>
       <c r="R100" s="42"/>
     </row>
@@ -8081,6 +8081,15 @@
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A104" s="1"/>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A105" s="1"/>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A106" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8111,69 +8120,69 @@
     <hyperlink ref="O35" r:id="rId21"/>
     <hyperlink ref="O36" r:id="rId22"/>
     <hyperlink ref="O37" r:id="rId23"/>
-    <hyperlink ref="O46" r:id="rId24"/>
-    <hyperlink ref="O47" r:id="rId25"/>
-    <hyperlink ref="O48" r:id="rId26"/>
-    <hyperlink ref="O50" r:id="rId27"/>
-    <hyperlink ref="O51" r:id="rId28"/>
-    <hyperlink ref="O55" r:id="rId29"/>
-    <hyperlink ref="O56" r:id="rId30"/>
-    <hyperlink ref="O58" r:id="rId31"/>
-    <hyperlink ref="O62" r:id="rId32"/>
-    <hyperlink ref="O63" r:id="rId33"/>
-    <hyperlink ref="O64" r:id="rId34"/>
-    <hyperlink ref="O65" r:id="rId35"/>
-    <hyperlink ref="O66" r:id="rId36"/>
-    <hyperlink ref="O67" r:id="rId37"/>
+    <hyperlink ref="O47" r:id="rId24"/>
+    <hyperlink ref="O48" r:id="rId25"/>
+    <hyperlink ref="O49" r:id="rId26"/>
+    <hyperlink ref="O51" r:id="rId27"/>
+    <hyperlink ref="O52" r:id="rId28"/>
+    <hyperlink ref="O56" r:id="rId29"/>
+    <hyperlink ref="O57" r:id="rId30"/>
+    <hyperlink ref="O59" r:id="rId31"/>
+    <hyperlink ref="O63" r:id="rId32"/>
+    <hyperlink ref="O65" r:id="rId33"/>
+    <hyperlink ref="O66" r:id="rId34"/>
+    <hyperlink ref="O67" r:id="rId35"/>
+    <hyperlink ref="O68" r:id="rId36"/>
+    <hyperlink ref="O69" r:id="rId37"/>
     <hyperlink ref="O80" r:id="rId38"/>
-    <hyperlink ref="O71" r:id="rId39"/>
-    <hyperlink ref="O72" r:id="rId40"/>
-    <hyperlink ref="O73" r:id="rId41"/>
-    <hyperlink ref="O74" r:id="rId42"/>
-    <hyperlink ref="O75" r:id="rId43"/>
-    <hyperlink ref="O76" r:id="rId44"/>
-    <hyperlink ref="O77" r:id="rId45"/>
-    <hyperlink ref="O78" r:id="rId46"/>
-    <hyperlink ref="O79" r:id="rId47"/>
-    <hyperlink ref="O81" r:id="rId48"/>
-    <hyperlink ref="O82" r:id="rId49"/>
-    <hyperlink ref="O83" r:id="rId50"/>
-    <hyperlink ref="O86" r:id="rId51"/>
-    <hyperlink ref="O84" r:id="rId52"/>
-    <hyperlink ref="O88" r:id="rId53"/>
-    <hyperlink ref="O89" r:id="rId54"/>
-    <hyperlink ref="O91" r:id="rId55"/>
-    <hyperlink ref="O92" r:id="rId56"/>
-    <hyperlink ref="O93" r:id="rId57"/>
-    <hyperlink ref="O94" r:id="rId58"/>
-    <hyperlink ref="O95" r:id="rId59"/>
-    <hyperlink ref="O98" r:id="rId60"/>
-    <hyperlink ref="O70" r:id="rId61"/>
-    <hyperlink ref="O10" r:id="rId62"/>
-    <hyperlink ref="O87" r:id="rId63"/>
-    <hyperlink ref="O69" r:id="rId64"/>
-    <hyperlink ref="O38" r:id="rId65"/>
-    <hyperlink ref="O39" r:id="rId66"/>
-    <hyperlink ref="O49" r:id="rId67"/>
-    <hyperlink ref="O52" r:id="rId68"/>
-    <hyperlink ref="O54" r:id="rId69"/>
-    <hyperlink ref="O60" r:id="rId70"/>
-    <hyperlink ref="O53" r:id="rId71"/>
-    <hyperlink ref="O26" r:id="rId72"/>
-    <hyperlink ref="O27" r:id="rId73"/>
-    <hyperlink ref="O28" r:id="rId74"/>
-    <hyperlink ref="O31" r:id="rId75"/>
-    <hyperlink ref="O40" r:id="rId76"/>
-    <hyperlink ref="O41" r:id="rId77"/>
-    <hyperlink ref="O42" r:id="rId78"/>
-    <hyperlink ref="O43" r:id="rId79"/>
-    <hyperlink ref="O44" r:id="rId80"/>
-    <hyperlink ref="O45" r:id="rId81"/>
-    <hyperlink ref="O57" r:id="rId82"/>
-    <hyperlink ref="O68" r:id="rId83"/>
-    <hyperlink ref="O96" r:id="rId84"/>
-    <hyperlink ref="O97" r:id="rId85"/>
-    <hyperlink ref="O90" r:id="rId86"/>
+    <hyperlink ref="O76" r:id="rId39"/>
+    <hyperlink ref="O77" r:id="rId40"/>
+    <hyperlink ref="O78" r:id="rId41"/>
+    <hyperlink ref="O79" r:id="rId42"/>
+    <hyperlink ref="O81" r:id="rId43"/>
+    <hyperlink ref="O82" r:id="rId44"/>
+    <hyperlink ref="O83" r:id="rId45"/>
+    <hyperlink ref="O86" r:id="rId46"/>
+    <hyperlink ref="O84" r:id="rId47"/>
+    <hyperlink ref="O88" r:id="rId48"/>
+    <hyperlink ref="O89" r:id="rId49"/>
+    <hyperlink ref="O91" r:id="rId50"/>
+    <hyperlink ref="O92" r:id="rId51"/>
+    <hyperlink ref="O93" r:id="rId52"/>
+    <hyperlink ref="O94" r:id="rId53"/>
+    <hyperlink ref="O98" r:id="rId54"/>
+    <hyperlink ref="O73" r:id="rId55"/>
+    <hyperlink ref="O10" r:id="rId56"/>
+    <hyperlink ref="O87" r:id="rId57"/>
+    <hyperlink ref="O72" r:id="rId58"/>
+    <hyperlink ref="O38" r:id="rId59"/>
+    <hyperlink ref="O39" r:id="rId60"/>
+    <hyperlink ref="O50" r:id="rId61"/>
+    <hyperlink ref="O53" r:id="rId62"/>
+    <hyperlink ref="O55" r:id="rId63"/>
+    <hyperlink ref="O61" r:id="rId64"/>
+    <hyperlink ref="O54" r:id="rId65"/>
+    <hyperlink ref="O26" r:id="rId66"/>
+    <hyperlink ref="O27" r:id="rId67"/>
+    <hyperlink ref="O28" r:id="rId68"/>
+    <hyperlink ref="O31" r:id="rId69"/>
+    <hyperlink ref="O40" r:id="rId70"/>
+    <hyperlink ref="O41" r:id="rId71"/>
+    <hyperlink ref="O42" r:id="rId72"/>
+    <hyperlink ref="O43" r:id="rId73"/>
+    <hyperlink ref="O44" r:id="rId74"/>
+    <hyperlink ref="O45" r:id="rId75"/>
+    <hyperlink ref="O58" r:id="rId76"/>
+    <hyperlink ref="O70" r:id="rId77"/>
+    <hyperlink ref="O90" r:id="rId78"/>
+    <hyperlink ref="O46" r:id="rId79"/>
+    <hyperlink ref="O64" r:id="rId80"/>
+    <hyperlink ref="O71" r:id="rId81"/>
+    <hyperlink ref="O74" r:id="rId82"/>
+    <hyperlink ref="O75" r:id="rId83"/>
+    <hyperlink ref="O95" r:id="rId84"/>
+    <hyperlink ref="O96" r:id="rId85"/>
+    <hyperlink ref="O97" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId87"/>

--- a/Design-Files/SM_Top_Board_v3.4/BOM/eSpark BOM_Top (20 Boards).xlsx
+++ b/Design-Files/SM_Top_Board_v3.4/BOM/eSpark BOM_Top (20 Boards).xlsx
@@ -5138,9 +5138,9 @@
       <c r="L46" s="37">
         <v>1</v>
       </c>
-      <c r="M46" s="37">
-        <f>L46*5</f>
-        <v>5</v>
+      <c r="M46" s="91">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="N46" s="37">
         <v>50</v>
@@ -6132,12 +6132,12 @@
       <c r="L64" s="78">
         <v>1</v>
       </c>
-      <c r="M64" s="78">
-        <f t="shared" ref="M64" si="43">L64*5</f>
-        <v>5</v>
+      <c r="M64" s="39">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="N64" s="78">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O64" s="109" t="s">
         <v>263</v>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="Q64" s="108">
         <f t="shared" si="42"/>
-        <v>9.9138000000000002</v>
+        <v>34.698300000000003</v>
       </c>
       <c r="R64" s="78"/>
     </row>
@@ -6201,7 +6201,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q65" s="72">
-        <f t="shared" ref="Q65" si="44">N65*P65</f>
+        <f t="shared" ref="Q65" si="43">N65*P65</f>
         <v>0.1</v>
       </c>
       <c r="R65" s="72"/>
@@ -6256,7 +6256,7 @@
         <v>1.4E-3</v>
       </c>
       <c r="Q66" s="39">
-        <f t="shared" ref="Q66" si="45">P66*N66</f>
+        <f t="shared" ref="Q66" si="44">P66*N66</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R66" s="39"/>
@@ -6311,7 +6311,7 @@
         <v>1.6000000000000001E-3</v>
       </c>
       <c r="Q67" s="72">
-        <f t="shared" ref="Q67" si="46">N67*P67</f>
+        <f t="shared" ref="Q67" si="45">N67*P67</f>
         <v>0.16</v>
       </c>
       <c r="R67" s="72"/>
@@ -6366,7 +6366,7 @@
         <v>1.4E-3</v>
       </c>
       <c r="Q68" s="39">
-        <f t="shared" ref="Q68" si="47">P68*N68</f>
+        <f t="shared" ref="Q68" si="46">P68*N68</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R68" s="39"/>
@@ -6421,7 +6421,7 @@
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q69" s="72">
-        <f t="shared" ref="Q69" si="48">N69*P69</f>
+        <f t="shared" ref="Q69" si="47">N69*P69</f>
         <v>0.13</v>
       </c>
       <c r="R69" s="72"/>
@@ -6476,7 +6476,7 @@
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q70" s="108">
-        <f t="shared" ref="Q70" si="49">P70*N70</f>
+        <f t="shared" ref="Q70" si="48">P70*N70</f>
         <v>0.09</v>
       </c>
       <c r="R70" s="78"/>
@@ -6517,12 +6517,12 @@
       <c r="L71" s="37">
         <v>1</v>
       </c>
-      <c r="M71" s="37">
-        <f>L71*5</f>
-        <v>5</v>
+      <c r="M71" s="72">
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="N71" s="37">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="O71" s="70" t="s">
         <v>263</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Q71" s="106">
         <f>P71*N71</f>
-        <v>0.52</v>
+        <v>1.04</v>
       </c>
       <c r="R71" s="37"/>
     </row>
@@ -6586,7 +6586,7 @@
         <v>2.9100000000000001E-2</v>
       </c>
       <c r="Q72" s="39">
-        <f t="shared" ref="Q72" si="50">P72*N72</f>
+        <f t="shared" ref="Q72" si="49">P72*N72</f>
         <v>1.3095000000000001</v>
       </c>
       <c r="R72" s="39"/>
@@ -6641,7 +6641,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q73" s="37">
-        <f t="shared" ref="Q73" si="51">N73*P73</f>
+        <f t="shared" ref="Q73" si="50">N73*P73</f>
         <v>0.22</v>
       </c>
       <c r="R73" s="68"/>
@@ -6682,12 +6682,12 @@
       <c r="L74" s="78">
         <v>2</v>
       </c>
-      <c r="M74" s="78">
-        <f t="shared" ref="M74" si="52">L74*5</f>
-        <v>10</v>
+      <c r="M74" s="37">
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="N74" s="78">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="O74" s="109" t="s">
         <v>519</v>
@@ -6696,8 +6696,8 @@
         <v>4.9800000000000001E-3</v>
       </c>
       <c r="Q74" s="108">
-        <f t="shared" ref="Q74" si="53">P74*N74</f>
-        <v>5.4780000000000002E-2</v>
+        <f t="shared" ref="Q74" si="51">P74*N74</f>
+        <v>0.20418</v>
       </c>
       <c r="R74" s="39"/>
     </row>
@@ -6738,11 +6738,11 @@
         <v>1</v>
       </c>
       <c r="M75" s="37">
-        <f>L75*5</f>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="N75" s="37">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O75" s="70" t="s">
         <v>297</v>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="Q75" s="106">
         <f>P75*N75</f>
-        <v>2.52E-2</v>
+        <v>8.8200000000000001E-2</v>
       </c>
       <c r="R75" s="72"/>
     </row>
@@ -6806,7 +6806,7 @@
         <v>4.6699999999999997E-3</v>
       </c>
       <c r="Q76" s="39">
-        <f t="shared" ref="Q76" si="54">P76*N76</f>
+        <f t="shared" ref="Q76" si="52">P76*N76</f>
         <v>0.23349999999999999</v>
       </c>
       <c r="R76" s="39"/>
@@ -6861,7 +6861,7 @@
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q77" s="72">
-        <f t="shared" ref="Q77" si="55">N77*P77</f>
+        <f t="shared" ref="Q77" si="53">N77*P77</f>
         <v>0.34499999999999997</v>
       </c>
       <c r="R77" s="72"/>
@@ -6916,7 +6916,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="Q78" s="39">
-        <f t="shared" ref="Q78" si="56">P78*N78</f>
+        <f t="shared" ref="Q78" si="54">P78*N78</f>
         <v>0.11</v>
       </c>
       <c r="R78" s="39"/>
@@ -6971,7 +6971,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="Q79" s="39">
-        <f t="shared" ref="Q79" si="57">P79*N79</f>
+        <f t="shared" ref="Q79" si="55">P79*N79</f>
         <v>0.15</v>
       </c>
       <c r="R79" s="39"/>
@@ -7079,7 +7079,7 @@
         <v>1.5E-3</v>
       </c>
       <c r="Q81" s="39">
-        <f t="shared" ref="Q81" si="58">P81*N81</f>
+        <f t="shared" ref="Q81" si="56">P81*N81</f>
         <v>0.15</v>
       </c>
       <c r="R81" s="39"/>
@@ -7134,7 +7134,7 @@
         <v>8.5400000000000004E-2</v>
       </c>
       <c r="Q82" s="72">
-        <f t="shared" ref="Q82" si="59">N82*P82</f>
+        <f t="shared" ref="Q82" si="57">N82*P82</f>
         <v>2.1350000000000002</v>
       </c>
       <c r="R82" s="72"/>
@@ -7176,7 +7176,7 @@
         <v>1</v>
       </c>
       <c r="M83" s="39">
-        <f t="shared" ref="M83:M94" si="60">L83*20</f>
+        <f t="shared" ref="M83:M98" si="58">L83*20</f>
         <v>20</v>
       </c>
       <c r="N83" s="39">
@@ -7189,7 +7189,7 @@
         <v>3.8E-3</v>
       </c>
       <c r="Q83" s="39">
-        <f t="shared" ref="Q83" si="61">P83*N83</f>
+        <f t="shared" ref="Q83" si="59">P83*N83</f>
         <v>0.19</v>
       </c>
       <c r="R83" s="68"/>
@@ -7244,7 +7244,7 @@
         <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q84" s="72">
-        <f t="shared" ref="Q84" si="62">N84*P84</f>
+        <f t="shared" ref="Q84" si="60">N84*P84</f>
         <v>0.24</v>
       </c>
       <c r="R84" s="68"/>
@@ -7286,7 +7286,7 @@
         <v>1</v>
       </c>
       <c r="M85" s="39">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N85" s="39">
@@ -7299,7 +7299,7 @@
         <v>1E-3</v>
       </c>
       <c r="Q85" s="39">
-        <f t="shared" ref="Q85" si="63">P85*N85</f>
+        <f t="shared" ref="Q85" si="61">P85*N85</f>
         <v>0.1</v>
       </c>
       <c r="R85" s="39"/>
@@ -7341,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="M86" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N86" s="72">
@@ -7354,7 +7354,7 @@
         <v>4.3E-3</v>
       </c>
       <c r="Q86" s="72">
-        <f t="shared" ref="Q86" si="64">N86*P86</f>
+        <f t="shared" ref="Q86" si="62">N86*P86</f>
         <v>0.215</v>
       </c>
       <c r="R86" s="72"/>
@@ -7362,7 +7362,7 @@
     <row r="87" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="105">
-        <f t="shared" ref="B87:B98" si="65">ROW(B87) - ROW($B$9)</f>
+        <f t="shared" ref="B87:B98" si="63">ROW(B87) - ROW($B$9)</f>
         <v>78</v>
       </c>
       <c r="C87" s="77" t="s">
@@ -7396,11 +7396,11 @@
         <v>1</v>
       </c>
       <c r="M87" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N87" s="72">
-        <f t="shared" ref="N87" si="66">M87+(M87*0.1)</f>
+        <f t="shared" ref="N87" si="64">M87+(M87*0.1)</f>
         <v>22</v>
       </c>
       <c r="O87" s="80" t="s">
@@ -7417,7 +7417,7 @@
     <row r="88" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>79</v>
       </c>
       <c r="C88" s="55" t="s">
@@ -7451,7 +7451,7 @@
         <v>1</v>
       </c>
       <c r="M88" s="39">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N88" s="39">
@@ -7464,7 +7464,7 @@
         <v>3.81</v>
       </c>
       <c r="Q88" s="39">
-        <f t="shared" ref="Q88" si="67">P88*N88</f>
+        <f t="shared" ref="Q88" si="65">P88*N88</f>
         <v>80.010000000000005</v>
       </c>
       <c r="R88" s="39"/>
@@ -7472,7 +7472,7 @@
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>80</v>
       </c>
       <c r="C89" s="77" t="s">
@@ -7506,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="M89" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N89" s="72">
@@ -7519,7 +7519,7 @@
         <v>2.48</v>
       </c>
       <c r="Q89" s="72">
-        <f t="shared" ref="Q89" si="68">N89*P89</f>
+        <f t="shared" ref="Q89" si="66">N89*P89</f>
         <v>52.08</v>
       </c>
       <c r="R89" s="72"/>
@@ -7527,7 +7527,7 @@
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>81</v>
       </c>
       <c r="C90" s="55" t="s">
@@ -7559,7 +7559,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N90" s="39">
@@ -7572,7 +7572,7 @@
         <v>0.28160000000000002</v>
       </c>
       <c r="Q90" s="39">
-        <f t="shared" ref="Q90" si="69">P90*N90</f>
+        <f t="shared" ref="Q90" si="67">P90*N90</f>
         <v>5.9136000000000006</v>
       </c>
       <c r="R90" s="69"/>
@@ -7580,7 +7580,7 @@
     <row r="91" spans="1:18" ht="36" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>82</v>
       </c>
       <c r="C91" s="77" t="s">
@@ -7614,7 +7614,7 @@
         <v>1</v>
       </c>
       <c r="M91" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N91" s="72">
@@ -7627,7 +7627,7 @@
         <v>0.30709999999999998</v>
       </c>
       <c r="Q91" s="72">
-        <f t="shared" ref="Q91" si="70">N91*P91</f>
+        <f t="shared" ref="Q91" si="68">N91*P91</f>
         <v>6.4490999999999996</v>
       </c>
       <c r="R91" s="69"/>
@@ -7635,7 +7635,7 @@
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>83</v>
       </c>
       <c r="C92" s="55" t="s">
@@ -7669,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="M92" s="39">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N92" s="39">
@@ -7682,7 +7682,7 @@
         <v>3.637</v>
       </c>
       <c r="Q92" s="39">
-        <f t="shared" ref="Q92" si="71">P92*N92</f>
+        <f t="shared" ref="Q92" si="69">P92*N92</f>
         <v>76.376999999999995</v>
       </c>
       <c r="R92" s="39"/>
@@ -7690,7 +7690,7 @@
     <row r="93" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>84</v>
       </c>
       <c r="C93" s="77" t="s">
@@ -7724,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="M93" s="72">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N93" s="72">
@@ -7737,7 +7737,7 @@
         <v>0.3463</v>
       </c>
       <c r="Q93" s="72">
-        <f t="shared" ref="Q93" si="72">N93*P93</f>
+        <f t="shared" ref="Q93" si="70">N93*P93</f>
         <v>8.6575000000000006</v>
       </c>
       <c r="R93" s="72"/>
@@ -7745,7 +7745,7 @@
     <row r="94" spans="1:18" ht="24" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>85</v>
       </c>
       <c r="C94" s="63" t="s">
@@ -7779,7 +7779,7 @@
         <v>1</v>
       </c>
       <c r="M94" s="66">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="N94" s="66">
@@ -7792,7 +7792,7 @@
         <v>7.4638</v>
       </c>
       <c r="Q94" s="66">
-        <f t="shared" ref="Q94" si="73">P94*N94</f>
+        <f t="shared" ref="Q94" si="71">P94*N94</f>
         <v>156.7398</v>
       </c>
       <c r="R94" s="66" t="s">
@@ -7802,7 +7802,7 @@
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>86</v>
       </c>
       <c r="C95" s="55" t="s">
@@ -7836,11 +7836,11 @@
         <v>1</v>
       </c>
       <c r="M95" s="37">
-        <f>L95*5</f>
-        <v>5</v>
+        <f>L95*20</f>
+        <v>20</v>
       </c>
       <c r="N95" s="37">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O95" s="70" t="s">
         <v>263</v>
@@ -7850,14 +7850,14 @@
       </c>
       <c r="Q95" s="106">
         <f>P95*N95</f>
-        <v>15.693</v>
+        <v>54.9255</v>
       </c>
       <c r="R95" s="72"/>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>87</v>
       </c>
       <c r="C96" s="77" t="s">
@@ -7890,12 +7890,12 @@
       <c r="L96" s="78">
         <v>1</v>
       </c>
-      <c r="M96" s="78">
-        <f t="shared" ref="M96" si="74">L96*5</f>
-        <v>5</v>
+      <c r="M96" s="37">
+        <f t="shared" ref="M96:M97" si="72">L96*20</f>
+        <v>20</v>
       </c>
       <c r="N96" s="78">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O96" s="109" t="s">
         <v>263</v>
@@ -7904,15 +7904,15 @@
         <v>6.2301000000000002</v>
       </c>
       <c r="Q96" s="108">
-        <f t="shared" ref="Q96" si="75">P96*N96</f>
-        <v>37.380600000000001</v>
+        <f t="shared" ref="Q96" si="73">P96*N96</f>
+        <v>130.8321</v>
       </c>
       <c r="R96" s="78"/>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>88</v>
       </c>
       <c r="C97" s="55" t="s">
@@ -7946,11 +7946,11 @@
         <v>1</v>
       </c>
       <c r="M97" s="37">
-        <f>L97*5</f>
-        <v>5</v>
+        <f t="shared" si="72"/>
+        <v>20</v>
       </c>
       <c r="N97" s="37">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O97" s="70" t="s">
         <v>263</v>
@@ -7960,14 +7960,14 @@
       </c>
       <c r="Q97" s="106">
         <f>P97*N97</f>
-        <v>28.292999999999999</v>
+        <v>99.025499999999994</v>
       </c>
       <c r="R97" s="37"/>
     </row>
     <row r="98" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="105">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>89</v>
       </c>
       <c r="C98" s="55" t="s">
@@ -8014,7 +8014,7 @@
         <v>0.39140000000000003</v>
       </c>
       <c r="Q98" s="39">
-        <f t="shared" ref="Q98" si="76">P98*N98</f>
+        <f t="shared" ref="Q98" si="74">P98*N98</f>
         <v>8.2194000000000003</v>
       </c>
       <c r="R98" s="39"/>
@@ -8042,7 +8042,7 @@
       <c r="P99" s="59"/>
       <c r="Q99" s="59">
         <f>SUM(Q10:Q98)</f>
-        <v>937.50607999999977</v>
+        <v>1166.43948</v>
       </c>
       <c r="R99" s="41"/>
     </row>
@@ -8069,7 +8069,7 @@
       <c r="P100" s="60"/>
       <c r="Q100" s="104">
         <f>Q99/20</f>
-        <v>46.875303999999986</v>
+        <v>58.321973999999997</v>
       </c>
       <c r="R100" s="42"/>
     </row>
